--- a/GovGrade11.xlsx
+++ b/GovGrade11.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB31"/>
+  <dimension ref="A1:DT31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,107 +611,457 @@
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>22T-21</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>23T-22</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>24T-23</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>25T-24</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>26T-25</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>27T-26</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>28T-27</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>29T-28</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>30T-29</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>31T-30</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>32T-31</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>33T-32</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>34T-33</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>35T-34</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>36T-35</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>37T-36</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>38T-37</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>39T-38</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>40T-39</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>41T-40</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>42T-41</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>43T-42</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>44T-43</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>45T-44</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>46T-45</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>47T-46</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>48T-47</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>49T-48</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>50T-49</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>51T-50</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>52T-51</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>53T-52</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>54T-53</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>55T-54</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>56T-55</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
           <t>1U</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>2U-1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>3U-2</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>4U-3</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>5U-4</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>6U-5</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>7U-6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>8U-7</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>9U-8</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>10U-9</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>11U-10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>12U-11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>13U-12</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>14U-13</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>15U-14</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>16U-15</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>17U-16</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>18U-17</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>19U-18</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>20U-19</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>21U-20</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>22U-21</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>23U-22</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>24U-23</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>25U-24</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>26U-25</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>27U-26</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>28U-27</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>29U-28</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>30U-29</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>31U-30</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>32U-31</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>33U-32</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>34U-33</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>35U-34</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>36U-35</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>37U-36</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>38U-37</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>39U-38</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>40U-39</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>41U-40</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>42U-41</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>43U-42</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>44U-43</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>45U-44</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>46U-45</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>47U-46</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>48U-47</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>49U-48</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>50U-49</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>51U-50</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>52U-51</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>53U-52</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>54U-53</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>55U-54</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>56U-55</t>
         </is>
       </c>
     </row>
@@ -871,89 +1221,159 @@
       </c>
       <c r="AH2" s="2" t="inlineStr"/>
       <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr"/>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="inlineStr"/>
+      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BB2" s="2" t="inlineStr"/>
+      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BD2" s="2" t="inlineStr"/>
+      <c r="BE2" s="2" t="inlineStr"/>
+      <c r="BF2" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BM2" s="2" t="inlineStr"/>
+      <c r="BN2" s="2" t="inlineStr"/>
+      <c r="BO2" s="2" t="inlineStr"/>
+      <c r="BP2" s="2" t="inlineStr"/>
+      <c r="BQ2" s="2" t="inlineStr"/>
+      <c r="BR2" s="2" t="inlineStr"/>
+      <c r="BS2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1jBmcXzjQZy7_LBggEl-bB6kqt1i5GBDl#list</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="BT2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1IyCOezpyLUlFnRWQTJqKNPSqM24Wx47f#list</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="BU2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=11C8DFqBFMyYl-w-oVJg3BujXkTS_AWOo#list</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="BV2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=156jv_Gmaa0-YQ2UR-k5XViPaexpwHB3o#list</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="BW2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1z-n-Yrpj8a19j8fIjlmKw76HjoNlrD5x#list</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="BX2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1fINv6lYOTMEIX8Y8NpackweT40e_18B2#list</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="BY2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1d9MWCXiOQBy2KD5OVxauc4ZolcUBstAP#list</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="BZ2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1WfwqM8BuCS4xs47LgsewBLKskwavom1h#list</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="CA2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=19Vf_wrL1r9RdUQYwl5gcLxjlOaAr9LLl#list</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="CB2" s="2" t="inlineStr"/>
+      <c r="CC2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=16dhNdQm2iBYXnbcaX03W0O0aGamVR2Z8#list</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1fhDNic3lznUAiGajIqb2JwY4vjUPD9Yx#list</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="CE2" s="2" t="inlineStr"/>
+      <c r="CF2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1jhm7yeH4PzbTmLdNSiziKgXGHXgy2VZD#list</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr">
+      <c r="CG2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=14KrYSmdB6lxJPmjUly7CuhF_LwKqpxxo#list</t>
         </is>
       </c>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr">
+      <c r="CH2" s="2" t="inlineStr"/>
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1VEvQJTuSlkTxNqg_1x2bqzdhCWhrPbH-#list</t>
         </is>
       </c>
-      <c r="BA2" s="2" t="inlineStr">
+      <c r="CJ2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Y1Ughq7bnLzzfooC28hBKw5gXEqglTna#list</t>
         </is>
       </c>
-      <c r="BB2" s="2" t="inlineStr">
+      <c r="CK2" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1cfvYHTbOjvBw_Lg-GIhwW5h73KJ35sU8#list</t>
         </is>
       </c>
+      <c r="CL2" s="2" t="inlineStr"/>
+      <c r="CM2" s="2" t="inlineStr"/>
+      <c r="CN2" s="2" t="inlineStr"/>
+      <c r="CO2" s="2" t="inlineStr"/>
+      <c r="CP2" s="2" t="inlineStr"/>
+      <c r="CQ2" s="2" t="inlineStr"/>
+      <c r="CR2" s="2" t="inlineStr"/>
+      <c r="CS2" s="2" t="inlineStr"/>
+      <c r="CT2" s="2" t="inlineStr"/>
+      <c r="CU2" s="2" t="inlineStr"/>
+      <c r="CV2" s="2" t="inlineStr"/>
+      <c r="CW2" s="2" t="inlineStr"/>
+      <c r="CX2" s="2" t="inlineStr"/>
+      <c r="CY2" s="2" t="inlineStr"/>
+      <c r="CZ2" s="2" t="inlineStr"/>
+      <c r="DA2" s="2" t="inlineStr"/>
+      <c r="DB2" s="2" t="inlineStr"/>
+      <c r="DC2" s="2" t="inlineStr"/>
+      <c r="DD2" s="2" t="inlineStr"/>
+      <c r="DE2" s="2" t="inlineStr"/>
+      <c r="DF2" s="2" t="inlineStr"/>
+      <c r="DG2" s="2" t="inlineStr"/>
+      <c r="DH2" s="2" t="inlineStr"/>
+      <c r="DI2" s="2" t="inlineStr"/>
+      <c r="DJ2" s="2" t="inlineStr"/>
+      <c r="DK2" s="2" t="inlineStr"/>
+      <c r="DL2" s="2" t="inlineStr"/>
+      <c r="DM2" s="2" t="inlineStr"/>
+      <c r="DN2" s="2" t="inlineStr"/>
+      <c r="DO2" s="2" t="inlineStr"/>
+      <c r="DP2" s="2" t="inlineStr"/>
+      <c r="DQ2" s="2" t="inlineStr"/>
+      <c r="DR2" s="2" t="inlineStr"/>
+      <c r="DS2" s="2" t="inlineStr"/>
+      <c r="DT2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1115,49 +1535,119 @@
       <c r="AK3" s="2" t="inlineStr"/>
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=11YfMXHZoN5Lmoa-582mdGyI2jSOh84ex#list</t>
-        </is>
-      </c>
+      <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1jhBl7mHuJKq5nrcL7n5OnAWieWndHkP-#list</t>
-        </is>
-      </c>
+      <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
       <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1rWTO-NQja9bwLmrb7YGn96KFifiDz-TQ#list</t>
-        </is>
-      </c>
+      <c r="AT3" s="2" t="inlineStr"/>
       <c r="AU3" s="2" t="inlineStr"/>
       <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1JjumxxIPE98HFpjzB89nsn5qU04Ve3cb#list</t>
-        </is>
-      </c>
+      <c r="AW3" s="2" t="inlineStr"/>
       <c r="AX3" s="2" t="inlineStr"/>
       <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr">
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr"/>
+      <c r="BC3" s="2" t="inlineStr"/>
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr"/>
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BM3" s="2" t="inlineStr"/>
+      <c r="BN3" s="2" t="inlineStr"/>
+      <c r="BO3" s="2" t="inlineStr"/>
+      <c r="BP3" s="2" t="inlineStr"/>
+      <c r="BQ3" s="2" t="inlineStr"/>
+      <c r="BR3" s="2" t="inlineStr"/>
+      <c r="BS3" s="2" t="inlineStr"/>
+      <c r="BT3" s="2" t="inlineStr"/>
+      <c r="BU3" s="2" t="inlineStr"/>
+      <c r="BV3" s="2" t="inlineStr"/>
+      <c r="BW3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11YfMXHZoN5Lmoa-582mdGyI2jSOh84ex#list</t>
+        </is>
+      </c>
+      <c r="BX3" s="2" t="inlineStr"/>
+      <c r="BY3" s="2" t="inlineStr"/>
+      <c r="BZ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jhBl7mHuJKq5nrcL7n5OnAWieWndHkP-#list</t>
+        </is>
+      </c>
+      <c r="CA3" s="2" t="inlineStr"/>
+      <c r="CB3" s="2" t="inlineStr"/>
+      <c r="CC3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rWTO-NQja9bwLmrb7YGn96KFifiDz-TQ#list</t>
+        </is>
+      </c>
+      <c r="CD3" s="2" t="inlineStr"/>
+      <c r="CE3" s="2" t="inlineStr"/>
+      <c r="CF3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1JjumxxIPE98HFpjzB89nsn5qU04Ve3cb#list</t>
+        </is>
+      </c>
+      <c r="CG3" s="2" t="inlineStr"/>
+      <c r="CH3" s="2" t="inlineStr"/>
+      <c r="CI3" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=144-k2EAbtHXs28sl_DhbaJZ5pA6LgGdi#list</t>
         </is>
       </c>
-      <c r="BA3" s="2" t="inlineStr">
+      <c r="CJ3" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1uccSxKJulprPVr1E0EgLncGtTX696ULt#list</t>
         </is>
       </c>
-      <c r="BB3" s="2" t="inlineStr">
+      <c r="CK3" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1E29tAZqC5D6MsXmVbVodFUjWWOOJK-mB#list</t>
         </is>
       </c>
+      <c r="CL3" s="2" t="inlineStr"/>
+      <c r="CM3" s="2" t="inlineStr"/>
+      <c r="CN3" s="2" t="inlineStr"/>
+      <c r="CO3" s="2" t="inlineStr"/>
+      <c r="CP3" s="2" t="inlineStr"/>
+      <c r="CQ3" s="2" t="inlineStr"/>
+      <c r="CR3" s="2" t="inlineStr"/>
+      <c r="CS3" s="2" t="inlineStr"/>
+      <c r="CT3" s="2" t="inlineStr"/>
+      <c r="CU3" s="2" t="inlineStr"/>
+      <c r="CV3" s="2" t="inlineStr"/>
+      <c r="CW3" s="2" t="inlineStr"/>
+      <c r="CX3" s="2" t="inlineStr"/>
+      <c r="CY3" s="2" t="inlineStr"/>
+      <c r="CZ3" s="2" t="inlineStr"/>
+      <c r="DA3" s="2" t="inlineStr"/>
+      <c r="DB3" s="2" t="inlineStr"/>
+      <c r="DC3" s="2" t="inlineStr"/>
+      <c r="DD3" s="2" t="inlineStr"/>
+      <c r="DE3" s="2" t="inlineStr"/>
+      <c r="DF3" s="2" t="inlineStr"/>
+      <c r="DG3" s="2" t="inlineStr"/>
+      <c r="DH3" s="2" t="inlineStr"/>
+      <c r="DI3" s="2" t="inlineStr"/>
+      <c r="DJ3" s="2" t="inlineStr"/>
+      <c r="DK3" s="2" t="inlineStr"/>
+      <c r="DL3" s="2" t="inlineStr"/>
+      <c r="DM3" s="2" t="inlineStr"/>
+      <c r="DN3" s="2" t="inlineStr"/>
+      <c r="DO3" s="2" t="inlineStr"/>
+      <c r="DP3" s="2" t="inlineStr"/>
+      <c r="DQ3" s="2" t="inlineStr"/>
+      <c r="DR3" s="2" t="inlineStr"/>
+      <c r="DS3" s="2" t="inlineStr"/>
+      <c r="DT3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1319,49 +1809,119 @@
       <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1u2rdw02egeHlzykAI1ni8ZlZ9Yb0dopp#list</t>
-        </is>
-      </c>
+      <c r="AN4" s="2" t="inlineStr"/>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1m2hKcpP5K1rEUXMh331lt3LUeeSIb-k7#list</t>
-        </is>
-      </c>
+      <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
       <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1pElwv9L0KW70JntyNpERIXEe2ZKxrGOx#list</t>
-        </is>
-      </c>
+      <c r="AT4" s="2" t="inlineStr"/>
       <c r="AU4" s="2" t="inlineStr"/>
       <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1kPPs14rzTFek7FwQ3WggxY7_iq9gfXw-#list</t>
-        </is>
-      </c>
+      <c r="AW4" s="2" t="inlineStr"/>
       <c r="AX4" s="2" t="inlineStr"/>
       <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr">
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr"/>
+      <c r="BC4" s="2" t="inlineStr"/>
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr"/>
+      <c r="BF4" s="2" t="inlineStr"/>
+      <c r="BG4" s="2" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BM4" s="2" t="inlineStr"/>
+      <c r="BN4" s="2" t="inlineStr"/>
+      <c r="BO4" s="2" t="inlineStr"/>
+      <c r="BP4" s="2" t="inlineStr"/>
+      <c r="BQ4" s="2" t="inlineStr"/>
+      <c r="BR4" s="2" t="inlineStr"/>
+      <c r="BS4" s="2" t="inlineStr"/>
+      <c r="BT4" s="2" t="inlineStr"/>
+      <c r="BU4" s="2" t="inlineStr"/>
+      <c r="BV4" s="2" t="inlineStr"/>
+      <c r="BW4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1u2rdw02egeHlzykAI1ni8ZlZ9Yb0dopp#list</t>
+        </is>
+      </c>
+      <c r="BX4" s="2" t="inlineStr"/>
+      <c r="BY4" s="2" t="inlineStr"/>
+      <c r="BZ4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1m2hKcpP5K1rEUXMh331lt3LUeeSIb-k7#list</t>
+        </is>
+      </c>
+      <c r="CA4" s="2" t="inlineStr"/>
+      <c r="CB4" s="2" t="inlineStr"/>
+      <c r="CC4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pElwv9L0KW70JntyNpERIXEe2ZKxrGOx#list</t>
+        </is>
+      </c>
+      <c r="CD4" s="2" t="inlineStr"/>
+      <c r="CE4" s="2" t="inlineStr"/>
+      <c r="CF4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kPPs14rzTFek7FwQ3WggxY7_iq9gfXw-#list</t>
+        </is>
+      </c>
+      <c r="CG4" s="2" t="inlineStr"/>
+      <c r="CH4" s="2" t="inlineStr"/>
+      <c r="CI4" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1sVH2kS-cQK6eeWgxdMGeuZfYRYxa-dkf#list</t>
         </is>
       </c>
-      <c r="BA4" s="2" t="inlineStr">
+      <c r="CJ4" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1lgSGw_7ORM6zn9m3crtuN3iH_DbNYwTH#list</t>
         </is>
       </c>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="CK4" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1NsPsUr4zNAo4ZRIRb-SN5mAkQdtcF6fs#list</t>
         </is>
       </c>
+      <c r="CL4" s="2" t="inlineStr"/>
+      <c r="CM4" s="2" t="inlineStr"/>
+      <c r="CN4" s="2" t="inlineStr"/>
+      <c r="CO4" s="2" t="inlineStr"/>
+      <c r="CP4" s="2" t="inlineStr"/>
+      <c r="CQ4" s="2" t="inlineStr"/>
+      <c r="CR4" s="2" t="inlineStr"/>
+      <c r="CS4" s="2" t="inlineStr"/>
+      <c r="CT4" s="2" t="inlineStr"/>
+      <c r="CU4" s="2" t="inlineStr"/>
+      <c r="CV4" s="2" t="inlineStr"/>
+      <c r="CW4" s="2" t="inlineStr"/>
+      <c r="CX4" s="2" t="inlineStr"/>
+      <c r="CY4" s="2" t="inlineStr"/>
+      <c r="CZ4" s="2" t="inlineStr"/>
+      <c r="DA4" s="2" t="inlineStr"/>
+      <c r="DB4" s="2" t="inlineStr"/>
+      <c r="DC4" s="2" t="inlineStr"/>
+      <c r="DD4" s="2" t="inlineStr"/>
+      <c r="DE4" s="2" t="inlineStr"/>
+      <c r="DF4" s="2" t="inlineStr"/>
+      <c r="DG4" s="2" t="inlineStr"/>
+      <c r="DH4" s="2" t="inlineStr"/>
+      <c r="DI4" s="2" t="inlineStr"/>
+      <c r="DJ4" s="2" t="inlineStr"/>
+      <c r="DK4" s="2" t="inlineStr"/>
+      <c r="DL4" s="2" t="inlineStr"/>
+      <c r="DM4" s="2" t="inlineStr"/>
+      <c r="DN4" s="2" t="inlineStr"/>
+      <c r="DO4" s="2" t="inlineStr"/>
+      <c r="DP4" s="2" t="inlineStr"/>
+      <c r="DQ4" s="2" t="inlineStr"/>
+      <c r="DR4" s="2" t="inlineStr"/>
+      <c r="DS4" s="2" t="inlineStr"/>
+      <c r="DT4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1519,89 +2079,159 @@
       </c>
       <c r="AH5" s="2" t="inlineStr"/>
       <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1WgYlbGgosDPefV1EqkRSmCO0lMCz_Qhl#list</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1pMROCVj0erJyxXf0QC26D01EccuXFXYb#list</t>
-        </is>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=13cNWvLGmg1UcFsw2GQ_M2ENmtEiImh8w#list</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1xb2V3kCNuSpB9pPp_qmIOAHPU1tsvyYa#list</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1z4xZCbU0N-H7a3RKEVVZdrHMpOcYSoou#list</t>
-        </is>
-      </c>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1zuUS5kTAmnY1iW4SPfSI3G50sx9hTcs8#list</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1BLI4oFJaO5_GdJJF6_ElOe7k5m0v1BkG#list</t>
-        </is>
-      </c>
-      <c r="AQ5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1P7WSKzRqeAkVI0iCbomABqxDJQeVAE0A#list</t>
-        </is>
-      </c>
-      <c r="AR5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=14cTDZHjwI2lgIGJjPqUNitHZz6wYv4iI#list</t>
-        </is>
-      </c>
-      <c r="AS5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1DceueckfI--x9EFw3dii7ReQG462-tpI#list</t>
-        </is>
-      </c>
-      <c r="AT5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1auJbdccwFGURaG2eaOwHqmqqv3Vzi600#list</t>
-        </is>
-      </c>
-      <c r="AU5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1aGxMPqvXk3aESaGolg-_fmcRXuyo_b9G#list</t>
-        </is>
-      </c>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
       <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Dzs6qeh7Z2B6mxSZSzfP8Iz5-XINVcOw#list</t>
-        </is>
-      </c>
+      <c r="AW5" s="2" t="inlineStr"/>
       <c r="AX5" s="2" t="inlineStr"/>
       <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr">
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr"/>
+      <c r="BC5" s="2" t="inlineStr"/>
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr"/>
+      <c r="BF5" s="2" t="inlineStr"/>
+      <c r="BG5" s="2" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BM5" s="2" t="inlineStr"/>
+      <c r="BN5" s="2" t="inlineStr"/>
+      <c r="BO5" s="2" t="inlineStr"/>
+      <c r="BP5" s="2" t="inlineStr"/>
+      <c r="BQ5" s="2" t="inlineStr"/>
+      <c r="BR5" s="2" t="inlineStr"/>
+      <c r="BS5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1WgYlbGgosDPefV1EqkRSmCO0lMCz_Qhl#list</t>
+        </is>
+      </c>
+      <c r="BT5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pMROCVj0erJyxXf0QC26D01EccuXFXYb#list</t>
+        </is>
+      </c>
+      <c r="BU5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=13cNWvLGmg1UcFsw2GQ_M2ENmtEiImh8w#list</t>
+        </is>
+      </c>
+      <c r="BV5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1xb2V3kCNuSpB9pPp_qmIOAHPU1tsvyYa#list</t>
+        </is>
+      </c>
+      <c r="BW5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1z4xZCbU0N-H7a3RKEVVZdrHMpOcYSoou#list</t>
+        </is>
+      </c>
+      <c r="BX5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1zuUS5kTAmnY1iW4SPfSI3G50sx9hTcs8#list</t>
+        </is>
+      </c>
+      <c r="BY5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BLI4oFJaO5_GdJJF6_ElOe7k5m0v1BkG#list</t>
+        </is>
+      </c>
+      <c r="BZ5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1P7WSKzRqeAkVI0iCbomABqxDJQeVAE0A#list</t>
+        </is>
+      </c>
+      <c r="CA5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14cTDZHjwI2lgIGJjPqUNitHZz6wYv4iI#list</t>
+        </is>
+      </c>
+      <c r="CB5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1DceueckfI--x9EFw3dii7ReQG462-tpI#list</t>
+        </is>
+      </c>
+      <c r="CC5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1auJbdccwFGURaG2eaOwHqmqqv3Vzi600#list</t>
+        </is>
+      </c>
+      <c r="CD5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1aGxMPqvXk3aESaGolg-_fmcRXuyo_b9G#list</t>
+        </is>
+      </c>
+      <c r="CE5" s="2" t="inlineStr"/>
+      <c r="CF5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Dzs6qeh7Z2B6mxSZSzfP8Iz5-XINVcOw#list</t>
+        </is>
+      </c>
+      <c r="CG5" s="2" t="inlineStr"/>
+      <c r="CH5" s="2" t="inlineStr"/>
+      <c r="CI5" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bnl5OK7wJi7AOnL2J3J4b8QT9Yql1ugW#list</t>
         </is>
       </c>
-      <c r="BA5" s="2" t="inlineStr">
+      <c r="CJ5" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=11bfoMlhrCWjMM30v5MQd7V1BfVQdjqad#list</t>
         </is>
       </c>
-      <c r="BB5" s="2" t="inlineStr">
+      <c r="CK5" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1n20KUoNge71cs3LSXdThX5Czpld0_NmE#list</t>
         </is>
       </c>
+      <c r="CL5" s="2" t="inlineStr"/>
+      <c r="CM5" s="2" t="inlineStr"/>
+      <c r="CN5" s="2" t="inlineStr"/>
+      <c r="CO5" s="2" t="inlineStr"/>
+      <c r="CP5" s="2" t="inlineStr"/>
+      <c r="CQ5" s="2" t="inlineStr"/>
+      <c r="CR5" s="2" t="inlineStr"/>
+      <c r="CS5" s="2" t="inlineStr"/>
+      <c r="CT5" s="2" t="inlineStr"/>
+      <c r="CU5" s="2" t="inlineStr"/>
+      <c r="CV5" s="2" t="inlineStr"/>
+      <c r="CW5" s="2" t="inlineStr"/>
+      <c r="CX5" s="2" t="inlineStr"/>
+      <c r="CY5" s="2" t="inlineStr"/>
+      <c r="CZ5" s="2" t="inlineStr"/>
+      <c r="DA5" s="2" t="inlineStr"/>
+      <c r="DB5" s="2" t="inlineStr"/>
+      <c r="DC5" s="2" t="inlineStr"/>
+      <c r="DD5" s="2" t="inlineStr"/>
+      <c r="DE5" s="2" t="inlineStr"/>
+      <c r="DF5" s="2" t="inlineStr"/>
+      <c r="DG5" s="2" t="inlineStr"/>
+      <c r="DH5" s="2" t="inlineStr"/>
+      <c r="DI5" s="2" t="inlineStr"/>
+      <c r="DJ5" s="2" t="inlineStr"/>
+      <c r="DK5" s="2" t="inlineStr"/>
+      <c r="DL5" s="2" t="inlineStr"/>
+      <c r="DM5" s="2" t="inlineStr"/>
+      <c r="DN5" s="2" t="inlineStr"/>
+      <c r="DO5" s="2" t="inlineStr"/>
+      <c r="DP5" s="2" t="inlineStr"/>
+      <c r="DQ5" s="2" t="inlineStr"/>
+      <c r="DR5" s="2" t="inlineStr"/>
+      <c r="DS5" s="2" t="inlineStr"/>
+      <c r="DT5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1757,99 +2387,169 @@
           <t>Eastern Cape November</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1mGhddysiycZKylwtHX_6WL-TrKo8Ob3e#list</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1lX13PwN3DJj_PdkwzPoDH-cy_wm4P-fR#list</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Qjpdcmv_Fz8laju-rUYa_54WyptUzRq9#list</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1pRt32VRwY_zI8_0uYAlvWJTjDEuyl-l5#list</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1KWpBuYCkfLmyKekGOMc7z_6j9iYiF_7F#list</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1jH1vM3LnPOBGxwTTnZTZJGpjyywlKoom#list</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=19g2LEONFHpG13qm2ulAraXgJ89V4qM5q#list</t>
-        </is>
-      </c>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1jVucYSECV77c_G65BBO3dPqjylwnMv7h#list</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1x1EfVpfXg8YacPv_2v3f5PQ3LbCvkLx1#list</t>
-        </is>
-      </c>
-      <c r="AQ6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1ALgOYRFCW0nKbCK2vLsFmYZ_B22SM2hr#list</t>
-        </is>
-      </c>
-      <c r="AR6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1gDuoWT--zoVvAM179mVKwJ6B54XWGreI#list</t>
-        </is>
-      </c>
-      <c r="AS6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1o9n9FTJ1QbJc8zTppBu8ZMFrwCxe3EtT#list</t>
-        </is>
-      </c>
-      <c r="AT6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Aw9n5nGmrXu4NdvknMpdb29QcJ9QgiH3#list</t>
-        </is>
-      </c>
-      <c r="AU6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1FQ0XrLnRaUTWAuKyHrR3UO9O7JdImSX-#list</t>
-        </is>
-      </c>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
       <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1pQFc3O3bIOaH_5L8g2NJjOkl3Q1g3IUz#list</t>
-        </is>
-      </c>
+      <c r="AW6" s="2" t="inlineStr"/>
       <c r="AX6" s="2" t="inlineStr"/>
       <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr">
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr"/>
+      <c r="BC6" s="2" t="inlineStr"/>
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr"/>
+      <c r="BF6" s="2" t="inlineStr"/>
+      <c r="BG6" s="2" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BM6" s="2" t="inlineStr"/>
+      <c r="BN6" s="2" t="inlineStr"/>
+      <c r="BO6" s="2" t="inlineStr"/>
+      <c r="BP6" s="2" t="inlineStr"/>
+      <c r="BQ6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1mGhddysiycZKylwtHX_6WL-TrKo8Ob3e#list</t>
+        </is>
+      </c>
+      <c r="BR6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1lX13PwN3DJj_PdkwzPoDH-cy_wm4P-fR#list</t>
+        </is>
+      </c>
+      <c r="BS6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Qjpdcmv_Fz8laju-rUYa_54WyptUzRq9#list</t>
+        </is>
+      </c>
+      <c r="BT6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pRt32VRwY_zI8_0uYAlvWJTjDEuyl-l5#list</t>
+        </is>
+      </c>
+      <c r="BU6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1KWpBuYCkfLmyKekGOMc7z_6j9iYiF_7F#list</t>
+        </is>
+      </c>
+      <c r="BV6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jH1vM3LnPOBGxwTTnZTZJGpjyywlKoom#list</t>
+        </is>
+      </c>
+      <c r="BW6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19g2LEONFHpG13qm2ulAraXgJ89V4qM5q#list</t>
+        </is>
+      </c>
+      <c r="BX6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jVucYSECV77c_G65BBO3dPqjylwnMv7h#list</t>
+        </is>
+      </c>
+      <c r="BY6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1x1EfVpfXg8YacPv_2v3f5PQ3LbCvkLx1#list</t>
+        </is>
+      </c>
+      <c r="BZ6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ALgOYRFCW0nKbCK2vLsFmYZ_B22SM2hr#list</t>
+        </is>
+      </c>
+      <c r="CA6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1gDuoWT--zoVvAM179mVKwJ6B54XWGreI#list</t>
+        </is>
+      </c>
+      <c r="CB6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1o9n9FTJ1QbJc8zTppBu8ZMFrwCxe3EtT#list</t>
+        </is>
+      </c>
+      <c r="CC6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Aw9n5nGmrXu4NdvknMpdb29QcJ9QgiH3#list</t>
+        </is>
+      </c>
+      <c r="CD6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FQ0XrLnRaUTWAuKyHrR3UO9O7JdImSX-#list</t>
+        </is>
+      </c>
+      <c r="CE6" s="2" t="inlineStr"/>
+      <c r="CF6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pQFc3O3bIOaH_5L8g2NJjOkl3Q1g3IUz#list</t>
+        </is>
+      </c>
+      <c r="CG6" s="2" t="inlineStr"/>
+      <c r="CH6" s="2" t="inlineStr"/>
+      <c r="CI6" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1H6n1bAMocHTnQsQ3FQfcRvHIDoKlAM7d#list</t>
         </is>
       </c>
-      <c r="BA6" s="2" t="inlineStr">
+      <c r="CJ6" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1E0u5ARvp0s1qIQZ6hWQGo-ooqp_EFY33#list</t>
         </is>
       </c>
-      <c r="BB6" s="2" t="inlineStr">
+      <c r="CK6" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=13oHxIOsAemPltIzGknpxQRtioWvMxZ9C#list</t>
         </is>
       </c>
+      <c r="CL6" s="2" t="inlineStr"/>
+      <c r="CM6" s="2" t="inlineStr"/>
+      <c r="CN6" s="2" t="inlineStr"/>
+      <c r="CO6" s="2" t="inlineStr"/>
+      <c r="CP6" s="2" t="inlineStr"/>
+      <c r="CQ6" s="2" t="inlineStr"/>
+      <c r="CR6" s="2" t="inlineStr"/>
+      <c r="CS6" s="2" t="inlineStr"/>
+      <c r="CT6" s="2" t="inlineStr"/>
+      <c r="CU6" s="2" t="inlineStr"/>
+      <c r="CV6" s="2" t="inlineStr"/>
+      <c r="CW6" s="2" t="inlineStr"/>
+      <c r="CX6" s="2" t="inlineStr"/>
+      <c r="CY6" s="2" t="inlineStr"/>
+      <c r="CZ6" s="2" t="inlineStr"/>
+      <c r="DA6" s="2" t="inlineStr"/>
+      <c r="DB6" s="2" t="inlineStr"/>
+      <c r="DC6" s="2" t="inlineStr"/>
+      <c r="DD6" s="2" t="inlineStr"/>
+      <c r="DE6" s="2" t="inlineStr"/>
+      <c r="DF6" s="2" t="inlineStr"/>
+      <c r="DG6" s="2" t="inlineStr"/>
+      <c r="DH6" s="2" t="inlineStr"/>
+      <c r="DI6" s="2" t="inlineStr"/>
+      <c r="DJ6" s="2" t="inlineStr"/>
+      <c r="DK6" s="2" t="inlineStr"/>
+      <c r="DL6" s="2" t="inlineStr"/>
+      <c r="DM6" s="2" t="inlineStr"/>
+      <c r="DN6" s="2" t="inlineStr"/>
+      <c r="DO6" s="2" t="inlineStr"/>
+      <c r="DP6" s="2" t="inlineStr"/>
+      <c r="DQ6" s="2" t="inlineStr"/>
+      <c r="DR6" s="2" t="inlineStr"/>
+      <c r="DS6" s="2" t="inlineStr"/>
+      <c r="DT6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2007,65 +2707,135 @@
       </c>
       <c r="AH7" s="2" t="inlineStr"/>
       <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1wcfRuffV6M1Qso5FMVNRn44CzlK_49jH#list</t>
-        </is>
-      </c>
-      <c r="AK7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1m4qynCF3mOXOicQ8BEpQQZAMQsKtd66o#list</t>
-        </is>
-      </c>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1zEzJS2KcMR13e4nxcrThs3bIVAVi3TJb#list</t>
-        </is>
-      </c>
+      <c r="AN7" s="2" t="inlineStr"/>
       <c r="AO7" s="2" t="inlineStr"/>
       <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1jtkfAX_tOVxIj-SkcvtXREKIp8DNe0xh#list</t>
-        </is>
-      </c>
-      <c r="AR7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=104Bd-s3Im4Q_Qj8yIU6BvViiPW0ppDaV#list</t>
-        </is>
-      </c>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
       <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1BUwhHhK0QldhhuGKrD4EMoWvu20qOA5t#list</t>
-        </is>
-      </c>
+      <c r="AT7" s="2" t="inlineStr"/>
       <c r="AU7" s="2" t="inlineStr"/>
       <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1p5gJ0yOKBwEZs-i-fHFs4ZcIG_W1OQnP#list</t>
-        </is>
-      </c>
+      <c r="AW7" s="2" t="inlineStr"/>
       <c r="AX7" s="2" t="inlineStr"/>
       <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr">
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr"/>
+      <c r="BC7" s="2" t="inlineStr"/>
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr"/>
+      <c r="BF7" s="2" t="inlineStr"/>
+      <c r="BG7" s="2" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BM7" s="2" t="inlineStr"/>
+      <c r="BN7" s="2" t="inlineStr"/>
+      <c r="BO7" s="2" t="inlineStr"/>
+      <c r="BP7" s="2" t="inlineStr"/>
+      <c r="BQ7" s="2" t="inlineStr"/>
+      <c r="BR7" s="2" t="inlineStr"/>
+      <c r="BS7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1wcfRuffV6M1Qso5FMVNRn44CzlK_49jH#list</t>
+        </is>
+      </c>
+      <c r="BT7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1m4qynCF3mOXOicQ8BEpQQZAMQsKtd66o#list</t>
+        </is>
+      </c>
+      <c r="BU7" s="2" t="inlineStr"/>
+      <c r="BV7" s="2" t="inlineStr"/>
+      <c r="BW7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1zEzJS2KcMR13e4nxcrThs3bIVAVi3TJb#list</t>
+        </is>
+      </c>
+      <c r="BX7" s="2" t="inlineStr"/>
+      <c r="BY7" s="2" t="inlineStr"/>
+      <c r="BZ7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jtkfAX_tOVxIj-SkcvtXREKIp8DNe0xh#list</t>
+        </is>
+      </c>
+      <c r="CA7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=104Bd-s3Im4Q_Qj8yIU6BvViiPW0ppDaV#list</t>
+        </is>
+      </c>
+      <c r="CB7" s="2" t="inlineStr"/>
+      <c r="CC7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BUwhHhK0QldhhuGKrD4EMoWvu20qOA5t#list</t>
+        </is>
+      </c>
+      <c r="CD7" s="2" t="inlineStr"/>
+      <c r="CE7" s="2" t="inlineStr"/>
+      <c r="CF7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1p5gJ0yOKBwEZs-i-fHFs4ZcIG_W1OQnP#list</t>
+        </is>
+      </c>
+      <c r="CG7" s="2" t="inlineStr"/>
+      <c r="CH7" s="2" t="inlineStr"/>
+      <c r="CI7" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aUZXx62pUVhFKU1wyQB4yiHCvf96aiDE#list</t>
         </is>
       </c>
-      <c r="BA7" s="2" t="inlineStr">
+      <c r="CJ7" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1DuP9CcXEWfrKa06uvEUirkSLsA23pDEj#list</t>
         </is>
       </c>
-      <c r="BB7" s="2" t="inlineStr">
+      <c r="CK7" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1AO_jwZMAnFWDkYGYQZJgnhKuz6jiTW7_#list</t>
         </is>
       </c>
+      <c r="CL7" s="2" t="inlineStr"/>
+      <c r="CM7" s="2" t="inlineStr"/>
+      <c r="CN7" s="2" t="inlineStr"/>
+      <c r="CO7" s="2" t="inlineStr"/>
+      <c r="CP7" s="2" t="inlineStr"/>
+      <c r="CQ7" s="2" t="inlineStr"/>
+      <c r="CR7" s="2" t="inlineStr"/>
+      <c r="CS7" s="2" t="inlineStr"/>
+      <c r="CT7" s="2" t="inlineStr"/>
+      <c r="CU7" s="2" t="inlineStr"/>
+      <c r="CV7" s="2" t="inlineStr"/>
+      <c r="CW7" s="2" t="inlineStr"/>
+      <c r="CX7" s="2" t="inlineStr"/>
+      <c r="CY7" s="2" t="inlineStr"/>
+      <c r="CZ7" s="2" t="inlineStr"/>
+      <c r="DA7" s="2" t="inlineStr"/>
+      <c r="DB7" s="2" t="inlineStr"/>
+      <c r="DC7" s="2" t="inlineStr"/>
+      <c r="DD7" s="2" t="inlineStr"/>
+      <c r="DE7" s="2" t="inlineStr"/>
+      <c r="DF7" s="2" t="inlineStr"/>
+      <c r="DG7" s="2" t="inlineStr"/>
+      <c r="DH7" s="2" t="inlineStr"/>
+      <c r="DI7" s="2" t="inlineStr"/>
+      <c r="DJ7" s="2" t="inlineStr"/>
+      <c r="DK7" s="2" t="inlineStr"/>
+      <c r="DL7" s="2" t="inlineStr"/>
+      <c r="DM7" s="2" t="inlineStr"/>
+      <c r="DN7" s="2" t="inlineStr"/>
+      <c r="DO7" s="2" t="inlineStr"/>
+      <c r="DP7" s="2" t="inlineStr"/>
+      <c r="DQ7" s="2" t="inlineStr"/>
+      <c r="DR7" s="2" t="inlineStr"/>
+      <c r="DS7" s="2" t="inlineStr"/>
+      <c r="DT7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2224,25 +2994,13 @@
       <c r="AH8" s="2" t="inlineStr"/>
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1bxRnLAlqY0prAR0KarI3wr1pt6_s1yTc#list</t>
-        </is>
-      </c>
+      <c r="AK8" s="2" t="inlineStr"/>
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Ntc7bHPyHxnCEWQf5ps4vJyORaoJqNLN#list</t>
-        </is>
-      </c>
+      <c r="AN8" s="2" t="inlineStr"/>
       <c r="AO8" s="2" t="inlineStr"/>
       <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=16Zz0U4Yv62KhWKfK8L3-8W-hr6qP0Bce#list</t>
-        </is>
-      </c>
+      <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
       <c r="AS8" s="2" t="inlineStr"/>
       <c r="AT8" s="2" t="inlineStr"/>
@@ -2254,6 +3012,88 @@
       <c r="AZ8" s="2" t="inlineStr"/>
       <c r="BA8" s="2" t="inlineStr"/>
       <c r="BB8" s="2" t="inlineStr"/>
+      <c r="BC8" s="2" t="inlineStr"/>
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr"/>
+      <c r="BF8" s="2" t="inlineStr"/>
+      <c r="BG8" s="2" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BM8" s="2" t="inlineStr"/>
+      <c r="BN8" s="2" t="inlineStr"/>
+      <c r="BO8" s="2" t="inlineStr"/>
+      <c r="BP8" s="2" t="inlineStr"/>
+      <c r="BQ8" s="2" t="inlineStr"/>
+      <c r="BR8" s="2" t="inlineStr"/>
+      <c r="BS8" s="2" t="inlineStr"/>
+      <c r="BT8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bxRnLAlqY0prAR0KarI3wr1pt6_s1yTc#list</t>
+        </is>
+      </c>
+      <c r="BU8" s="2" t="inlineStr"/>
+      <c r="BV8" s="2" t="inlineStr"/>
+      <c r="BW8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ntc7bHPyHxnCEWQf5ps4vJyORaoJqNLN#list</t>
+        </is>
+      </c>
+      <c r="BX8" s="2" t="inlineStr"/>
+      <c r="BY8" s="2" t="inlineStr"/>
+      <c r="BZ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16Zz0U4Yv62KhWKfK8L3-8W-hr6qP0Bce#list</t>
+        </is>
+      </c>
+      <c r="CA8" s="2" t="inlineStr"/>
+      <c r="CB8" s="2" t="inlineStr"/>
+      <c r="CC8" s="2" t="inlineStr"/>
+      <c r="CD8" s="2" t="inlineStr"/>
+      <c r="CE8" s="2" t="inlineStr"/>
+      <c r="CF8" s="2" t="inlineStr"/>
+      <c r="CG8" s="2" t="inlineStr"/>
+      <c r="CH8" s="2" t="inlineStr"/>
+      <c r="CI8" s="2" t="inlineStr"/>
+      <c r="CJ8" s="2" t="inlineStr"/>
+      <c r="CK8" s="2" t="inlineStr"/>
+      <c r="CL8" s="2" t="inlineStr"/>
+      <c r="CM8" s="2" t="inlineStr"/>
+      <c r="CN8" s="2" t="inlineStr"/>
+      <c r="CO8" s="2" t="inlineStr"/>
+      <c r="CP8" s="2" t="inlineStr"/>
+      <c r="CQ8" s="2" t="inlineStr"/>
+      <c r="CR8" s="2" t="inlineStr"/>
+      <c r="CS8" s="2" t="inlineStr"/>
+      <c r="CT8" s="2" t="inlineStr"/>
+      <c r="CU8" s="2" t="inlineStr"/>
+      <c r="CV8" s="2" t="inlineStr"/>
+      <c r="CW8" s="2" t="inlineStr"/>
+      <c r="CX8" s="2" t="inlineStr"/>
+      <c r="CY8" s="2" t="inlineStr"/>
+      <c r="CZ8" s="2" t="inlineStr"/>
+      <c r="DA8" s="2" t="inlineStr"/>
+      <c r="DB8" s="2" t="inlineStr"/>
+      <c r="DC8" s="2" t="inlineStr"/>
+      <c r="DD8" s="2" t="inlineStr"/>
+      <c r="DE8" s="2" t="inlineStr"/>
+      <c r="DF8" s="2" t="inlineStr"/>
+      <c r="DG8" s="2" t="inlineStr"/>
+      <c r="DH8" s="2" t="inlineStr"/>
+      <c r="DI8" s="2" t="inlineStr"/>
+      <c r="DJ8" s="2" t="inlineStr"/>
+      <c r="DK8" s="2" t="inlineStr"/>
+      <c r="DL8" s="2" t="inlineStr"/>
+      <c r="DM8" s="2" t="inlineStr"/>
+      <c r="DN8" s="2" t="inlineStr"/>
+      <c r="DO8" s="2" t="inlineStr"/>
+      <c r="DP8" s="2" t="inlineStr"/>
+      <c r="DQ8" s="2" t="inlineStr"/>
+      <c r="DR8" s="2" t="inlineStr"/>
+      <c r="DS8" s="2" t="inlineStr"/>
+      <c r="DT8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2415,49 +3255,119 @@
       <c r="AK9" s="2" t="inlineStr"/>
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1qu7SMy8D01BdirvMoqhGdtCp69W28GPG#list</t>
-        </is>
-      </c>
+      <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" s="2" t="inlineStr"/>
       <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=12n8STt1B_ZGgYLVsIJkcGyQK0yT95mZu#list</t>
-        </is>
-      </c>
+      <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
       <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=12Mw7Cd8FROoteqpxtoLxEaOIytTxY754#list</t>
-        </is>
-      </c>
+      <c r="AT9" s="2" t="inlineStr"/>
       <c r="AU9" s="2" t="inlineStr"/>
       <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1-dRerWHpZbfzDiho3cbDRGxYhl-s-9f5#list</t>
-        </is>
-      </c>
+      <c r="AW9" s="2" t="inlineStr"/>
       <c r="AX9" s="2" t="inlineStr"/>
       <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr">
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr"/>
+      <c r="BC9" s="2" t="inlineStr"/>
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr"/>
+      <c r="BF9" s="2" t="inlineStr"/>
+      <c r="BG9" s="2" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BM9" s="2" t="inlineStr"/>
+      <c r="BN9" s="2" t="inlineStr"/>
+      <c r="BO9" s="2" t="inlineStr"/>
+      <c r="BP9" s="2" t="inlineStr"/>
+      <c r="BQ9" s="2" t="inlineStr"/>
+      <c r="BR9" s="2" t="inlineStr"/>
+      <c r="BS9" s="2" t="inlineStr"/>
+      <c r="BT9" s="2" t="inlineStr"/>
+      <c r="BU9" s="2" t="inlineStr"/>
+      <c r="BV9" s="2" t="inlineStr"/>
+      <c r="BW9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qu7SMy8D01BdirvMoqhGdtCp69W28GPG#list</t>
+        </is>
+      </c>
+      <c r="BX9" s="2" t="inlineStr"/>
+      <c r="BY9" s="2" t="inlineStr"/>
+      <c r="BZ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=12n8STt1B_ZGgYLVsIJkcGyQK0yT95mZu#list</t>
+        </is>
+      </c>
+      <c r="CA9" s="2" t="inlineStr"/>
+      <c r="CB9" s="2" t="inlineStr"/>
+      <c r="CC9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=12Mw7Cd8FROoteqpxtoLxEaOIytTxY754#list</t>
+        </is>
+      </c>
+      <c r="CD9" s="2" t="inlineStr"/>
+      <c r="CE9" s="2" t="inlineStr"/>
+      <c r="CF9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-dRerWHpZbfzDiho3cbDRGxYhl-s-9f5#list</t>
+        </is>
+      </c>
+      <c r="CG9" s="2" t="inlineStr"/>
+      <c r="CH9" s="2" t="inlineStr"/>
+      <c r="CI9" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1-4rOWP92YVCddpzt5UphR-Q4GKgViw_i#list</t>
         </is>
       </c>
-      <c r="BA9" s="2" t="inlineStr">
+      <c r="CJ9" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1fs2TFlfTBMtU1s4I7cZMoWv8dmY6TsbL#list</t>
         </is>
       </c>
-      <c r="BB9" s="2" t="inlineStr">
+      <c r="CK9" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aJF7h1eGmDiIMm0qDtvjGAF-TkxEqRYx#list</t>
         </is>
       </c>
+      <c r="CL9" s="2" t="inlineStr"/>
+      <c r="CM9" s="2" t="inlineStr"/>
+      <c r="CN9" s="2" t="inlineStr"/>
+      <c r="CO9" s="2" t="inlineStr"/>
+      <c r="CP9" s="2" t="inlineStr"/>
+      <c r="CQ9" s="2" t="inlineStr"/>
+      <c r="CR9" s="2" t="inlineStr"/>
+      <c r="CS9" s="2" t="inlineStr"/>
+      <c r="CT9" s="2" t="inlineStr"/>
+      <c r="CU9" s="2" t="inlineStr"/>
+      <c r="CV9" s="2" t="inlineStr"/>
+      <c r="CW9" s="2" t="inlineStr"/>
+      <c r="CX9" s="2" t="inlineStr"/>
+      <c r="CY9" s="2" t="inlineStr"/>
+      <c r="CZ9" s="2" t="inlineStr"/>
+      <c r="DA9" s="2" t="inlineStr"/>
+      <c r="DB9" s="2" t="inlineStr"/>
+      <c r="DC9" s="2" t="inlineStr"/>
+      <c r="DD9" s="2" t="inlineStr"/>
+      <c r="DE9" s="2" t="inlineStr"/>
+      <c r="DF9" s="2" t="inlineStr"/>
+      <c r="DG9" s="2" t="inlineStr"/>
+      <c r="DH9" s="2" t="inlineStr"/>
+      <c r="DI9" s="2" t="inlineStr"/>
+      <c r="DJ9" s="2" t="inlineStr"/>
+      <c r="DK9" s="2" t="inlineStr"/>
+      <c r="DL9" s="2" t="inlineStr"/>
+      <c r="DM9" s="2" t="inlineStr"/>
+      <c r="DN9" s="2" t="inlineStr"/>
+      <c r="DO9" s="2" t="inlineStr"/>
+      <c r="DP9" s="2" t="inlineStr"/>
+      <c r="DQ9" s="2" t="inlineStr"/>
+      <c r="DR9" s="2" t="inlineStr"/>
+      <c r="DS9" s="2" t="inlineStr"/>
+      <c r="DT9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2619,49 +3529,119 @@
       <c r="AK10" s="2" t="inlineStr"/>
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=10y-Zc4VZEpGQhl2_YB7sJy1Mm9rCrd7j#list</t>
-        </is>
-      </c>
+      <c r="AN10" s="2" t="inlineStr"/>
       <c r="AO10" s="2" t="inlineStr"/>
       <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=14dcSGoNZErQiKYe5NszJdhOldrCWjARh#list</t>
-        </is>
-      </c>
+      <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
       <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1do4UyquDxnyqWjxY8arCpX8XXlI7xpMN#list</t>
-        </is>
-      </c>
+      <c r="AT10" s="2" t="inlineStr"/>
       <c r="AU10" s="2" t="inlineStr"/>
       <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1PzAgncnZoaqEMHmq0STOA-aBc6lQ0Aik#list</t>
-        </is>
-      </c>
+      <c r="AW10" s="2" t="inlineStr"/>
       <c r="AX10" s="2" t="inlineStr"/>
       <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr">
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr"/>
+      <c r="BC10" s="2" t="inlineStr"/>
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr"/>
+      <c r="BF10" s="2" t="inlineStr"/>
+      <c r="BG10" s="2" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BM10" s="2" t="inlineStr"/>
+      <c r="BN10" s="2" t="inlineStr"/>
+      <c r="BO10" s="2" t="inlineStr"/>
+      <c r="BP10" s="2" t="inlineStr"/>
+      <c r="BQ10" s="2" t="inlineStr"/>
+      <c r="BR10" s="2" t="inlineStr"/>
+      <c r="BS10" s="2" t="inlineStr"/>
+      <c r="BT10" s="2" t="inlineStr"/>
+      <c r="BU10" s="2" t="inlineStr"/>
+      <c r="BV10" s="2" t="inlineStr"/>
+      <c r="BW10" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=10y-Zc4VZEpGQhl2_YB7sJy1Mm9rCrd7j#list</t>
+        </is>
+      </c>
+      <c r="BX10" s="2" t="inlineStr"/>
+      <c r="BY10" s="2" t="inlineStr"/>
+      <c r="BZ10" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14dcSGoNZErQiKYe5NszJdhOldrCWjARh#list</t>
+        </is>
+      </c>
+      <c r="CA10" s="2" t="inlineStr"/>
+      <c r="CB10" s="2" t="inlineStr"/>
+      <c r="CC10" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1do4UyquDxnyqWjxY8arCpX8XXlI7xpMN#list</t>
+        </is>
+      </c>
+      <c r="CD10" s="2" t="inlineStr"/>
+      <c r="CE10" s="2" t="inlineStr"/>
+      <c r="CF10" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1PzAgncnZoaqEMHmq0STOA-aBc6lQ0Aik#list</t>
+        </is>
+      </c>
+      <c r="CG10" s="2" t="inlineStr"/>
+      <c r="CH10" s="2" t="inlineStr"/>
+      <c r="CI10" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1NuZB3mNGAu4tyaSF6RMZ-zHN9-wjxFFH#list</t>
         </is>
       </c>
-      <c r="BA10" s="2" t="inlineStr">
+      <c r="CJ10" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1LbeCHnAT0_euKWv9pDMrHqwQG9yoIC7z#list</t>
         </is>
       </c>
-      <c r="BB10" s="2" t="inlineStr">
+      <c r="CK10" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1QcSAdWnNxUDP6UQxnk1-VndtyNfwGN11#list</t>
         </is>
       </c>
+      <c r="CL10" s="2" t="inlineStr"/>
+      <c r="CM10" s="2" t="inlineStr"/>
+      <c r="CN10" s="2" t="inlineStr"/>
+      <c r="CO10" s="2" t="inlineStr"/>
+      <c r="CP10" s="2" t="inlineStr"/>
+      <c r="CQ10" s="2" t="inlineStr"/>
+      <c r="CR10" s="2" t="inlineStr"/>
+      <c r="CS10" s="2" t="inlineStr"/>
+      <c r="CT10" s="2" t="inlineStr"/>
+      <c r="CU10" s="2" t="inlineStr"/>
+      <c r="CV10" s="2" t="inlineStr"/>
+      <c r="CW10" s="2" t="inlineStr"/>
+      <c r="CX10" s="2" t="inlineStr"/>
+      <c r="CY10" s="2" t="inlineStr"/>
+      <c r="CZ10" s="2" t="inlineStr"/>
+      <c r="DA10" s="2" t="inlineStr"/>
+      <c r="DB10" s="2" t="inlineStr"/>
+      <c r="DC10" s="2" t="inlineStr"/>
+      <c r="DD10" s="2" t="inlineStr"/>
+      <c r="DE10" s="2" t="inlineStr"/>
+      <c r="DF10" s="2" t="inlineStr"/>
+      <c r="DG10" s="2" t="inlineStr"/>
+      <c r="DH10" s="2" t="inlineStr"/>
+      <c r="DI10" s="2" t="inlineStr"/>
+      <c r="DJ10" s="2" t="inlineStr"/>
+      <c r="DK10" s="2" t="inlineStr"/>
+      <c r="DL10" s="2" t="inlineStr"/>
+      <c r="DM10" s="2" t="inlineStr"/>
+      <c r="DN10" s="2" t="inlineStr"/>
+      <c r="DO10" s="2" t="inlineStr"/>
+      <c r="DP10" s="2" t="inlineStr"/>
+      <c r="DQ10" s="2" t="inlineStr"/>
+      <c r="DR10" s="2" t="inlineStr"/>
+      <c r="DS10" s="2" t="inlineStr"/>
+      <c r="DT10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2817,79 +3797,149 @@
           <t>Eastern Cape November</t>
         </is>
       </c>
-      <c r="AH11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=11qsVunt8QeAJYFeTis8CVDkuYJWqVGlk#list</t>
-        </is>
-      </c>
+      <c r="AH11" s="2" t="inlineStr"/>
       <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1b9fru4iJ0Ylh0f3Gbl-JGXKwYKHKwaeD#list</t>
-        </is>
-      </c>
-      <c r="AK11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1yB4JSW6swPHKxx-u_8YpjBqguwI27KEL#list</t>
-        </is>
-      </c>
-      <c r="AL11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=166WL1JQzQ9EmZx33TFOxYfjcLhDqAYYI#list</t>
-        </is>
-      </c>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=13Ysg_HyRKI4c311yhg2cG04VQELAAhQG#list</t>
-        </is>
-      </c>
-      <c r="AO11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1FMBAQ7B8CArjPLk0NkCJbvUz6hyGGIs2#list</t>
-        </is>
-      </c>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr"/>
       <c r="AP11" s="2" t="inlineStr"/>
-      <c r="AQ11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=16HFyQeOlKYuaNo_8opldC1a_pVJskIqv#list</t>
-        </is>
-      </c>
-      <c r="AR11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1G_aB9isPClTMOEs-Flv7twi0AV9yO122#list</t>
-        </is>
-      </c>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
       <c r="AS11" s="2" t="inlineStr"/>
-      <c r="AT11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1bKMOheYjl3G58ppgweUMvx0t_ovkJbX2#list</t>
-        </is>
-      </c>
+      <c r="AT11" s="2" t="inlineStr"/>
       <c r="AU11" s="2" t="inlineStr"/>
       <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1iI5Upm5cvv6RnLJmTeWDP-on5DrpOScy#list</t>
-        </is>
-      </c>
+      <c r="AW11" s="2" t="inlineStr"/>
       <c r="AX11" s="2" t="inlineStr"/>
       <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr">
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr"/>
+      <c r="BC11" s="2" t="inlineStr"/>
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr"/>
+      <c r="BF11" s="2" t="inlineStr"/>
+      <c r="BG11" s="2" t="inlineStr"/>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BM11" s="2" t="inlineStr"/>
+      <c r="BN11" s="2" t="inlineStr"/>
+      <c r="BO11" s="2" t="inlineStr"/>
+      <c r="BP11" s="2" t="inlineStr"/>
+      <c r="BQ11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11qsVunt8QeAJYFeTis8CVDkuYJWqVGlk#list</t>
+        </is>
+      </c>
+      <c r="BR11" s="2" t="inlineStr"/>
+      <c r="BS11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1b9fru4iJ0Ylh0f3Gbl-JGXKwYKHKwaeD#list</t>
+        </is>
+      </c>
+      <c r="BT11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yB4JSW6swPHKxx-u_8YpjBqguwI27KEL#list</t>
+        </is>
+      </c>
+      <c r="BU11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=166WL1JQzQ9EmZx33TFOxYfjcLhDqAYYI#list</t>
+        </is>
+      </c>
+      <c r="BV11" s="2" t="inlineStr"/>
+      <c r="BW11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=13Ysg_HyRKI4c311yhg2cG04VQELAAhQG#list</t>
+        </is>
+      </c>
+      <c r="BX11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FMBAQ7B8CArjPLk0NkCJbvUz6hyGGIs2#list</t>
+        </is>
+      </c>
+      <c r="BY11" s="2" t="inlineStr"/>
+      <c r="BZ11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16HFyQeOlKYuaNo_8opldC1a_pVJskIqv#list</t>
+        </is>
+      </c>
+      <c r="CA11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1G_aB9isPClTMOEs-Flv7twi0AV9yO122#list</t>
+        </is>
+      </c>
+      <c r="CB11" s="2" t="inlineStr"/>
+      <c r="CC11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bKMOheYjl3G58ppgweUMvx0t_ovkJbX2#list</t>
+        </is>
+      </c>
+      <c r="CD11" s="2" t="inlineStr"/>
+      <c r="CE11" s="2" t="inlineStr"/>
+      <c r="CF11" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iI5Upm5cvv6RnLJmTeWDP-on5DrpOScy#list</t>
+        </is>
+      </c>
+      <c r="CG11" s="2" t="inlineStr"/>
+      <c r="CH11" s="2" t="inlineStr"/>
+      <c r="CI11" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Z1nEAlW4rMw0nOgOh4gLqVqCc3PeLtHb#list</t>
         </is>
       </c>
-      <c r="BA11" s="2" t="inlineStr">
+      <c r="CJ11" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bwMQmk3K-5Jxhqo4CjUcKLRjFKOGxmGb#list</t>
         </is>
       </c>
-      <c r="BB11" s="2" t="inlineStr">
+      <c r="CK11" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Sa9PnhEEMuVAfZ4Trf8f-S34bvFis8Nz#list</t>
         </is>
       </c>
+      <c r="CL11" s="2" t="inlineStr"/>
+      <c r="CM11" s="2" t="inlineStr"/>
+      <c r="CN11" s="2" t="inlineStr"/>
+      <c r="CO11" s="2" t="inlineStr"/>
+      <c r="CP11" s="2" t="inlineStr"/>
+      <c r="CQ11" s="2" t="inlineStr"/>
+      <c r="CR11" s="2" t="inlineStr"/>
+      <c r="CS11" s="2" t="inlineStr"/>
+      <c r="CT11" s="2" t="inlineStr"/>
+      <c r="CU11" s="2" t="inlineStr"/>
+      <c r="CV11" s="2" t="inlineStr"/>
+      <c r="CW11" s="2" t="inlineStr"/>
+      <c r="CX11" s="2" t="inlineStr"/>
+      <c r="CY11" s="2" t="inlineStr"/>
+      <c r="CZ11" s="2" t="inlineStr"/>
+      <c r="DA11" s="2" t="inlineStr"/>
+      <c r="DB11" s="2" t="inlineStr"/>
+      <c r="DC11" s="2" t="inlineStr"/>
+      <c r="DD11" s="2" t="inlineStr"/>
+      <c r="DE11" s="2" t="inlineStr"/>
+      <c r="DF11" s="2" t="inlineStr"/>
+      <c r="DG11" s="2" t="inlineStr"/>
+      <c r="DH11" s="2" t="inlineStr"/>
+      <c r="DI11" s="2" t="inlineStr"/>
+      <c r="DJ11" s="2" t="inlineStr"/>
+      <c r="DK11" s="2" t="inlineStr"/>
+      <c r="DL11" s="2" t="inlineStr"/>
+      <c r="DM11" s="2" t="inlineStr"/>
+      <c r="DN11" s="2" t="inlineStr"/>
+      <c r="DO11" s="2" t="inlineStr"/>
+      <c r="DP11" s="2" t="inlineStr"/>
+      <c r="DQ11" s="2" t="inlineStr"/>
+      <c r="DR11" s="2" t="inlineStr"/>
+      <c r="DS11" s="2" t="inlineStr"/>
+      <c r="DT11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3047,97 +4097,167 @@
       </c>
       <c r="AH12" s="2" t="inlineStr"/>
       <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr"/>
+      <c r="BC12" s="2" t="inlineStr"/>
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr"/>
+      <c r="BF12" s="2" t="inlineStr"/>
+      <c r="BG12" s="2" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BM12" s="2" t="inlineStr"/>
+      <c r="BN12" s="2" t="inlineStr"/>
+      <c r="BO12" s="2" t="inlineStr"/>
+      <c r="BP12" s="2" t="inlineStr"/>
+      <c r="BQ12" s="2" t="inlineStr"/>
+      <c r="BR12" s="2" t="inlineStr"/>
+      <c r="BS12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1TGSOHPGSbNbZtvYU9M8XP3UJQTK2e5Po#list</t>
         </is>
       </c>
-      <c r="AK12" s="2" t="inlineStr">
+      <c r="BT12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1rIbUizQILGW0Om6Zlnt_dfRdR5CKtHmP#list</t>
         </is>
       </c>
-      <c r="AL12" s="2" t="inlineStr">
+      <c r="BU12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1e39Gp-ixrUzaVnIxjOp7b28GUqcxfDzJ#list</t>
         </is>
       </c>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr">
+      <c r="BV12" s="2" t="inlineStr"/>
+      <c r="BW12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1M_AbmZVjxF9fxBI55ywEU1_5kpigLoyx#list</t>
         </is>
       </c>
-      <c r="AO12" s="2" t="inlineStr">
+      <c r="BX12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1n9M1jPaQas63_HXA3Ldw0qtqLCLgMwXM#list</t>
         </is>
       </c>
-      <c r="AP12" s="2" t="inlineStr">
+      <c r="BY12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1E-9RFlSWHfK6ikjd1Vj7yN87ZdMOTZgU#list</t>
         </is>
       </c>
-      <c r="AQ12" s="2" t="inlineStr">
+      <c r="BZ12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1KZ81YBkKJe0mJ7CUHbcYFgHhjP1J9zl6#list</t>
         </is>
       </c>
-      <c r="AR12" s="2" t="inlineStr">
+      <c r="CA12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1XkPegj354_sqF96Jt25awBHnY0QY0SxD#list</t>
         </is>
       </c>
-      <c r="AS12" s="2" t="inlineStr">
+      <c r="CB12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1IQT8bAhHV3Jp1hAmWmLykTOkVuE7aCcQ#list</t>
         </is>
       </c>
-      <c r="AT12" s="2" t="inlineStr">
+      <c r="CC12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1OpNBN4TK8vs-OIJhmlLE0Dr9KX0a8ak7#list</t>
         </is>
       </c>
-      <c r="AU12" s="2" t="inlineStr">
+      <c r="CD12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1MEgKZnVscBTKxv29d4GZjiP-nW6oxL3k#list</t>
         </is>
       </c>
-      <c r="AV12" s="2" t="inlineStr">
+      <c r="CE12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1tENvot5LM4EO1YxBRilF43gdIfDmKw_u#list</t>
         </is>
       </c>
-      <c r="AW12" s="2" t="inlineStr">
+      <c r="CF12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1neGDnbff4gRPgqvt3_aOha5MRcpvDOkW#list</t>
         </is>
       </c>
-      <c r="AX12" s="2" t="inlineStr">
+      <c r="CG12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1-BydxHi6jMGL621GZGFhwkwvJNYTkvDc#list</t>
         </is>
       </c>
-      <c r="AY12" s="2" t="inlineStr">
+      <c r="CH12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1oRP7eeaZR7pbgpaD2ljLyCEJPLh-vAqN#list</t>
         </is>
       </c>
-      <c r="AZ12" s="2" t="inlineStr">
+      <c r="CI12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1c5yf99e1QmQKgN6xCDP9PxixEUn9v2h4#list</t>
         </is>
       </c>
-      <c r="BA12" s="2" t="inlineStr">
+      <c r="CJ12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Qf7E_Lm1iQWpHZYaleCusyaJWqOQfERJ#list</t>
         </is>
       </c>
-      <c r="BB12" s="2" t="inlineStr">
+      <c r="CK12" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=19t5MQvNkBGAytt8M8mlz-wRumzGjOupv#list</t>
         </is>
       </c>
+      <c r="CL12" s="2" t="inlineStr"/>
+      <c r="CM12" s="2" t="inlineStr"/>
+      <c r="CN12" s="2" t="inlineStr"/>
+      <c r="CO12" s="2" t="inlineStr"/>
+      <c r="CP12" s="2" t="inlineStr"/>
+      <c r="CQ12" s="2" t="inlineStr"/>
+      <c r="CR12" s="2" t="inlineStr"/>
+      <c r="CS12" s="2" t="inlineStr"/>
+      <c r="CT12" s="2" t="inlineStr"/>
+      <c r="CU12" s="2" t="inlineStr"/>
+      <c r="CV12" s="2" t="inlineStr"/>
+      <c r="CW12" s="2" t="inlineStr"/>
+      <c r="CX12" s="2" t="inlineStr"/>
+      <c r="CY12" s="2" t="inlineStr"/>
+      <c r="CZ12" s="2" t="inlineStr"/>
+      <c r="DA12" s="2" t="inlineStr"/>
+      <c r="DB12" s="2" t="inlineStr"/>
+      <c r="DC12" s="2" t="inlineStr"/>
+      <c r="DD12" s="2" t="inlineStr"/>
+      <c r="DE12" s="2" t="inlineStr"/>
+      <c r="DF12" s="2" t="inlineStr"/>
+      <c r="DG12" s="2" t="inlineStr"/>
+      <c r="DH12" s="2" t="inlineStr"/>
+      <c r="DI12" s="2" t="inlineStr"/>
+      <c r="DJ12" s="2" t="inlineStr"/>
+      <c r="DK12" s="2" t="inlineStr"/>
+      <c r="DL12" s="2" t="inlineStr"/>
+      <c r="DM12" s="2" t="inlineStr"/>
+      <c r="DN12" s="2" t="inlineStr"/>
+      <c r="DO12" s="2" t="inlineStr"/>
+      <c r="DP12" s="2" t="inlineStr"/>
+      <c r="DQ12" s="2" t="inlineStr"/>
+      <c r="DR12" s="2" t="inlineStr"/>
+      <c r="DS12" s="2" t="inlineStr"/>
+      <c r="DT12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3295,73 +4415,143 @@
       </c>
       <c r="AH13" s="2" t="inlineStr"/>
       <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1kABxH03ZLmaZjAkbvH26Jo1jL0hLke-N#list</t>
-        </is>
-      </c>
-      <c r="AK13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Ei8AXBGtkst_X8r7G_ED5SpfGGCAj8sE#list</t>
-        </is>
-      </c>
-      <c r="AL13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1m0-6ZgV0ORDWi0iWEeBPBhovvZFy25GK#list</t>
-        </is>
-      </c>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1gDviJpH4l-z9edk7m8HJLoKecZiF2T1s#list</t>
-        </is>
-      </c>
-      <c r="AO13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Vj4n9Ok1K953DM0UJl_MLqxwNZ7buByy#list</t>
-        </is>
-      </c>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr"/>
       <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=15Nc0DHZOtKWJILvtKOjrPO1Cxuy7-o1C#list</t>
-        </is>
-      </c>
-      <c r="AR13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1s4y6rLssRLy4U3_aA8fQO0H1yve44Sed#list</t>
-        </is>
-      </c>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
       <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=19jZDdI6wQT9KQrVLLWEFBz21evRTuNHK#list</t>
-        </is>
-      </c>
+      <c r="AT13" s="2" t="inlineStr"/>
       <c r="AU13" s="2" t="inlineStr"/>
       <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1UGVGPGTWkmpsjKWwWctUxSwgLuxDdZ-S#list</t>
-        </is>
-      </c>
+      <c r="AW13" s="2" t="inlineStr"/>
       <c r="AX13" s="2" t="inlineStr"/>
       <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr">
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr"/>
+      <c r="BC13" s="2" t="inlineStr"/>
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr"/>
+      <c r="BF13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="inlineStr"/>
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BM13" s="2" t="inlineStr"/>
+      <c r="BN13" s="2" t="inlineStr"/>
+      <c r="BO13" s="2" t="inlineStr"/>
+      <c r="BP13" s="2" t="inlineStr"/>
+      <c r="BQ13" s="2" t="inlineStr"/>
+      <c r="BR13" s="2" t="inlineStr"/>
+      <c r="BS13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kABxH03ZLmaZjAkbvH26Jo1jL0hLke-N#list</t>
+        </is>
+      </c>
+      <c r="BT13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ei8AXBGtkst_X8r7G_ED5SpfGGCAj8sE#list</t>
+        </is>
+      </c>
+      <c r="BU13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1m0-6ZgV0ORDWi0iWEeBPBhovvZFy25GK#list</t>
+        </is>
+      </c>
+      <c r="BV13" s="2" t="inlineStr"/>
+      <c r="BW13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1gDviJpH4l-z9edk7m8HJLoKecZiF2T1s#list</t>
+        </is>
+      </c>
+      <c r="BX13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Vj4n9Ok1K953DM0UJl_MLqxwNZ7buByy#list</t>
+        </is>
+      </c>
+      <c r="BY13" s="2" t="inlineStr"/>
+      <c r="BZ13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15Nc0DHZOtKWJILvtKOjrPO1Cxuy7-o1C#list</t>
+        </is>
+      </c>
+      <c r="CA13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1s4y6rLssRLy4U3_aA8fQO0H1yve44Sed#list</t>
+        </is>
+      </c>
+      <c r="CB13" s="2" t="inlineStr"/>
+      <c r="CC13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19jZDdI6wQT9KQrVLLWEFBz21evRTuNHK#list</t>
+        </is>
+      </c>
+      <c r="CD13" s="2" t="inlineStr"/>
+      <c r="CE13" s="2" t="inlineStr"/>
+      <c r="CF13" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UGVGPGTWkmpsjKWwWctUxSwgLuxDdZ-S#list</t>
+        </is>
+      </c>
+      <c r="CG13" s="2" t="inlineStr"/>
+      <c r="CH13" s="2" t="inlineStr"/>
+      <c r="CI13" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1xwucW7jUJwHa7XOATQi7FDZpp7cWawDL#list</t>
         </is>
       </c>
-      <c r="BA13" s="2" t="inlineStr">
+      <c r="CJ13" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=12o6iXDkZREGtGE9VDE6aW-73rs0AOHNk#list</t>
         </is>
       </c>
-      <c r="BB13" s="2" t="inlineStr">
+      <c r="CK13" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1iERyv8L7lrVu80wq6G7_cG3kV0eHG0sJ#list</t>
         </is>
       </c>
+      <c r="CL13" s="2" t="inlineStr"/>
+      <c r="CM13" s="2" t="inlineStr"/>
+      <c r="CN13" s="2" t="inlineStr"/>
+      <c r="CO13" s="2" t="inlineStr"/>
+      <c r="CP13" s="2" t="inlineStr"/>
+      <c r="CQ13" s="2" t="inlineStr"/>
+      <c r="CR13" s="2" t="inlineStr"/>
+      <c r="CS13" s="2" t="inlineStr"/>
+      <c r="CT13" s="2" t="inlineStr"/>
+      <c r="CU13" s="2" t="inlineStr"/>
+      <c r="CV13" s="2" t="inlineStr"/>
+      <c r="CW13" s="2" t="inlineStr"/>
+      <c r="CX13" s="2" t="inlineStr"/>
+      <c r="CY13" s="2" t="inlineStr"/>
+      <c r="CZ13" s="2" t="inlineStr"/>
+      <c r="DA13" s="2" t="inlineStr"/>
+      <c r="DB13" s="2" t="inlineStr"/>
+      <c r="DC13" s="2" t="inlineStr"/>
+      <c r="DD13" s="2" t="inlineStr"/>
+      <c r="DE13" s="2" t="inlineStr"/>
+      <c r="DF13" s="2" t="inlineStr"/>
+      <c r="DG13" s="2" t="inlineStr"/>
+      <c r="DH13" s="2" t="inlineStr"/>
+      <c r="DI13" s="2" t="inlineStr"/>
+      <c r="DJ13" s="2" t="inlineStr"/>
+      <c r="DK13" s="2" t="inlineStr"/>
+      <c r="DL13" s="2" t="inlineStr"/>
+      <c r="DM13" s="2" t="inlineStr"/>
+      <c r="DN13" s="2" t="inlineStr"/>
+      <c r="DO13" s="2" t="inlineStr"/>
+      <c r="DP13" s="2" t="inlineStr"/>
+      <c r="DQ13" s="2" t="inlineStr"/>
+      <c r="DR13" s="2" t="inlineStr"/>
+      <c r="DS13" s="2" t="inlineStr"/>
+      <c r="DT13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3519,57 +4709,127 @@
       </c>
       <c r="AH14" s="2" t="inlineStr"/>
       <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=15gbadg6dr0SY4As5J6SllgdJY7fElbMS#list</t>
-        </is>
-      </c>
-      <c r="AK14" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1sNdF57nLwhxQYaAOB_m84RQB-lmDt4Iq#list</t>
-        </is>
-      </c>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
       <c r="AO14" s="2" t="inlineStr"/>
       <c r="AP14" s="2" t="inlineStr"/>
-      <c r="AQ14" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1mD7RWH1IkwEogxalW_LPsMLQ0yDyuQvi#list</t>
-        </is>
-      </c>
+      <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
       <c r="AS14" s="2" t="inlineStr"/>
-      <c r="AT14" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1NZfzYIh3yW0h8FpCYColKZN_zHHjVdSV#list</t>
-        </is>
-      </c>
+      <c r="AT14" s="2" t="inlineStr"/>
       <c r="AU14" s="2" t="inlineStr"/>
       <c r="AV14" s="2" t="inlineStr"/>
-      <c r="AW14" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=17o2935s-_FQzUzgDeW95AqNbFueO2kho#list</t>
-        </is>
-      </c>
+      <c r="AW14" s="2" t="inlineStr"/>
       <c r="AX14" s="2" t="inlineStr"/>
       <c r="AY14" s="2" t="inlineStr"/>
-      <c r="AZ14" s="2" t="inlineStr">
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr"/>
+      <c r="BC14" s="2" t="inlineStr"/>
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr"/>
+      <c r="BF14" s="2" t="inlineStr"/>
+      <c r="BG14" s="2" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BM14" s="2" t="inlineStr"/>
+      <c r="BN14" s="2" t="inlineStr"/>
+      <c r="BO14" s="2" t="inlineStr"/>
+      <c r="BP14" s="2" t="inlineStr"/>
+      <c r="BQ14" s="2" t="inlineStr"/>
+      <c r="BR14" s="2" t="inlineStr"/>
+      <c r="BS14" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15gbadg6dr0SY4As5J6SllgdJY7fElbMS#list</t>
+        </is>
+      </c>
+      <c r="BT14" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1sNdF57nLwhxQYaAOB_m84RQB-lmDt4Iq#list</t>
+        </is>
+      </c>
+      <c r="BU14" s="2" t="inlineStr"/>
+      <c r="BV14" s="2" t="inlineStr"/>
+      <c r="BW14" s="2" t="inlineStr"/>
+      <c r="BX14" s="2" t="inlineStr"/>
+      <c r="BY14" s="2" t="inlineStr"/>
+      <c r="BZ14" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1mD7RWH1IkwEogxalW_LPsMLQ0yDyuQvi#list</t>
+        </is>
+      </c>
+      <c r="CA14" s="2" t="inlineStr"/>
+      <c r="CB14" s="2" t="inlineStr"/>
+      <c r="CC14" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NZfzYIh3yW0h8FpCYColKZN_zHHjVdSV#list</t>
+        </is>
+      </c>
+      <c r="CD14" s="2" t="inlineStr"/>
+      <c r="CE14" s="2" t="inlineStr"/>
+      <c r="CF14" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=17o2935s-_FQzUzgDeW95AqNbFueO2kho#list</t>
+        </is>
+      </c>
+      <c r="CG14" s="2" t="inlineStr"/>
+      <c r="CH14" s="2" t="inlineStr"/>
+      <c r="CI14" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Oq4votgYHby5XUMUec-NrpyMjAGzS88Z#list</t>
         </is>
       </c>
-      <c r="BA14" s="2" t="inlineStr">
+      <c r="CJ14" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1hxAQYLT-nDACXEa6JDLyYG1VkZTJGkDQ#list</t>
         </is>
       </c>
-      <c r="BB14" s="2" t="inlineStr">
+      <c r="CK14" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1nZOXiCljiywVgJsR_T-LPvrNSZBOKqtN#list</t>
         </is>
       </c>
+      <c r="CL14" s="2" t="inlineStr"/>
+      <c r="CM14" s="2" t="inlineStr"/>
+      <c r="CN14" s="2" t="inlineStr"/>
+      <c r="CO14" s="2" t="inlineStr"/>
+      <c r="CP14" s="2" t="inlineStr"/>
+      <c r="CQ14" s="2" t="inlineStr"/>
+      <c r="CR14" s="2" t="inlineStr"/>
+      <c r="CS14" s="2" t="inlineStr"/>
+      <c r="CT14" s="2" t="inlineStr"/>
+      <c r="CU14" s="2" t="inlineStr"/>
+      <c r="CV14" s="2" t="inlineStr"/>
+      <c r="CW14" s="2" t="inlineStr"/>
+      <c r="CX14" s="2" t="inlineStr"/>
+      <c r="CY14" s="2" t="inlineStr"/>
+      <c r="CZ14" s="2" t="inlineStr"/>
+      <c r="DA14" s="2" t="inlineStr"/>
+      <c r="DB14" s="2" t="inlineStr"/>
+      <c r="DC14" s="2" t="inlineStr"/>
+      <c r="DD14" s="2" t="inlineStr"/>
+      <c r="DE14" s="2" t="inlineStr"/>
+      <c r="DF14" s="2" t="inlineStr"/>
+      <c r="DG14" s="2" t="inlineStr"/>
+      <c r="DH14" s="2" t="inlineStr"/>
+      <c r="DI14" s="2" t="inlineStr"/>
+      <c r="DJ14" s="2" t="inlineStr"/>
+      <c r="DK14" s="2" t="inlineStr"/>
+      <c r="DL14" s="2" t="inlineStr"/>
+      <c r="DM14" s="2" t="inlineStr"/>
+      <c r="DN14" s="2" t="inlineStr"/>
+      <c r="DO14" s="2" t="inlineStr"/>
+      <c r="DP14" s="2" t="inlineStr"/>
+      <c r="DQ14" s="2" t="inlineStr"/>
+      <c r="DR14" s="2" t="inlineStr"/>
+      <c r="DS14" s="2" t="inlineStr"/>
+      <c r="DT14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3727,61 +4987,131 @@
       </c>
       <c r="AH15" s="2" t="inlineStr"/>
       <c r="AI15" s="2" t="inlineStr"/>
-      <c r="AJ15" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1wQVAJ5-QEWo85DTON1J2xzdPB4Z6GQfr#list</t>
-        </is>
-      </c>
-      <c r="AK15" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1hm_kV8JxAEBU65KwuVpLoAMRY67hpypK#list</t>
-        </is>
-      </c>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
-      <c r="AN15" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1-K72PcRRWMPVP98aipztPb0TQhH6GYNt#list</t>
-        </is>
-      </c>
+      <c r="AN15" s="2" t="inlineStr"/>
       <c r="AO15" s="2" t="inlineStr"/>
       <c r="AP15" s="2" t="inlineStr"/>
-      <c r="AQ15" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1OaEZYpq3jd-1cfSObY3SDVyYplEw0AEc#list</t>
-        </is>
-      </c>
+      <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
       <c r="AS15" s="2" t="inlineStr"/>
-      <c r="AT15" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1rLfC7y0bI7bmkC-iv1_ER9mLuhXMmcfi#list</t>
-        </is>
-      </c>
+      <c r="AT15" s="2" t="inlineStr"/>
       <c r="AU15" s="2" t="inlineStr"/>
       <c r="AV15" s="2" t="inlineStr"/>
-      <c r="AW15" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1P2Ja5beYFz_bLpS5Rthz5N82xf5aEzla#list</t>
-        </is>
-      </c>
+      <c r="AW15" s="2" t="inlineStr"/>
       <c r="AX15" s="2" t="inlineStr"/>
       <c r="AY15" s="2" t="inlineStr"/>
-      <c r="AZ15" s="2" t="inlineStr">
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr"/>
+      <c r="BC15" s="2" t="inlineStr"/>
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr"/>
+      <c r="BF15" s="2" t="inlineStr"/>
+      <c r="BG15" s="2" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BM15" s="2" t="inlineStr"/>
+      <c r="BN15" s="2" t="inlineStr"/>
+      <c r="BO15" s="2" t="inlineStr"/>
+      <c r="BP15" s="2" t="inlineStr"/>
+      <c r="BQ15" s="2" t="inlineStr"/>
+      <c r="BR15" s="2" t="inlineStr"/>
+      <c r="BS15" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1wQVAJ5-QEWo85DTON1J2xzdPB4Z6GQfr#list</t>
+        </is>
+      </c>
+      <c r="BT15" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1hm_kV8JxAEBU65KwuVpLoAMRY67hpypK#list</t>
+        </is>
+      </c>
+      <c r="BU15" s="2" t="inlineStr"/>
+      <c r="BV15" s="2" t="inlineStr"/>
+      <c r="BW15" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-K72PcRRWMPVP98aipztPb0TQhH6GYNt#list</t>
+        </is>
+      </c>
+      <c r="BX15" s="2" t="inlineStr"/>
+      <c r="BY15" s="2" t="inlineStr"/>
+      <c r="BZ15" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OaEZYpq3jd-1cfSObY3SDVyYplEw0AEc#list</t>
+        </is>
+      </c>
+      <c r="CA15" s="2" t="inlineStr"/>
+      <c r="CB15" s="2" t="inlineStr"/>
+      <c r="CC15" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rLfC7y0bI7bmkC-iv1_ER9mLuhXMmcfi#list</t>
+        </is>
+      </c>
+      <c r="CD15" s="2" t="inlineStr"/>
+      <c r="CE15" s="2" t="inlineStr"/>
+      <c r="CF15" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1P2Ja5beYFz_bLpS5Rthz5N82xf5aEzla#list</t>
+        </is>
+      </c>
+      <c r="CG15" s="2" t="inlineStr"/>
+      <c r="CH15" s="2" t="inlineStr"/>
+      <c r="CI15" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1kYhrBakmNyY484G21Ak9dvBaxuj5xSHh#list</t>
         </is>
       </c>
-      <c r="BA15" s="2" t="inlineStr">
+      <c r="CJ15" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aeK9oVkI34t3jSgRmgOHYCahcnjiQl7P#list</t>
         </is>
       </c>
-      <c r="BB15" s="2" t="inlineStr">
+      <c r="CK15" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1XbOy9DacEOTLZOpTdqeE_aWaFdbaE_Ts#list</t>
         </is>
       </c>
+      <c r="CL15" s="2" t="inlineStr"/>
+      <c r="CM15" s="2" t="inlineStr"/>
+      <c r="CN15" s="2" t="inlineStr"/>
+      <c r="CO15" s="2" t="inlineStr"/>
+      <c r="CP15" s="2" t="inlineStr"/>
+      <c r="CQ15" s="2" t="inlineStr"/>
+      <c r="CR15" s="2" t="inlineStr"/>
+      <c r="CS15" s="2" t="inlineStr"/>
+      <c r="CT15" s="2" t="inlineStr"/>
+      <c r="CU15" s="2" t="inlineStr"/>
+      <c r="CV15" s="2" t="inlineStr"/>
+      <c r="CW15" s="2" t="inlineStr"/>
+      <c r="CX15" s="2" t="inlineStr"/>
+      <c r="CY15" s="2" t="inlineStr"/>
+      <c r="CZ15" s="2" t="inlineStr"/>
+      <c r="DA15" s="2" t="inlineStr"/>
+      <c r="DB15" s="2" t="inlineStr"/>
+      <c r="DC15" s="2" t="inlineStr"/>
+      <c r="DD15" s="2" t="inlineStr"/>
+      <c r="DE15" s="2" t="inlineStr"/>
+      <c r="DF15" s="2" t="inlineStr"/>
+      <c r="DG15" s="2" t="inlineStr"/>
+      <c r="DH15" s="2" t="inlineStr"/>
+      <c r="DI15" s="2" t="inlineStr"/>
+      <c r="DJ15" s="2" t="inlineStr"/>
+      <c r="DK15" s="2" t="inlineStr"/>
+      <c r="DL15" s="2" t="inlineStr"/>
+      <c r="DM15" s="2" t="inlineStr"/>
+      <c r="DN15" s="2" t="inlineStr"/>
+      <c r="DO15" s="2" t="inlineStr"/>
+      <c r="DP15" s="2" t="inlineStr"/>
+      <c r="DQ15" s="2" t="inlineStr"/>
+      <c r="DR15" s="2" t="inlineStr"/>
+      <c r="DS15" s="2" t="inlineStr"/>
+      <c r="DT15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3939,61 +5269,131 @@
       </c>
       <c r="AH16" s="2" t="inlineStr"/>
       <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=11YkQjnYH4VKsyU1oD-WG3iydrWW7YLUk#list</t>
-        </is>
-      </c>
-      <c r="AK16" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Y6xTqiOlZEx9lqbdqrDfwdH5AvkNw5fL#list</t>
-        </is>
-      </c>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
-      <c r="AN16" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1t1nmx_c02BMA85jkus4unyfKwVAJzbz-#list</t>
-        </is>
-      </c>
+      <c r="AN16" s="2" t="inlineStr"/>
       <c r="AO16" s="2" t="inlineStr"/>
       <c r="AP16" s="2" t="inlineStr"/>
-      <c r="AQ16" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1aAzLdac0FselZg5zIlyUPI5XUwfAr-GN#list</t>
-        </is>
-      </c>
+      <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
       <c r="AS16" s="2" t="inlineStr"/>
-      <c r="AT16" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1QZVmEy_11lKrJzeFxx1v3KWZH7E7mzKZ#list</t>
-        </is>
-      </c>
+      <c r="AT16" s="2" t="inlineStr"/>
       <c r="AU16" s="2" t="inlineStr"/>
       <c r="AV16" s="2" t="inlineStr"/>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1K5iQ32ReJ8EfMSl0xJ1MNh-OmS59RjhK#list</t>
-        </is>
-      </c>
+      <c r="AW16" s="2" t="inlineStr"/>
       <c r="AX16" s="2" t="inlineStr"/>
       <c r="AY16" s="2" t="inlineStr"/>
-      <c r="AZ16" s="2" t="inlineStr">
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr"/>
+      <c r="BC16" s="2" t="inlineStr"/>
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr"/>
+      <c r="BF16" s="2" t="inlineStr"/>
+      <c r="BG16" s="2" t="inlineStr"/>
+      <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BM16" s="2" t="inlineStr"/>
+      <c r="BN16" s="2" t="inlineStr"/>
+      <c r="BO16" s="2" t="inlineStr"/>
+      <c r="BP16" s="2" t="inlineStr"/>
+      <c r="BQ16" s="2" t="inlineStr"/>
+      <c r="BR16" s="2" t="inlineStr"/>
+      <c r="BS16" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11YkQjnYH4VKsyU1oD-WG3iydrWW7YLUk#list</t>
+        </is>
+      </c>
+      <c r="BT16" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Y6xTqiOlZEx9lqbdqrDfwdH5AvkNw5fL#list</t>
+        </is>
+      </c>
+      <c r="BU16" s="2" t="inlineStr"/>
+      <c r="BV16" s="2" t="inlineStr"/>
+      <c r="BW16" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1t1nmx_c02BMA85jkus4unyfKwVAJzbz-#list</t>
+        </is>
+      </c>
+      <c r="BX16" s="2" t="inlineStr"/>
+      <c r="BY16" s="2" t="inlineStr"/>
+      <c r="BZ16" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1aAzLdac0FselZg5zIlyUPI5XUwfAr-GN#list</t>
+        </is>
+      </c>
+      <c r="CA16" s="2" t="inlineStr"/>
+      <c r="CB16" s="2" t="inlineStr"/>
+      <c r="CC16" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QZVmEy_11lKrJzeFxx1v3KWZH7E7mzKZ#list</t>
+        </is>
+      </c>
+      <c r="CD16" s="2" t="inlineStr"/>
+      <c r="CE16" s="2" t="inlineStr"/>
+      <c r="CF16" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1K5iQ32ReJ8EfMSl0xJ1MNh-OmS59RjhK#list</t>
+        </is>
+      </c>
+      <c r="CG16" s="2" t="inlineStr"/>
+      <c r="CH16" s="2" t="inlineStr"/>
+      <c r="CI16" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ov2JZ34a53Lp0xzwGx4WjiHaIdYB1Iuh#list</t>
         </is>
       </c>
-      <c r="BA16" s="2" t="inlineStr">
+      <c r="CJ16" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=13tfQUr0lN8wwXjeDEFX2xRQgzQ9Hgwwd#list</t>
         </is>
       </c>
-      <c r="BB16" s="2" t="inlineStr">
+      <c r="CK16" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1k5OQ47AwZyWtQv1OsgNjp8H4GzFWQ5ht#list</t>
         </is>
       </c>
+      <c r="CL16" s="2" t="inlineStr"/>
+      <c r="CM16" s="2" t="inlineStr"/>
+      <c r="CN16" s="2" t="inlineStr"/>
+      <c r="CO16" s="2" t="inlineStr"/>
+      <c r="CP16" s="2" t="inlineStr"/>
+      <c r="CQ16" s="2" t="inlineStr"/>
+      <c r="CR16" s="2" t="inlineStr"/>
+      <c r="CS16" s="2" t="inlineStr"/>
+      <c r="CT16" s="2" t="inlineStr"/>
+      <c r="CU16" s="2" t="inlineStr"/>
+      <c r="CV16" s="2" t="inlineStr"/>
+      <c r="CW16" s="2" t="inlineStr"/>
+      <c r="CX16" s="2" t="inlineStr"/>
+      <c r="CY16" s="2" t="inlineStr"/>
+      <c r="CZ16" s="2" t="inlineStr"/>
+      <c r="DA16" s="2" t="inlineStr"/>
+      <c r="DB16" s="2" t="inlineStr"/>
+      <c r="DC16" s="2" t="inlineStr"/>
+      <c r="DD16" s="2" t="inlineStr"/>
+      <c r="DE16" s="2" t="inlineStr"/>
+      <c r="DF16" s="2" t="inlineStr"/>
+      <c r="DG16" s="2" t="inlineStr"/>
+      <c r="DH16" s="2" t="inlineStr"/>
+      <c r="DI16" s="2" t="inlineStr"/>
+      <c r="DJ16" s="2" t="inlineStr"/>
+      <c r="DK16" s="2" t="inlineStr"/>
+      <c r="DL16" s="2" t="inlineStr"/>
+      <c r="DM16" s="2" t="inlineStr"/>
+      <c r="DN16" s="2" t="inlineStr"/>
+      <c r="DO16" s="2" t="inlineStr"/>
+      <c r="DP16" s="2" t="inlineStr"/>
+      <c r="DQ16" s="2" t="inlineStr"/>
+      <c r="DR16" s="2" t="inlineStr"/>
+      <c r="DS16" s="2" t="inlineStr"/>
+      <c r="DT16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4151,65 +5551,135 @@
       </c>
       <c r="AH17" s="2" t="inlineStr"/>
       <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=109MVtze2amhFTQKnZKz7vOfy1-o9tO7r#list</t>
-        </is>
-      </c>
-      <c r="AK17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=18HTtPUzHf3aaAPlLgRcANk8Y2Dtsf8zt#list</t>
-        </is>
-      </c>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
-      <c r="AN17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1iiFbV18mToNILfGcYEfPpxnTVKoi80zF#list</t>
-        </is>
-      </c>
+      <c r="AN17" s="2" t="inlineStr"/>
       <c r="AO17" s="2" t="inlineStr"/>
       <c r="AP17" s="2" t="inlineStr"/>
-      <c r="AQ17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1ejA8cjFPOpXzxP2SMe8Lf0MzBgsWhkwt#list</t>
-        </is>
-      </c>
+      <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
       <c r="AS17" s="2" t="inlineStr"/>
-      <c r="AT17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1-UA85r5ez-IWMmjejFrR7_Zz6LKhi7ZC#list</t>
-        </is>
-      </c>
-      <c r="AU17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1RodclQ8_Ar3gLDnRwFjVjG3dEbFxIlk-#list</t>
-        </is>
-      </c>
+      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AU17" s="2" t="inlineStr"/>
       <c r="AV17" s="2" t="inlineStr"/>
-      <c r="AW17" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1RodclQ8_Ar3gLDnRwFjVjG3dEbFxIlk-#list</t>
-        </is>
-      </c>
+      <c r="AW17" s="2" t="inlineStr"/>
       <c r="AX17" s="2" t="inlineStr"/>
       <c r="AY17" s="2" t="inlineStr"/>
-      <c r="AZ17" s="2" t="inlineStr">
+      <c r="AZ17" s="2" t="inlineStr"/>
+      <c r="BA17" s="2" t="inlineStr"/>
+      <c r="BB17" s="2" t="inlineStr"/>
+      <c r="BC17" s="2" t="inlineStr"/>
+      <c r="BD17" s="2" t="inlineStr"/>
+      <c r="BE17" s="2" t="inlineStr"/>
+      <c r="BF17" s="2" t="inlineStr"/>
+      <c r="BG17" s="2" t="inlineStr"/>
+      <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BM17" s="2" t="inlineStr"/>
+      <c r="BN17" s="2" t="inlineStr"/>
+      <c r="BO17" s="2" t="inlineStr"/>
+      <c r="BP17" s="2" t="inlineStr"/>
+      <c r="BQ17" s="2" t="inlineStr"/>
+      <c r="BR17" s="2" t="inlineStr"/>
+      <c r="BS17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=109MVtze2amhFTQKnZKz7vOfy1-o9tO7r#list</t>
+        </is>
+      </c>
+      <c r="BT17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18HTtPUzHf3aaAPlLgRcANk8Y2Dtsf8zt#list</t>
+        </is>
+      </c>
+      <c r="BU17" s="2" t="inlineStr"/>
+      <c r="BV17" s="2" t="inlineStr"/>
+      <c r="BW17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iiFbV18mToNILfGcYEfPpxnTVKoi80zF#list</t>
+        </is>
+      </c>
+      <c r="BX17" s="2" t="inlineStr"/>
+      <c r="BY17" s="2" t="inlineStr"/>
+      <c r="BZ17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ejA8cjFPOpXzxP2SMe8Lf0MzBgsWhkwt#list</t>
+        </is>
+      </c>
+      <c r="CA17" s="2" t="inlineStr"/>
+      <c r="CB17" s="2" t="inlineStr"/>
+      <c r="CC17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-UA85r5ez-IWMmjejFrR7_Zz6LKhi7ZC#list</t>
+        </is>
+      </c>
+      <c r="CD17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RodclQ8_Ar3gLDnRwFjVjG3dEbFxIlk-#list</t>
+        </is>
+      </c>
+      <c r="CE17" s="2" t="inlineStr"/>
+      <c r="CF17" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RodclQ8_Ar3gLDnRwFjVjG3dEbFxIlk-#list</t>
+        </is>
+      </c>
+      <c r="CG17" s="2" t="inlineStr"/>
+      <c r="CH17" s="2" t="inlineStr"/>
+      <c r="CI17" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1VOMU6ph21te_3zgNuDpOUJmOCaYlGpr5#list</t>
         </is>
       </c>
-      <c r="BA17" s="2" t="inlineStr">
+      <c r="CJ17" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=19YDtv3mxGRMLjz2h2V09rQb6Zz1hmwkL#list</t>
         </is>
       </c>
-      <c r="BB17" s="2" t="inlineStr">
+      <c r="CK17" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Gnuff-4DPOZeS7R7Pjt_9wQP34CHmPU7#list</t>
         </is>
       </c>
+      <c r="CL17" s="2" t="inlineStr"/>
+      <c r="CM17" s="2" t="inlineStr"/>
+      <c r="CN17" s="2" t="inlineStr"/>
+      <c r="CO17" s="2" t="inlineStr"/>
+      <c r="CP17" s="2" t="inlineStr"/>
+      <c r="CQ17" s="2" t="inlineStr"/>
+      <c r="CR17" s="2" t="inlineStr"/>
+      <c r="CS17" s="2" t="inlineStr"/>
+      <c r="CT17" s="2" t="inlineStr"/>
+      <c r="CU17" s="2" t="inlineStr"/>
+      <c r="CV17" s="2" t="inlineStr"/>
+      <c r="CW17" s="2" t="inlineStr"/>
+      <c r="CX17" s="2" t="inlineStr"/>
+      <c r="CY17" s="2" t="inlineStr"/>
+      <c r="CZ17" s="2" t="inlineStr"/>
+      <c r="DA17" s="2" t="inlineStr"/>
+      <c r="DB17" s="2" t="inlineStr"/>
+      <c r="DC17" s="2" t="inlineStr"/>
+      <c r="DD17" s="2" t="inlineStr"/>
+      <c r="DE17" s="2" t="inlineStr"/>
+      <c r="DF17" s="2" t="inlineStr"/>
+      <c r="DG17" s="2" t="inlineStr"/>
+      <c r="DH17" s="2" t="inlineStr"/>
+      <c r="DI17" s="2" t="inlineStr"/>
+      <c r="DJ17" s="2" t="inlineStr"/>
+      <c r="DK17" s="2" t="inlineStr"/>
+      <c r="DL17" s="2" t="inlineStr"/>
+      <c r="DM17" s="2" t="inlineStr"/>
+      <c r="DN17" s="2" t="inlineStr"/>
+      <c r="DO17" s="2" t="inlineStr"/>
+      <c r="DP17" s="2" t="inlineStr"/>
+      <c r="DQ17" s="2" t="inlineStr"/>
+      <c r="DR17" s="2" t="inlineStr"/>
+      <c r="DS17" s="2" t="inlineStr"/>
+      <c r="DT17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4367,61 +5837,131 @@
       </c>
       <c r="AH18" s="2" t="inlineStr"/>
       <c r="AI18" s="2" t="inlineStr"/>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1qODcbTBzRFaf9MOTwn8Wq_aL6gjLXAoY#list</t>
-        </is>
-      </c>
-      <c r="AK18" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1G5ELrWfgybaWS4-QKBSPiCgghpDdjiNZ#list</t>
-        </is>
-      </c>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
-      <c r="AN18" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1lejK4Vlbqc6NAgzEZ84GBdpqbqbZ1C-y#list</t>
-        </is>
-      </c>
+      <c r="AN18" s="2" t="inlineStr"/>
       <c r="AO18" s="2" t="inlineStr"/>
       <c r="AP18" s="2" t="inlineStr"/>
-      <c r="AQ18" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1z-BDkv-0d-DmDdPNTPr0WgfWADVuT5Si#list</t>
-        </is>
-      </c>
+      <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
       <c r="AS18" s="2" t="inlineStr"/>
-      <c r="AT18" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=15Qrny1d2zboFAo9iD_Uaj51DrTzwEiMj#list</t>
-        </is>
-      </c>
+      <c r="AT18" s="2" t="inlineStr"/>
       <c r="AU18" s="2" t="inlineStr"/>
       <c r="AV18" s="2" t="inlineStr"/>
-      <c r="AW18" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1YjWlL1RPWYTjtXGiU9IrG5req-0VqIGP#list</t>
-        </is>
-      </c>
+      <c r="AW18" s="2" t="inlineStr"/>
       <c r="AX18" s="2" t="inlineStr"/>
       <c r="AY18" s="2" t="inlineStr"/>
-      <c r="AZ18" s="2" t="inlineStr">
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr"/>
+      <c r="BC18" s="2" t="inlineStr"/>
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr"/>
+      <c r="BF18" s="2" t="inlineStr"/>
+      <c r="BG18" s="2" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BM18" s="2" t="inlineStr"/>
+      <c r="BN18" s="2" t="inlineStr"/>
+      <c r="BO18" s="2" t="inlineStr"/>
+      <c r="BP18" s="2" t="inlineStr"/>
+      <c r="BQ18" s="2" t="inlineStr"/>
+      <c r="BR18" s="2" t="inlineStr"/>
+      <c r="BS18" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qODcbTBzRFaf9MOTwn8Wq_aL6gjLXAoY#list</t>
+        </is>
+      </c>
+      <c r="BT18" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1G5ELrWfgybaWS4-QKBSPiCgghpDdjiNZ#list</t>
+        </is>
+      </c>
+      <c r="BU18" s="2" t="inlineStr"/>
+      <c r="BV18" s="2" t="inlineStr"/>
+      <c r="BW18" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1lejK4Vlbqc6NAgzEZ84GBdpqbqbZ1C-y#list</t>
+        </is>
+      </c>
+      <c r="BX18" s="2" t="inlineStr"/>
+      <c r="BY18" s="2" t="inlineStr"/>
+      <c r="BZ18" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1z-BDkv-0d-DmDdPNTPr0WgfWADVuT5Si#list</t>
+        </is>
+      </c>
+      <c r="CA18" s="2" t="inlineStr"/>
+      <c r="CB18" s="2" t="inlineStr"/>
+      <c r="CC18" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15Qrny1d2zboFAo9iD_Uaj51DrTzwEiMj#list</t>
+        </is>
+      </c>
+      <c r="CD18" s="2" t="inlineStr"/>
+      <c r="CE18" s="2" t="inlineStr"/>
+      <c r="CF18" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YjWlL1RPWYTjtXGiU9IrG5req-0VqIGP#list</t>
+        </is>
+      </c>
+      <c r="CG18" s="2" t="inlineStr"/>
+      <c r="CH18" s="2" t="inlineStr"/>
+      <c r="CI18" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1t4SoTe3p9aT6uuHUmt6X0t3grHyHKPqY#list</t>
         </is>
       </c>
-      <c r="BA18" s="2" t="inlineStr">
+      <c r="CJ18" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1TdXFpXBYtmjYomn5rRWSBvDNEXAZoJmg#list</t>
         </is>
       </c>
-      <c r="BB18" s="2" t="inlineStr">
+      <c r="CK18" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1kDJEZUiM0mgUe4zS4S7DtI1AhtT506jW#list</t>
         </is>
       </c>
+      <c r="CL18" s="2" t="inlineStr"/>
+      <c r="CM18" s="2" t="inlineStr"/>
+      <c r="CN18" s="2" t="inlineStr"/>
+      <c r="CO18" s="2" t="inlineStr"/>
+      <c r="CP18" s="2" t="inlineStr"/>
+      <c r="CQ18" s="2" t="inlineStr"/>
+      <c r="CR18" s="2" t="inlineStr"/>
+      <c r="CS18" s="2" t="inlineStr"/>
+      <c r="CT18" s="2" t="inlineStr"/>
+      <c r="CU18" s="2" t="inlineStr"/>
+      <c r="CV18" s="2" t="inlineStr"/>
+      <c r="CW18" s="2" t="inlineStr"/>
+      <c r="CX18" s="2" t="inlineStr"/>
+      <c r="CY18" s="2" t="inlineStr"/>
+      <c r="CZ18" s="2" t="inlineStr"/>
+      <c r="DA18" s="2" t="inlineStr"/>
+      <c r="DB18" s="2" t="inlineStr"/>
+      <c r="DC18" s="2" t="inlineStr"/>
+      <c r="DD18" s="2" t="inlineStr"/>
+      <c r="DE18" s="2" t="inlineStr"/>
+      <c r="DF18" s="2" t="inlineStr"/>
+      <c r="DG18" s="2" t="inlineStr"/>
+      <c r="DH18" s="2" t="inlineStr"/>
+      <c r="DI18" s="2" t="inlineStr"/>
+      <c r="DJ18" s="2" t="inlineStr"/>
+      <c r="DK18" s="2" t="inlineStr"/>
+      <c r="DL18" s="2" t="inlineStr"/>
+      <c r="DM18" s="2" t="inlineStr"/>
+      <c r="DN18" s="2" t="inlineStr"/>
+      <c r="DO18" s="2" t="inlineStr"/>
+      <c r="DP18" s="2" t="inlineStr"/>
+      <c r="DQ18" s="2" t="inlineStr"/>
+      <c r="DR18" s="2" t="inlineStr"/>
+      <c r="DS18" s="2" t="inlineStr"/>
+      <c r="DT18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4579,61 +6119,131 @@
       </c>
       <c r="AH19" s="2" t="inlineStr"/>
       <c r="AI19" s="2" t="inlineStr"/>
-      <c r="AJ19" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1nI7CZ7s1aJjWl07nivdmj5zBx4kx88SA#list</t>
-        </is>
-      </c>
-      <c r="AK19" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1aoGvBFj_4Q7XZs6zTTmw4ko3KhyC-mwZ#list</t>
-        </is>
-      </c>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
-      <c r="AN19" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1cTuHZru6X2Hhv2n6ZH1LQ0fyAmWBw7BM#list</t>
-        </is>
-      </c>
+      <c r="AN19" s="2" t="inlineStr"/>
       <c r="AO19" s="2" t="inlineStr"/>
       <c r="AP19" s="2" t="inlineStr"/>
-      <c r="AQ19" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=197xnijvtgPZNSaw8B1QWQ-o7tNLREO2T#list</t>
-        </is>
-      </c>
+      <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
       <c r="AS19" s="2" t="inlineStr"/>
-      <c r="AT19" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1L63jsLFS4eCQhsczvoZBtmQDEzc1vQnw#list</t>
-        </is>
-      </c>
+      <c r="AT19" s="2" t="inlineStr"/>
       <c r="AU19" s="2" t="inlineStr"/>
       <c r="AV19" s="2" t="inlineStr"/>
-      <c r="AW19" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1F8HxMZ9xk_AYOgoqYBchWT22BmcLaJS9#list</t>
-        </is>
-      </c>
+      <c r="AW19" s="2" t="inlineStr"/>
       <c r="AX19" s="2" t="inlineStr"/>
       <c r="AY19" s="2" t="inlineStr"/>
-      <c r="AZ19" s="2" t="inlineStr">
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr"/>
+      <c r="BC19" s="2" t="inlineStr"/>
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr"/>
+      <c r="BF19" s="2" t="inlineStr"/>
+      <c r="BG19" s="2" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BM19" s="2" t="inlineStr"/>
+      <c r="BN19" s="2" t="inlineStr"/>
+      <c r="BO19" s="2" t="inlineStr"/>
+      <c r="BP19" s="2" t="inlineStr"/>
+      <c r="BQ19" s="2" t="inlineStr"/>
+      <c r="BR19" s="2" t="inlineStr"/>
+      <c r="BS19" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nI7CZ7s1aJjWl07nivdmj5zBx4kx88SA#list</t>
+        </is>
+      </c>
+      <c r="BT19" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1aoGvBFj_4Q7XZs6zTTmw4ko3KhyC-mwZ#list</t>
+        </is>
+      </c>
+      <c r="BU19" s="2" t="inlineStr"/>
+      <c r="BV19" s="2" t="inlineStr"/>
+      <c r="BW19" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1cTuHZru6X2Hhv2n6ZH1LQ0fyAmWBw7BM#list</t>
+        </is>
+      </c>
+      <c r="BX19" s="2" t="inlineStr"/>
+      <c r="BY19" s="2" t="inlineStr"/>
+      <c r="BZ19" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=197xnijvtgPZNSaw8B1QWQ-o7tNLREO2T#list</t>
+        </is>
+      </c>
+      <c r="CA19" s="2" t="inlineStr"/>
+      <c r="CB19" s="2" t="inlineStr"/>
+      <c r="CC19" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1L63jsLFS4eCQhsczvoZBtmQDEzc1vQnw#list</t>
+        </is>
+      </c>
+      <c r="CD19" s="2" t="inlineStr"/>
+      <c r="CE19" s="2" t="inlineStr"/>
+      <c r="CF19" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1F8HxMZ9xk_AYOgoqYBchWT22BmcLaJS9#list</t>
+        </is>
+      </c>
+      <c r="CG19" s="2" t="inlineStr"/>
+      <c r="CH19" s="2" t="inlineStr"/>
+      <c r="CI19" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ggbREtOKH8y5GRbKSMEt1kPeqSiEJc8Q#list</t>
         </is>
       </c>
-      <c r="BA19" s="2" t="inlineStr">
+      <c r="CJ19" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Q8eh7m05mtjouTtiwxfjm9lzObO8LBdm#list</t>
         </is>
       </c>
-      <c r="BB19" s="2" t="inlineStr">
+      <c r="CK19" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1DZO_1ud6z6w3VziF5jVs8VNLRQbC9vS3#list</t>
         </is>
       </c>
+      <c r="CL19" s="2" t="inlineStr"/>
+      <c r="CM19" s="2" t="inlineStr"/>
+      <c r="CN19" s="2" t="inlineStr"/>
+      <c r="CO19" s="2" t="inlineStr"/>
+      <c r="CP19" s="2" t="inlineStr"/>
+      <c r="CQ19" s="2" t="inlineStr"/>
+      <c r="CR19" s="2" t="inlineStr"/>
+      <c r="CS19" s="2" t="inlineStr"/>
+      <c r="CT19" s="2" t="inlineStr"/>
+      <c r="CU19" s="2" t="inlineStr"/>
+      <c r="CV19" s="2" t="inlineStr"/>
+      <c r="CW19" s="2" t="inlineStr"/>
+      <c r="CX19" s="2" t="inlineStr"/>
+      <c r="CY19" s="2" t="inlineStr"/>
+      <c r="CZ19" s="2" t="inlineStr"/>
+      <c r="DA19" s="2" t="inlineStr"/>
+      <c r="DB19" s="2" t="inlineStr"/>
+      <c r="DC19" s="2" t="inlineStr"/>
+      <c r="DD19" s="2" t="inlineStr"/>
+      <c r="DE19" s="2" t="inlineStr"/>
+      <c r="DF19" s="2" t="inlineStr"/>
+      <c r="DG19" s="2" t="inlineStr"/>
+      <c r="DH19" s="2" t="inlineStr"/>
+      <c r="DI19" s="2" t="inlineStr"/>
+      <c r="DJ19" s="2" t="inlineStr"/>
+      <c r="DK19" s="2" t="inlineStr"/>
+      <c r="DL19" s="2" t="inlineStr"/>
+      <c r="DM19" s="2" t="inlineStr"/>
+      <c r="DN19" s="2" t="inlineStr"/>
+      <c r="DO19" s="2" t="inlineStr"/>
+      <c r="DP19" s="2" t="inlineStr"/>
+      <c r="DQ19" s="2" t="inlineStr"/>
+      <c r="DR19" s="2" t="inlineStr"/>
+      <c r="DS19" s="2" t="inlineStr"/>
+      <c r="DT19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4789,79 +6399,149 @@
           <t>Eastern Cape November</t>
         </is>
       </c>
-      <c r="AH20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1EcBq1UoXr6jfbl6paxV70gzy50YYAMxE#list</t>
-        </is>
-      </c>
+      <c r="AH20" s="2" t="inlineStr"/>
       <c r="AI20" s="2" t="inlineStr"/>
-      <c r="AJ20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Gvnr76_xNRbYpkTNeS06aRyfMFfNFaYb#list</t>
-        </is>
-      </c>
-      <c r="AK20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1BmhXFehNVD9-PsUeue0j_vsFJNYb2Ovd#list</t>
-        </is>
-      </c>
-      <c r="AL20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1ocicHDsaN1_HY__gqPf5opLxgPBQ9tKo#list</t>
-        </is>
-      </c>
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr"/>
+      <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
-      <c r="AN20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1jqWqdInLfgBR6ewM127YXVdhS9RgfK6t#list</t>
-        </is>
-      </c>
-      <c r="AO20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1NpCeD05C3X5NG6CA8_U0kXfxbTjGKpCd#list</t>
-        </is>
-      </c>
+      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr"/>
       <c r="AP20" s="2" t="inlineStr"/>
-      <c r="AQ20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=12X6j6GS9HzBJBUyYJgGtpB1vBbQn-b2w#list</t>
-        </is>
-      </c>
-      <c r="AR20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1abdd-gyz2FbWvB_6ZXKFuBdZsAbOy3X2#list</t>
-        </is>
-      </c>
+      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="inlineStr"/>
       <c r="AS20" s="2" t="inlineStr"/>
-      <c r="AT20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1DVHdSL-bnGQIkNgawbD0Q3qRLuIxM46L#list</t>
-        </is>
-      </c>
+      <c r="AT20" s="2" t="inlineStr"/>
       <c r="AU20" s="2" t="inlineStr"/>
       <c r="AV20" s="2" t="inlineStr"/>
-      <c r="AW20" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1vKZj0yZkO_RUolWLO0vSJ_S53HSI5M0Z#list</t>
-        </is>
-      </c>
+      <c r="AW20" s="2" t="inlineStr"/>
       <c r="AX20" s="2" t="inlineStr"/>
       <c r="AY20" s="2" t="inlineStr"/>
-      <c r="AZ20" s="2" t="inlineStr">
+      <c r="AZ20" s="2" t="inlineStr"/>
+      <c r="BA20" s="2" t="inlineStr"/>
+      <c r="BB20" s="2" t="inlineStr"/>
+      <c r="BC20" s="2" t="inlineStr"/>
+      <c r="BD20" s="2" t="inlineStr"/>
+      <c r="BE20" s="2" t="inlineStr"/>
+      <c r="BF20" s="2" t="inlineStr"/>
+      <c r="BG20" s="2" t="inlineStr"/>
+      <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BM20" s="2" t="inlineStr"/>
+      <c r="BN20" s="2" t="inlineStr"/>
+      <c r="BO20" s="2" t="inlineStr"/>
+      <c r="BP20" s="2" t="inlineStr"/>
+      <c r="BQ20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1EcBq1UoXr6jfbl6paxV70gzy50YYAMxE#list</t>
+        </is>
+      </c>
+      <c r="BR20" s="2" t="inlineStr"/>
+      <c r="BS20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Gvnr76_xNRbYpkTNeS06aRyfMFfNFaYb#list</t>
+        </is>
+      </c>
+      <c r="BT20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BmhXFehNVD9-PsUeue0j_vsFJNYb2Ovd#list</t>
+        </is>
+      </c>
+      <c r="BU20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ocicHDsaN1_HY__gqPf5opLxgPBQ9tKo#list</t>
+        </is>
+      </c>
+      <c r="BV20" s="2" t="inlineStr"/>
+      <c r="BW20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jqWqdInLfgBR6ewM127YXVdhS9RgfK6t#list</t>
+        </is>
+      </c>
+      <c r="BX20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NpCeD05C3X5NG6CA8_U0kXfxbTjGKpCd#list</t>
+        </is>
+      </c>
+      <c r="BY20" s="2" t="inlineStr"/>
+      <c r="BZ20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=12X6j6GS9HzBJBUyYJgGtpB1vBbQn-b2w#list</t>
+        </is>
+      </c>
+      <c r="CA20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1abdd-gyz2FbWvB_6ZXKFuBdZsAbOy3X2#list</t>
+        </is>
+      </c>
+      <c r="CB20" s="2" t="inlineStr"/>
+      <c r="CC20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1DVHdSL-bnGQIkNgawbD0Q3qRLuIxM46L#list</t>
+        </is>
+      </c>
+      <c r="CD20" s="2" t="inlineStr"/>
+      <c r="CE20" s="2" t="inlineStr"/>
+      <c r="CF20" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vKZj0yZkO_RUolWLO0vSJ_S53HSI5M0Z#list</t>
+        </is>
+      </c>
+      <c r="CG20" s="2" t="inlineStr"/>
+      <c r="CH20" s="2" t="inlineStr"/>
+      <c r="CI20" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=134qX57ziOtxh6_fbgvfg5yjLKAy5hinU#list</t>
         </is>
       </c>
-      <c r="BA20" s="2" t="inlineStr">
+      <c r="CJ20" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1dV9NGMfx7jIO3rpvQCkt_cCzcSjHsHkU#list</t>
         </is>
       </c>
-      <c r="BB20" s="2" t="inlineStr">
+      <c r="CK20" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1qKxiYLmF1TdG2LybK2GolKs4I_P9fQey#list</t>
         </is>
       </c>
+      <c r="CL20" s="2" t="inlineStr"/>
+      <c r="CM20" s="2" t="inlineStr"/>
+      <c r="CN20" s="2" t="inlineStr"/>
+      <c r="CO20" s="2" t="inlineStr"/>
+      <c r="CP20" s="2" t="inlineStr"/>
+      <c r="CQ20" s="2" t="inlineStr"/>
+      <c r="CR20" s="2" t="inlineStr"/>
+      <c r="CS20" s="2" t="inlineStr"/>
+      <c r="CT20" s="2" t="inlineStr"/>
+      <c r="CU20" s="2" t="inlineStr"/>
+      <c r="CV20" s="2" t="inlineStr"/>
+      <c r="CW20" s="2" t="inlineStr"/>
+      <c r="CX20" s="2" t="inlineStr"/>
+      <c r="CY20" s="2" t="inlineStr"/>
+      <c r="CZ20" s="2" t="inlineStr"/>
+      <c r="DA20" s="2" t="inlineStr"/>
+      <c r="DB20" s="2" t="inlineStr"/>
+      <c r="DC20" s="2" t="inlineStr"/>
+      <c r="DD20" s="2" t="inlineStr"/>
+      <c r="DE20" s="2" t="inlineStr"/>
+      <c r="DF20" s="2" t="inlineStr"/>
+      <c r="DG20" s="2" t="inlineStr"/>
+      <c r="DH20" s="2" t="inlineStr"/>
+      <c r="DI20" s="2" t="inlineStr"/>
+      <c r="DJ20" s="2" t="inlineStr"/>
+      <c r="DK20" s="2" t="inlineStr"/>
+      <c r="DL20" s="2" t="inlineStr"/>
+      <c r="DM20" s="2" t="inlineStr"/>
+      <c r="DN20" s="2" t="inlineStr"/>
+      <c r="DO20" s="2" t="inlineStr"/>
+      <c r="DP20" s="2" t="inlineStr"/>
+      <c r="DQ20" s="2" t="inlineStr"/>
+      <c r="DR20" s="2" t="inlineStr"/>
+      <c r="DS20" s="2" t="inlineStr"/>
+      <c r="DT20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5023,49 +6703,119 @@
       <c r="AK21" s="2" t="inlineStr"/>
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
-      <c r="AN21" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1EhCXQx9L-kWuC5CRfPZ9n9v2YqYrgqbn#list</t>
-        </is>
-      </c>
+      <c r="AN21" s="2" t="inlineStr"/>
       <c r="AO21" s="2" t="inlineStr"/>
       <c r="AP21" s="2" t="inlineStr"/>
-      <c r="AQ21" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1ZCYli5kfjdKMp68O5_RTQ2m1ZHs8otZj#list</t>
-        </is>
-      </c>
+      <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
       <c r="AS21" s="2" t="inlineStr"/>
-      <c r="AT21" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1ELouzqWspFWOa4V0z1RhINDBAmXxh__G#list</t>
-        </is>
-      </c>
+      <c r="AT21" s="2" t="inlineStr"/>
       <c r="AU21" s="2" t="inlineStr"/>
       <c r="AV21" s="2" t="inlineStr"/>
-      <c r="AW21" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1k4_7PTO6SsygI5Blvk1wcMSPIwRleC5C#list</t>
-        </is>
-      </c>
+      <c r="AW21" s="2" t="inlineStr"/>
       <c r="AX21" s="2" t="inlineStr"/>
       <c r="AY21" s="2" t="inlineStr"/>
-      <c r="AZ21" s="2" t="inlineStr">
+      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="BA21" s="2" t="inlineStr"/>
+      <c r="BB21" s="2" t="inlineStr"/>
+      <c r="BC21" s="2" t="inlineStr"/>
+      <c r="BD21" s="2" t="inlineStr"/>
+      <c r="BE21" s="2" t="inlineStr"/>
+      <c r="BF21" s="2" t="inlineStr"/>
+      <c r="BG21" s="2" t="inlineStr"/>
+      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BM21" s="2" t="inlineStr"/>
+      <c r="BN21" s="2" t="inlineStr"/>
+      <c r="BO21" s="2" t="inlineStr"/>
+      <c r="BP21" s="2" t="inlineStr"/>
+      <c r="BQ21" s="2" t="inlineStr"/>
+      <c r="BR21" s="2" t="inlineStr"/>
+      <c r="BS21" s="2" t="inlineStr"/>
+      <c r="BT21" s="2" t="inlineStr"/>
+      <c r="BU21" s="2" t="inlineStr"/>
+      <c r="BV21" s="2" t="inlineStr"/>
+      <c r="BW21" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1EhCXQx9L-kWuC5CRfPZ9n9v2YqYrgqbn#list</t>
+        </is>
+      </c>
+      <c r="BX21" s="2" t="inlineStr"/>
+      <c r="BY21" s="2" t="inlineStr"/>
+      <c r="BZ21" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ZCYli5kfjdKMp68O5_RTQ2m1ZHs8otZj#list</t>
+        </is>
+      </c>
+      <c r="CA21" s="2" t="inlineStr"/>
+      <c r="CB21" s="2" t="inlineStr"/>
+      <c r="CC21" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ELouzqWspFWOa4V0z1RhINDBAmXxh__G#list</t>
+        </is>
+      </c>
+      <c r="CD21" s="2" t="inlineStr"/>
+      <c r="CE21" s="2" t="inlineStr"/>
+      <c r="CF21" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1k4_7PTO6SsygI5Blvk1wcMSPIwRleC5C#list</t>
+        </is>
+      </c>
+      <c r="CG21" s="2" t="inlineStr"/>
+      <c r="CH21" s="2" t="inlineStr"/>
+      <c r="CI21" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1WTnTsbyX9YoB0I7axs1AMZBO8oVj8u5n#list</t>
         </is>
       </c>
-      <c r="BA21" s="2" t="inlineStr">
+      <c r="CJ21" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aSWfFdN3IpyZC5nxM9c2MVdI-os55N2g#list</t>
         </is>
       </c>
-      <c r="BB21" s="2" t="inlineStr">
+      <c r="CK21" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1FXDcepDnUNk8tCbUUobEVOA-UEXk1CWz#list</t>
         </is>
       </c>
+      <c r="CL21" s="2" t="inlineStr"/>
+      <c r="CM21" s="2" t="inlineStr"/>
+      <c r="CN21" s="2" t="inlineStr"/>
+      <c r="CO21" s="2" t="inlineStr"/>
+      <c r="CP21" s="2" t="inlineStr"/>
+      <c r="CQ21" s="2" t="inlineStr"/>
+      <c r="CR21" s="2" t="inlineStr"/>
+      <c r="CS21" s="2" t="inlineStr"/>
+      <c r="CT21" s="2" t="inlineStr"/>
+      <c r="CU21" s="2" t="inlineStr"/>
+      <c r="CV21" s="2" t="inlineStr"/>
+      <c r="CW21" s="2" t="inlineStr"/>
+      <c r="CX21" s="2" t="inlineStr"/>
+      <c r="CY21" s="2" t="inlineStr"/>
+      <c r="CZ21" s="2" t="inlineStr"/>
+      <c r="DA21" s="2" t="inlineStr"/>
+      <c r="DB21" s="2" t="inlineStr"/>
+      <c r="DC21" s="2" t="inlineStr"/>
+      <c r="DD21" s="2" t="inlineStr"/>
+      <c r="DE21" s="2" t="inlineStr"/>
+      <c r="DF21" s="2" t="inlineStr"/>
+      <c r="DG21" s="2" t="inlineStr"/>
+      <c r="DH21" s="2" t="inlineStr"/>
+      <c r="DI21" s="2" t="inlineStr"/>
+      <c r="DJ21" s="2" t="inlineStr"/>
+      <c r="DK21" s="2" t="inlineStr"/>
+      <c r="DL21" s="2" t="inlineStr"/>
+      <c r="DM21" s="2" t="inlineStr"/>
+      <c r="DN21" s="2" t="inlineStr"/>
+      <c r="DO21" s="2" t="inlineStr"/>
+      <c r="DP21" s="2" t="inlineStr"/>
+      <c r="DQ21" s="2" t="inlineStr"/>
+      <c r="DR21" s="2" t="inlineStr"/>
+      <c r="DS21" s="2" t="inlineStr"/>
+      <c r="DT21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5223,61 +6973,131 @@
       </c>
       <c r="AH22" s="2" t="inlineStr"/>
       <c r="AI22" s="2" t="inlineStr"/>
-      <c r="AJ22" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=10NdJyBQCPWwrqI-44daeWT16JrVg0tuB#list</t>
-        </is>
-      </c>
-      <c r="AK22" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1RW0epWCaBqCy16REhMcWpeFLZNx77CAr#list</t>
-        </is>
-      </c>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
-      <c r="AN22" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1Ed37MZRYoTF9g1OR3pAHaVCyrbO_7jvx#list</t>
-        </is>
-      </c>
+      <c r="AN22" s="2" t="inlineStr"/>
       <c r="AO22" s="2" t="inlineStr"/>
       <c r="AP22" s="2" t="inlineStr"/>
-      <c r="AQ22" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1uWr3Pag7SSz2UYd419Z8qrihZnHbiEZX#list</t>
-        </is>
-      </c>
+      <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
       <c r="AS22" s="2" t="inlineStr"/>
-      <c r="AT22" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=121uAV2TgAYHUAWjUrbNJUEa-1XtWW20g#list</t>
-        </is>
-      </c>
+      <c r="AT22" s="2" t="inlineStr"/>
       <c r="AU22" s="2" t="inlineStr"/>
       <c r="AV22" s="2" t="inlineStr"/>
-      <c r="AW22" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1rA0vBoNr4xOOA-Vv4XFHmbTus0a8mZ-A#list</t>
-        </is>
-      </c>
+      <c r="AW22" s="2" t="inlineStr"/>
       <c r="AX22" s="2" t="inlineStr"/>
       <c r="AY22" s="2" t="inlineStr"/>
-      <c r="AZ22" s="2" t="inlineStr">
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr"/>
+      <c r="BC22" s="2" t="inlineStr"/>
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr"/>
+      <c r="BF22" s="2" t="inlineStr"/>
+      <c r="BG22" s="2" t="inlineStr"/>
+      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BM22" s="2" t="inlineStr"/>
+      <c r="BN22" s="2" t="inlineStr"/>
+      <c r="BO22" s="2" t="inlineStr"/>
+      <c r="BP22" s="2" t="inlineStr"/>
+      <c r="BQ22" s="2" t="inlineStr"/>
+      <c r="BR22" s="2" t="inlineStr"/>
+      <c r="BS22" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=10NdJyBQCPWwrqI-44daeWT16JrVg0tuB#list</t>
+        </is>
+      </c>
+      <c r="BT22" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RW0epWCaBqCy16REhMcWpeFLZNx77CAr#list</t>
+        </is>
+      </c>
+      <c r="BU22" s="2" t="inlineStr"/>
+      <c r="BV22" s="2" t="inlineStr"/>
+      <c r="BW22" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ed37MZRYoTF9g1OR3pAHaVCyrbO_7jvx#list</t>
+        </is>
+      </c>
+      <c r="BX22" s="2" t="inlineStr"/>
+      <c r="BY22" s="2" t="inlineStr"/>
+      <c r="BZ22" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1uWr3Pag7SSz2UYd419Z8qrihZnHbiEZX#list</t>
+        </is>
+      </c>
+      <c r="CA22" s="2" t="inlineStr"/>
+      <c r="CB22" s="2" t="inlineStr"/>
+      <c r="CC22" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=121uAV2TgAYHUAWjUrbNJUEa-1XtWW20g#list</t>
+        </is>
+      </c>
+      <c r="CD22" s="2" t="inlineStr"/>
+      <c r="CE22" s="2" t="inlineStr"/>
+      <c r="CF22" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rA0vBoNr4xOOA-Vv4XFHmbTus0a8mZ-A#list</t>
+        </is>
+      </c>
+      <c r="CG22" s="2" t="inlineStr"/>
+      <c r="CH22" s="2" t="inlineStr"/>
+      <c r="CI22" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1_SLHZB5C8TSE8SMw6rVEPE1xGe0t57-Y#list</t>
         </is>
       </c>
-      <c r="BA22" s="2" t="inlineStr">
+      <c r="CJ22" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Df78qGQQbTSoULKyzcsJuwuts8vk3Kf_#list</t>
         </is>
       </c>
-      <c r="BB22" s="2" t="inlineStr">
+      <c r="CK22" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Y57fYCKA4ONbGBZYNtSmEdW1iy1puKs_#list</t>
         </is>
       </c>
+      <c r="CL22" s="2" t="inlineStr"/>
+      <c r="CM22" s="2" t="inlineStr"/>
+      <c r="CN22" s="2" t="inlineStr"/>
+      <c r="CO22" s="2" t="inlineStr"/>
+      <c r="CP22" s="2" t="inlineStr"/>
+      <c r="CQ22" s="2" t="inlineStr"/>
+      <c r="CR22" s="2" t="inlineStr"/>
+      <c r="CS22" s="2" t="inlineStr"/>
+      <c r="CT22" s="2" t="inlineStr"/>
+      <c r="CU22" s="2" t="inlineStr"/>
+      <c r="CV22" s="2" t="inlineStr"/>
+      <c r="CW22" s="2" t="inlineStr"/>
+      <c r="CX22" s="2" t="inlineStr"/>
+      <c r="CY22" s="2" t="inlineStr"/>
+      <c r="CZ22" s="2" t="inlineStr"/>
+      <c r="DA22" s="2" t="inlineStr"/>
+      <c r="DB22" s="2" t="inlineStr"/>
+      <c r="DC22" s="2" t="inlineStr"/>
+      <c r="DD22" s="2" t="inlineStr"/>
+      <c r="DE22" s="2" t="inlineStr"/>
+      <c r="DF22" s="2" t="inlineStr"/>
+      <c r="DG22" s="2" t="inlineStr"/>
+      <c r="DH22" s="2" t="inlineStr"/>
+      <c r="DI22" s="2" t="inlineStr"/>
+      <c r="DJ22" s="2" t="inlineStr"/>
+      <c r="DK22" s="2" t="inlineStr"/>
+      <c r="DL22" s="2" t="inlineStr"/>
+      <c r="DM22" s="2" t="inlineStr"/>
+      <c r="DN22" s="2" t="inlineStr"/>
+      <c r="DO22" s="2" t="inlineStr"/>
+      <c r="DP22" s="2" t="inlineStr"/>
+      <c r="DQ22" s="2" t="inlineStr"/>
+      <c r="DR22" s="2" t="inlineStr"/>
+      <c r="DS22" s="2" t="inlineStr"/>
+      <c r="DT22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5435,61 +7255,131 @@
       </c>
       <c r="AH23" s="2" t="inlineStr"/>
       <c r="AI23" s="2" t="inlineStr"/>
-      <c r="AJ23" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1jNOW_e7NACb7NkojspitdynXjpe9VLxs#list</t>
-        </is>
-      </c>
-      <c r="AK23" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1NVBm1cdIFDpbXLhsS4apCKWGwAmENN78#list</t>
-        </is>
-      </c>
+      <c r="AJ23" s="2" t="inlineStr"/>
+      <c r="AK23" s="2" t="inlineStr"/>
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
-      <c r="AN23" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1PNuL6-5CWk8z_wxSxBpHxiI82qir3aJO#list</t>
-        </is>
-      </c>
+      <c r="AN23" s="2" t="inlineStr"/>
       <c r="AO23" s="2" t="inlineStr"/>
       <c r="AP23" s="2" t="inlineStr"/>
-      <c r="AQ23" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1oqhiaOywgohCIOmjBamCbSPK33Ikqtu1#list</t>
-        </is>
-      </c>
+      <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
       <c r="AS23" s="2" t="inlineStr"/>
-      <c r="AT23" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1a6nF3N3GpiRD3JirnWh_CV7n1M4ARzPN#list</t>
-        </is>
-      </c>
+      <c r="AT23" s="2" t="inlineStr"/>
       <c r="AU23" s="2" t="inlineStr"/>
       <c r="AV23" s="2" t="inlineStr"/>
-      <c r="AW23" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/embeddedfolderview?id=1qSLxW0xf6pyPLXjm5M5mXWJrswNTKihk#list</t>
-        </is>
-      </c>
+      <c r="AW23" s="2" t="inlineStr"/>
       <c r="AX23" s="2" t="inlineStr"/>
       <c r="AY23" s="2" t="inlineStr"/>
-      <c r="AZ23" s="2" t="inlineStr">
+      <c r="AZ23" s="2" t="inlineStr"/>
+      <c r="BA23" s="2" t="inlineStr"/>
+      <c r="BB23" s="2" t="inlineStr"/>
+      <c r="BC23" s="2" t="inlineStr"/>
+      <c r="BD23" s="2" t="inlineStr"/>
+      <c r="BE23" s="2" t="inlineStr"/>
+      <c r="BF23" s="2" t="inlineStr"/>
+      <c r="BG23" s="2" t="inlineStr"/>
+      <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BM23" s="2" t="inlineStr"/>
+      <c r="BN23" s="2" t="inlineStr"/>
+      <c r="BO23" s="2" t="inlineStr"/>
+      <c r="BP23" s="2" t="inlineStr"/>
+      <c r="BQ23" s="2" t="inlineStr"/>
+      <c r="BR23" s="2" t="inlineStr"/>
+      <c r="BS23" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jNOW_e7NACb7NkojspitdynXjpe9VLxs#list</t>
+        </is>
+      </c>
+      <c r="BT23" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NVBm1cdIFDpbXLhsS4apCKWGwAmENN78#list</t>
+        </is>
+      </c>
+      <c r="BU23" s="2" t="inlineStr"/>
+      <c r="BV23" s="2" t="inlineStr"/>
+      <c r="BW23" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1PNuL6-5CWk8z_wxSxBpHxiI82qir3aJO#list</t>
+        </is>
+      </c>
+      <c r="BX23" s="2" t="inlineStr"/>
+      <c r="BY23" s="2" t="inlineStr"/>
+      <c r="BZ23" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1oqhiaOywgohCIOmjBamCbSPK33Ikqtu1#list</t>
+        </is>
+      </c>
+      <c r="CA23" s="2" t="inlineStr"/>
+      <c r="CB23" s="2" t="inlineStr"/>
+      <c r="CC23" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1a6nF3N3GpiRD3JirnWh_CV7n1M4ARzPN#list</t>
+        </is>
+      </c>
+      <c r="CD23" s="2" t="inlineStr"/>
+      <c r="CE23" s="2" t="inlineStr"/>
+      <c r="CF23" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qSLxW0xf6pyPLXjm5M5mXWJrswNTKihk#list</t>
+        </is>
+      </c>
+      <c r="CG23" s="2" t="inlineStr"/>
+      <c r="CH23" s="2" t="inlineStr"/>
+      <c r="CI23" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aSZg3NsLq05rXgQ76kOO_-ZYoa_UA7Jr#list</t>
         </is>
       </c>
-      <c r="BA23" s="2" t="inlineStr">
+      <c r="CJ23" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1mpcSm1pDNxtCFfQM9AV_vyT2Kws3P-NR#list</t>
         </is>
       </c>
-      <c r="BB23" s="2" t="inlineStr">
+      <c r="CK23" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1gJapbkW7Nkq5e5SduBs4Wnh_ToT3H_nF#list</t>
         </is>
       </c>
+      <c r="CL23" s="2" t="inlineStr"/>
+      <c r="CM23" s="2" t="inlineStr"/>
+      <c r="CN23" s="2" t="inlineStr"/>
+      <c r="CO23" s="2" t="inlineStr"/>
+      <c r="CP23" s="2" t="inlineStr"/>
+      <c r="CQ23" s="2" t="inlineStr"/>
+      <c r="CR23" s="2" t="inlineStr"/>
+      <c r="CS23" s="2" t="inlineStr"/>
+      <c r="CT23" s="2" t="inlineStr"/>
+      <c r="CU23" s="2" t="inlineStr"/>
+      <c r="CV23" s="2" t="inlineStr"/>
+      <c r="CW23" s="2" t="inlineStr"/>
+      <c r="CX23" s="2" t="inlineStr"/>
+      <c r="CY23" s="2" t="inlineStr"/>
+      <c r="CZ23" s="2" t="inlineStr"/>
+      <c r="DA23" s="2" t="inlineStr"/>
+      <c r="DB23" s="2" t="inlineStr"/>
+      <c r="DC23" s="2" t="inlineStr"/>
+      <c r="DD23" s="2" t="inlineStr"/>
+      <c r="DE23" s="2" t="inlineStr"/>
+      <c r="DF23" s="2" t="inlineStr"/>
+      <c r="DG23" s="2" t="inlineStr"/>
+      <c r="DH23" s="2" t="inlineStr"/>
+      <c r="DI23" s="2" t="inlineStr"/>
+      <c r="DJ23" s="2" t="inlineStr"/>
+      <c r="DK23" s="2" t="inlineStr"/>
+      <c r="DL23" s="2" t="inlineStr"/>
+      <c r="DM23" s="2" t="inlineStr"/>
+      <c r="DN23" s="2" t="inlineStr"/>
+      <c r="DO23" s="2" t="inlineStr"/>
+      <c r="DP23" s="2" t="inlineStr"/>
+      <c r="DQ23" s="2" t="inlineStr"/>
+      <c r="DR23" s="2" t="inlineStr"/>
+      <c r="DS23" s="2" t="inlineStr"/>
+      <c r="DT23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5631,109 +7521,439 @@
       </c>
       <c r="AH24" s="2" t="inlineStr">
         <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AN24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AP24" s="2" t="inlineStr">
+        <is>
+          <t>Free State September</t>
+        </is>
+      </c>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AR24" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AT24" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="AU24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AV24" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AW24" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AX24" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AY24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="AZ24" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BA24" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BB24" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="BC24" s="2" t="inlineStr">
+        <is>
+          <t>Free State November</t>
+        </is>
+      </c>
+      <c r="BD24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="BE24" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="BF24" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="BG24" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="BH24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="BJ24" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BM24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BN24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BO24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BP24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BQ24" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=1BNLkoiz4Y9A8022YsDZfsiR4uCg_ov2h#list</t>
         </is>
       </c>
-      <c r="AI24" s="2" t="inlineStr">
+      <c r="BR24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Pl01GgnSLUWAuPCLi7EyMDRAHK1lDi_h#list</t>
         </is>
       </c>
-      <c r="AJ24" s="2" t="inlineStr">
+      <c r="BS24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1cBBsl0Ruznlv0_lk47vk5eOMWryNt9PX#list</t>
         </is>
       </c>
-      <c r="AK24" s="2" t="inlineStr">
+      <c r="BT24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1S7OJFW4ZNVjIw06db6mXcf0nfn2FzM1l#list</t>
         </is>
       </c>
-      <c r="AL24" s="2" t="inlineStr">
+      <c r="BU24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1i1ZVnFAIh11ZBOyjRqgDWLa6ndNVSVE2#list</t>
         </is>
       </c>
-      <c r="AM24" s="2" t="inlineStr">
+      <c r="BV24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=17rpijarHp65f3X7l7dZOuBvHkvr_s_r7#list</t>
         </is>
       </c>
-      <c r="AN24" s="2" t="inlineStr">
+      <c r="BW24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1_aoARbQ_hKvDcN0yyi8H8524aRMl7Aj9#list</t>
         </is>
       </c>
-      <c r="AO24" s="2" t="inlineStr">
+      <c r="BX24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1joFRnzqSdw5XUCk5-Lyiku6XogHef6lD#list</t>
         </is>
       </c>
-      <c r="AP24" s="2" t="inlineStr">
+      <c r="BY24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1T3VSiloSHJ-4o4VDHpxL-NL9VnUn586t#list</t>
         </is>
       </c>
-      <c r="AQ24" s="2" t="inlineStr">
+      <c r="BZ24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1xv_0fQVpjuwlEJJWi_KIDpKa-F2EWMnl#list</t>
         </is>
       </c>
-      <c r="AR24" s="2" t="inlineStr">
+      <c r="CA24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aVs0nEGai_TGFCpeNtydS-WP8VypVoxy#list</t>
         </is>
       </c>
-      <c r="AS24" s="2" t="inlineStr">
+      <c r="CB24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=19WDlVj25cKkfkgXXfuqrCKUT0Rcossdg#list</t>
         </is>
       </c>
-      <c r="AT24" s="2" t="inlineStr">
+      <c r="CC24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1QDeyL6f5o83z3X9rqvTQBE8-KPTp_J_J#list</t>
         </is>
       </c>
-      <c r="AU24" s="2" t="inlineStr">
+      <c r="CD24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1RhrBy107HdAeGseVHIrTjLukTLa1pE2x#list</t>
         </is>
       </c>
-      <c r="AV24" s="2" t="inlineStr">
+      <c r="CE24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1htlC9rZg7vFHEn9tGXPXml2Cnw6YO5Bj#list</t>
         </is>
       </c>
-      <c r="AW24" s="2" t="inlineStr">
+      <c r="CF24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1GfnJ_2ykfFG6roR7qITltWWWJ9LNUFw0#list</t>
         </is>
       </c>
-      <c r="AX24" s="2" t="inlineStr">
+      <c r="CG24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ELNDUk6_WZq59evq1aeSDx-P5mVSMGBF#list</t>
         </is>
       </c>
-      <c r="AY24" s="2" t="inlineStr">
+      <c r="CH24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1nSBiNWWJY1N6u8Rd5-VcTViCPXpW3KCi#list</t>
         </is>
       </c>
-      <c r="AZ24" s="2" t="inlineStr">
+      <c r="CI24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=14n4E1e49Av7ufRdHQnm2uHK13DU6lHsp#list</t>
         </is>
       </c>
-      <c r="BA24" s="2" t="inlineStr">
+      <c r="CJ24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=14Q1Cu7RObbqGX-6Nb2L9aZ-GoLpP_VP7#list</t>
         </is>
       </c>
-      <c r="BB24" s="2" t="inlineStr">
+      <c r="CK24" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bbNG_n4KkfAhnHPNih4ICq79NH_TyTd6#list</t>
         </is>
       </c>
+      <c r="CL24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_n3g-ENm1aeWSWPJ56wOsXF5djmsJvPx#list</t>
+        </is>
+      </c>
+      <c r="CM24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QUqEopYeYksT8rEgYDamhrdVKs_PqfqG#list</t>
+        </is>
+      </c>
+      <c r="CN24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=172GOd40ybZty2s9qMPVxPbY1OEfSPY09#list</t>
+        </is>
+      </c>
+      <c r="CO24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1afND2fyUXQv-MgNi3f0FSkP-doudCOio#list</t>
+        </is>
+      </c>
+      <c r="CP24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OxeiTpPqufzDXVS9Ig0FR3aHiYsQpIpF#list</t>
+        </is>
+      </c>
+      <c r="CQ24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1AMyi7w8rJVDK4aRNgdEvpwk4ku-PWn5B#list</t>
+        </is>
+      </c>
+      <c r="CR24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1v9czssjA1G5eB2EA-g-KEUv379pEW6Hc#list</t>
+        </is>
+      </c>
+      <c r="CS24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16utpmapUrzzWyXlbwgT5mx3qUveAG7Kk#list</t>
+        </is>
+      </c>
+      <c r="CT24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Y7cfG8QnjoxiO4mOPgkptgGi4XvF9GK1#list</t>
+        </is>
+      </c>
+      <c r="CU24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iNj7jSaW9G4Ir3BSvPLH_eB2cvI-dpFX#list</t>
+        </is>
+      </c>
+      <c r="CV24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YaXGedL1zhMdwbvO2g2e10zCs5W8_LWH#list</t>
+        </is>
+      </c>
+      <c r="CW24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1GUg0_80DgW2Zed6DFygkRr7soPhsT_ND#list</t>
+        </is>
+      </c>
+      <c r="CX24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yTPBFVRbK6QN-YYy-zufjJ1fJrD_HZFq#list</t>
+        </is>
+      </c>
+      <c r="CY24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vFw6BjGRlkCqse1bTGaYAxnaiL7TJfTg#list</t>
+        </is>
+      </c>
+      <c r="CZ24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1e1l_WJZqlu_xmMNHPXQOySfxCDumqL_N#list</t>
+        </is>
+      </c>
+      <c r="DA24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XJk-U-l11QzJIz0p8TI07_km1UqYLRBB#list</t>
+        </is>
+      </c>
+      <c r="DB24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15xhMgtY0KTBAsfnyOf3iEf3wKRsZF0ZU#list</t>
+        </is>
+      </c>
+      <c r="DC24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iEObK9RdGXhg1ah8C1yG6RshBfvXOK_c#list</t>
+        </is>
+      </c>
+      <c r="DD24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UqGMQASSnL1-fx3IDIOUfhdpbGWlBvGH#list</t>
+        </is>
+      </c>
+      <c r="DE24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-pi7dnC-I-3s1cjFchtA5sq6qUrBB-1B#list</t>
+        </is>
+      </c>
+      <c r="DF24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1T_qQGp7UhCjYx_0KAhuPX8AAqXLt0Bd3#list</t>
+        </is>
+      </c>
+      <c r="DG24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1WryZmJhMDm81PxtR0wOUJm1TZlJ7938D#list</t>
+        </is>
+      </c>
+      <c r="DH24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YtgARypSH04yz6kepL1uVaKy6aHpPkqf#list</t>
+        </is>
+      </c>
+      <c r="DI24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1EHHF4wym6NCyBFvvL01gJx4Xje9nnp3P#list</t>
+        </is>
+      </c>
+      <c r="DJ24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UySvU9qiZgc7CA-T_lMCCo3_MkMhEa1u#list</t>
+        </is>
+      </c>
+      <c r="DK24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1R7gXff80AxgmWcQwN-b6OmhoaPS6Ifx-#list</t>
+        </is>
+      </c>
+      <c r="DL24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1x2QEGtaufcxggr0Lmqw1nPTCRoJHR_Bk#list</t>
+        </is>
+      </c>
+      <c r="DM24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1q7OwDqIyPqZUcaAjPiDrxmkk8bMul_QX#list</t>
+        </is>
+      </c>
+      <c r="DN24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-M0xG-2lQIEN98HE_i4u_ty4y_BLagB0#list</t>
+        </is>
+      </c>
+      <c r="DO24" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_u7gK2bXNEwFh9ZxIPUsQ11U9GzIJmoi#list</t>
+        </is>
+      </c>
+      <c r="DP24" s="2" t="inlineStr"/>
+      <c r="DQ24" s="2" t="inlineStr"/>
+      <c r="DR24" s="2" t="inlineStr"/>
+      <c r="DS24" s="2" t="inlineStr"/>
+      <c r="DT24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5875,109 +8095,419 @@
       </c>
       <c r="AH25" s="2" t="inlineStr">
         <is>
+          <t>North West September</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AM25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="AN25" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AP25" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AQ25" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga March</t>
+        </is>
+      </c>
+      <c r="AR25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AS25" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="AT25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AU25" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AV25" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="AW25" s="2" t="inlineStr">
+        <is>
+          <t>National Term 3</t>
+        </is>
+      </c>
+      <c r="AX25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AY25" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AZ25" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BA25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="BB25" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="BC25" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BD25" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BE25" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="BF25" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="BG25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BM25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BN25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BO25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BP25" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BQ25" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ILSbEx09OrugKOSZ9S2LOUqUDxl6w69l#list</t>
         </is>
       </c>
-      <c r="AI25" s="2" t="inlineStr">
+      <c r="BR25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1vfvWqQ9kh9jLIElzGt08tiT9riSPuAE1#list</t>
         </is>
       </c>
-      <c r="AJ25" s="2" t="inlineStr">
+      <c r="BS25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bG6T3uJH9o_IX7lrPUUU1znYLD94XkNw#list</t>
         </is>
       </c>
-      <c r="AK25" s="2" t="inlineStr">
+      <c r="BT25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1wTqRW_9GIqsEkOGJggD7ejqfWUTQgh2z#list</t>
         </is>
       </c>
-      <c r="AL25" s="2" t="inlineStr">
+      <c r="BU25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1VPmyBaRjaJxupF8Jmrmax3ha8XpocVsI#list</t>
         </is>
       </c>
-      <c r="AM25" s="2" t="inlineStr">
+      <c r="BV25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=18UM5OUnEBTV8hJaGhi_ETKn2c6Uv00vv#list</t>
         </is>
       </c>
-      <c r="AN25" s="2" t="inlineStr">
+      <c r="BW25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ngCu9JSUO-XMWzQMYtvYec89BfLHaaMY#list</t>
         </is>
       </c>
-      <c r="AO25" s="2" t="inlineStr">
+      <c r="BX25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1MsG6nnZK_YDWJPDjWl66i_Sk49WxKy19#list</t>
         </is>
       </c>
-      <c r="AP25" s="2" t="inlineStr">
+      <c r="BY25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1kxLG1ZQHPs6Dck_PK_FffuyGCsLB1CB9#list</t>
         </is>
       </c>
-      <c r="AQ25" s="2" t="inlineStr">
+      <c r="BZ25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=11KTHokdznKnru8175cC7yOKDl_dqPDJK#list</t>
         </is>
       </c>
-      <c r="AR25" s="2" t="inlineStr">
+      <c r="CA25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Qx2i9FrEq6BFeYtTrnL82CFbadIpOcwb#list</t>
         </is>
       </c>
-      <c r="AS25" s="2" t="inlineStr">
+      <c r="CB25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1uHb1Evf3rMZpMk_OESN7G8oHfUfx5M-0#list</t>
         </is>
       </c>
-      <c r="AT25" s="2" t="inlineStr">
+      <c r="CC25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1nhb-iZ8DUoi8AxP-EgCsF1OBTZizbKVE#list</t>
         </is>
       </c>
-      <c r="AU25" s="2" t="inlineStr">
+      <c r="CD25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1fqEL6xstybEHtL-gg5doGOYyX-87_WuI#list</t>
         </is>
       </c>
-      <c r="AV25" s="2" t="inlineStr">
+      <c r="CE25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1xUILWpltl1210jknhc2pHrVuBad1wyif#list</t>
         </is>
       </c>
-      <c r="AW25" s="2" t="inlineStr">
+      <c r="CF25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=11stNj61r_em2IAMN9q_RcUpL1al642nN#list</t>
         </is>
       </c>
-      <c r="AX25" s="2" t="inlineStr">
+      <c r="CG25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1O2bqUFV4Rf97xyoF9foz3PV4wKRKWf8A#list</t>
         </is>
       </c>
-      <c r="AY25" s="2" t="inlineStr">
+      <c r="CH25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1G__IB1tjqgQ4G8fWcfh7zK9iy2-W-jOv#list</t>
         </is>
       </c>
-      <c r="AZ25" s="2" t="inlineStr">
+      <c r="CI25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1NhvWZKrYkh0eEIr0oqC8hXsCmmWaVo1m#list</t>
         </is>
       </c>
-      <c r="BA25" s="2" t="inlineStr">
+      <c r="CJ25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1FxUFEvbDYevRRaWsp2n0GUMXMd-8Pdxd#list</t>
         </is>
       </c>
-      <c r="BB25" s="2" t="inlineStr">
+      <c r="CK25" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1VlnTDpsD68CkvfSGlkWH7JICjRRKEVy0#list</t>
         </is>
       </c>
+      <c r="CL25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14uyWirLI7X_Zz-1vgf8KaYw38ObCsIf6#list</t>
+        </is>
+      </c>
+      <c r="CM25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15zBq7evNUtMGh9T6Nvi43EXTaOiePyvf#list</t>
+        </is>
+      </c>
+      <c r="CN25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IOLntE-Fo68YEyHEsCIJ_KcEnpskdQV2#list</t>
+        </is>
+      </c>
+      <c r="CO25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XeGESgnRrUmhP8J4vfNudPTO_RBLXQ08#list</t>
+        </is>
+      </c>
+      <c r="CP25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1LCnDWDg8HDBrx7nr3xOYsO5FFcFtCH2r#list</t>
+        </is>
+      </c>
+      <c r="CQ25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FAkTGYzmapUnuLo37GyS9MxbRmTVcoSu#list</t>
+        </is>
+      </c>
+      <c r="CR25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1O2YZZ-LTn78rQd_NMYZoGtFAC_G6wQIn#list</t>
+        </is>
+      </c>
+      <c r="CS25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fakh80UZPjlksgyznkti3Zlo-zW8OxAl#list</t>
+        </is>
+      </c>
+      <c r="CT25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iOoynXyvv1ArDLMWAbha6lKkmDcqtPgQ#list</t>
+        </is>
+      </c>
+      <c r="CU25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vP59zgJBNRCrSbiqEXHqjG4IMm4mMZSu#list</t>
+        </is>
+      </c>
+      <c r="CV25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1oQYJUeE4i6kV9pCOek_vhlcq-cB60fsz#list</t>
+        </is>
+      </c>
+      <c r="CW25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Tgr3A5aPiJEu6HBugLa3PM93Gkym1h5K#list</t>
+        </is>
+      </c>
+      <c r="CX25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nBZ8jqJpSUnB-Awmnu1ZnJgSqqxmk-qz#list</t>
+        </is>
+      </c>
+      <c r="CY25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=187XuXC0NK6zImuIZbHpg63VWYyChat0a#list</t>
+        </is>
+      </c>
+      <c r="CZ25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1sTstpxeQ8OJSyf5fqK_Smc0onEak9un_#list</t>
+        </is>
+      </c>
+      <c r="DA25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pnY18aB96YP_Cb6l7-rgcaJ3ujRLqweZ#list</t>
+        </is>
+      </c>
+      <c r="DB25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qsLyJs4zup4w3lbNRYi4qpinDjpsWxOm#list</t>
+        </is>
+      </c>
+      <c r="DC25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18UCrZm0pWlRTCx4MMQ83WGneQ6L-EZUf#list</t>
+        </is>
+      </c>
+      <c r="DD25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IboP2sv9T4IaSkPdUGbQVjLWlo6pbrQy#list</t>
+        </is>
+      </c>
+      <c r="DE25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1tqQ_0-0nWBVWrnk0_v--fyDFOY3ChX7z#list</t>
+        </is>
+      </c>
+      <c r="DF25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fXS_MlI1L99j7G8Mf1MXai0RMlJ-ehLk#list</t>
+        </is>
+      </c>
+      <c r="DG25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19tZZzu8_sp0KY5jwLAf9zMA6ojiXXFV9#list</t>
+        </is>
+      </c>
+      <c r="DH25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OQAaU2CBt6w9bghG18vtzFST9-Ben3VN#list</t>
+        </is>
+      </c>
+      <c r="DI25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fyyVnYlNLCRWLeWfrCZOclgjlw-DDHwa#list</t>
+        </is>
+      </c>
+      <c r="DJ25" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1d_VKaHoHR4DttEFPjb90JchXSHMjPTo5#list</t>
+        </is>
+      </c>
+      <c r="DK25" s="2" t="inlineStr"/>
+      <c r="DL25" s="2" t="inlineStr"/>
+      <c r="DM25" s="2" t="inlineStr"/>
+      <c r="DN25" s="2" t="inlineStr"/>
+      <c r="DO25" s="2" t="inlineStr"/>
+      <c r="DP25" s="2" t="inlineStr"/>
+      <c r="DQ25" s="2" t="inlineStr"/>
+      <c r="DR25" s="2" t="inlineStr"/>
+      <c r="DS25" s="2" t="inlineStr"/>
+      <c r="DT25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6119,109 +8649,339 @@
       </c>
       <c r="AH26" s="2" t="inlineStr">
         <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AN26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AQ26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AR26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AS26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AT26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AU26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AV26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AW26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AX26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AY26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AZ26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BA26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BB26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BC26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BD26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BM26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BN26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BO26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BP26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BQ26" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=1t7Ruy_7LSeHFm1iDklpBHBenJUcI-ysX#list</t>
         </is>
       </c>
-      <c r="AI26" s="2" t="inlineStr">
+      <c r="BR26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1qbz1G0h9MdqfGDdLfRs_hFvg_Xfzrpjk#list</t>
         </is>
       </c>
-      <c r="AJ26" s="2" t="inlineStr">
+      <c r="BS26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1QDz1Y9zipyiKaV72nluOvu2xsR56DM_-#list</t>
         </is>
       </c>
-      <c r="AK26" s="2" t="inlineStr">
+      <c r="BT26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1qnWLa7Fs7N1X9LpHtvOb-L-rPYR185IE#list</t>
         </is>
       </c>
-      <c r="AL26" s="2" t="inlineStr">
+      <c r="BU26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1e_B7ZMRsNP-DLJG7f9SaH28rK9IMMq9b#list</t>
         </is>
       </c>
-      <c r="AM26" s="2" t="inlineStr">
+      <c r="BV26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1-e_OWGH4UZGHkR8MPxIghDLuZ4HfTEZM#list</t>
         </is>
       </c>
-      <c r="AN26" s="2" t="inlineStr">
+      <c r="BW26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1VipE7qp9Co_xbzl2TwaGWrxB-XCopXMI#list</t>
         </is>
       </c>
-      <c r="AO26" s="2" t="inlineStr">
+      <c r="BX26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=14UN3Lu7emOciPOyc11af2V2S6O2EqPLi#list</t>
         </is>
       </c>
-      <c r="AP26" s="2" t="inlineStr">
+      <c r="BY26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1SREIqdL8aqSv1sIJxPgOuOidM4sdNbd8#list</t>
         </is>
       </c>
-      <c r="AQ26" s="2" t="inlineStr">
+      <c r="BZ26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1pgWD3I0_0I6pOcGIp41tPj0ciSzUMwYg#list</t>
         </is>
       </c>
-      <c r="AR26" s="2" t="inlineStr">
+      <c r="CA26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1KipvINHOvclShh6hP3qr0xUaj4tJU8Z2#list</t>
         </is>
       </c>
-      <c r="AS26" s="2" t="inlineStr">
+      <c r="CB26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1HTg7yrkprpKa6d4kPKdSH8g7WVt-tCo1#list</t>
         </is>
       </c>
-      <c r="AT26" s="2" t="inlineStr">
+      <c r="CC26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1qH8abS3puOKSdD46843dbViMM-ZhF7EI#list</t>
         </is>
       </c>
-      <c r="AU26" s="2" t="inlineStr">
+      <c r="CD26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1wnCa1gI8g43fjBEZGVEPWGj1_t-9mirR#list</t>
         </is>
       </c>
-      <c r="AV26" s="2" t="inlineStr">
+      <c r="CE26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1nPv4b-a7xTNSK6oSfTd9bcOz6QZcvpd0#list</t>
         </is>
       </c>
-      <c r="AW26" s="2" t="inlineStr">
+      <c r="CF26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=16NWHeXez-ZabNAzhHatykycmacYjnxXO#list</t>
         </is>
       </c>
-      <c r="AX26" s="2" t="inlineStr">
+      <c r="CG26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1rztyyjQO6_tigvAT5ye4UghckmawFt6H#list</t>
         </is>
       </c>
-      <c r="AY26" s="2" t="inlineStr">
+      <c r="CH26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1mIZ8WdvR0_1uLZJKHEmdeVdtRECGwCzD#list</t>
         </is>
       </c>
-      <c r="AZ26" s="2" t="inlineStr">
+      <c r="CI26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=119xYuPQCAQ7AZSsEdF9wpHtcBOttPDzG#list</t>
         </is>
       </c>
-      <c r="BA26" s="2" t="inlineStr">
+      <c r="CJ26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bkvyxXo6VGR8uZqoK30_T6c5oDcY4nJd#list</t>
         </is>
       </c>
-      <c r="BB26" s="2" t="inlineStr">
+      <c r="CK26" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1acBTs3bYw6MORHp_JPvD9rmqP-y7z2Mn#list</t>
         </is>
       </c>
+      <c r="CL26" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1LtHbMu6tcExQXLfMWGmy2ufN30Yi1cYC#list</t>
+        </is>
+      </c>
+      <c r="CM26" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1uOxAjb0LfVtwmk_AK7t2yQluzMeOk9bo#list</t>
+        </is>
+      </c>
+      <c r="CN26" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1lD6lQuLbM6er2hJCvDMTe5oE7Nv4EmFh#list</t>
+        </is>
+      </c>
+      <c r="CO26" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14cm3YrMA1A1ZaLq2OSW34sD3xquWBzbR#list</t>
+        </is>
+      </c>
+      <c r="CP26" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1U_fEp9Zd-C9ae3OMT_5sDs_e3iJ0o2cH#list</t>
+        </is>
+      </c>
+      <c r="CQ26" s="2" t="inlineStr"/>
+      <c r="CR26" s="2" t="inlineStr"/>
+      <c r="CS26" s="2" t="inlineStr"/>
+      <c r="CT26" s="2" t="inlineStr"/>
+      <c r="CU26" s="2" t="inlineStr"/>
+      <c r="CV26" s="2" t="inlineStr"/>
+      <c r="CW26" s="2" t="inlineStr"/>
+      <c r="CX26" s="2" t="inlineStr"/>
+      <c r="CY26" s="2" t="inlineStr"/>
+      <c r="CZ26" s="2" t="inlineStr"/>
+      <c r="DA26" s="2" t="inlineStr"/>
+      <c r="DB26" s="2" t="inlineStr"/>
+      <c r="DC26" s="2" t="inlineStr"/>
+      <c r="DD26" s="2" t="inlineStr"/>
+      <c r="DE26" s="2" t="inlineStr"/>
+      <c r="DF26" s="2" t="inlineStr"/>
+      <c r="DG26" s="2" t="inlineStr"/>
+      <c r="DH26" s="2" t="inlineStr"/>
+      <c r="DI26" s="2" t="inlineStr"/>
+      <c r="DJ26" s="2" t="inlineStr"/>
+      <c r="DK26" s="2" t="inlineStr"/>
+      <c r="DL26" s="2" t="inlineStr"/>
+      <c r="DM26" s="2" t="inlineStr"/>
+      <c r="DN26" s="2" t="inlineStr"/>
+      <c r="DO26" s="2" t="inlineStr"/>
+      <c r="DP26" s="2" t="inlineStr"/>
+      <c r="DQ26" s="2" t="inlineStr"/>
+      <c r="DR26" s="2" t="inlineStr"/>
+      <c r="DS26" s="2" t="inlineStr"/>
+      <c r="DT26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6363,109 +9123,343 @@
       </c>
       <c r="AH27" s="2" t="inlineStr">
         <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AN27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AQ27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AR27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AS27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AT27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AU27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AV27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AW27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AX27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AY27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AZ27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BA27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BB27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BC27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BD27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BM27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BN27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BO27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BP27" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BQ27" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=1rVhKPh9JIG1EaVgmCtuCCYt5c3U8gw_y#list</t>
         </is>
       </c>
-      <c r="AI27" s="2" t="inlineStr">
+      <c r="BR27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Tv5AbmSYXlxpTXAK9_Rcfh3TZhJDMMB8#list</t>
         </is>
       </c>
-      <c r="AJ27" s="2" t="inlineStr">
+      <c r="BS27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ep8XnMIOTqd2jpzoOjDfDdRsCqzH4sa8#list</t>
         </is>
       </c>
-      <c r="AK27" s="2" t="inlineStr">
+      <c r="BT27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1qguq6ceoejLWXrS4roP-J8jFjBgkk7nY#list</t>
         </is>
       </c>
-      <c r="AL27" s="2" t="inlineStr">
+      <c r="BU27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1TmzQj6rs8s-t4nE57ediVp7Rbd2wOBtC#list</t>
         </is>
       </c>
-      <c r="AM27" s="2" t="inlineStr">
+      <c r="BV27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1doLBqu6nUGKcZ_j5NfK2aZF8jDDwUorH#list</t>
         </is>
       </c>
-      <c r="AN27" s="2" t="inlineStr">
+      <c r="BW27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1HHwwfjhLbF_sq_lgUDDeM97RWz1i-x1I#list</t>
         </is>
       </c>
-      <c r="AO27" s="2" t="inlineStr">
+      <c r="BX27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1P1f7oEZPrgrLhBULvbAWWwi96zAFh1gW#list</t>
         </is>
       </c>
-      <c r="AP27" s="2" t="inlineStr">
+      <c r="BY27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=16nq9u1ikdKi9zhSuM2OFyt3yLWxaCIRo#list</t>
         </is>
       </c>
-      <c r="AQ27" s="2" t="inlineStr">
+      <c r="BZ27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1YajEZmx7g9NAMdjyIvcwzcOwouj5Alms#list</t>
         </is>
       </c>
-      <c r="AR27" s="2" t="inlineStr">
+      <c r="CA27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=11bZiXQgbMt0mei3ARLjUYHzTqsK_mcgu#list</t>
         </is>
       </c>
-      <c r="AS27" s="2" t="inlineStr">
+      <c r="CB27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1JBt2A621mkvP5Nh1z_gaDKGsRoSjHZI-#list</t>
         </is>
       </c>
-      <c r="AT27" s="2" t="inlineStr">
+      <c r="CC27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1iisItRY-NE6AP_fqMALsjUhZwhb6v17B#list</t>
         </is>
       </c>
-      <c r="AU27" s="2" t="inlineStr">
+      <c r="CD27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1MAD_CoecHpq-oUOHxlaWChCDpOhM0vey#list</t>
         </is>
       </c>
-      <c r="AV27" s="2" t="inlineStr">
+      <c r="CE27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1tDwySF4NOSo4XUtzcq2jl40scZDo4f8M#list</t>
         </is>
       </c>
-      <c r="AW27" s="2" t="inlineStr">
+      <c r="CF27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1_AFXqXfH0nNOShqyWO0a0ZixeHNZPtnj#list</t>
         </is>
       </c>
-      <c r="AX27" s="2" t="inlineStr">
+      <c r="CG27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=18M3CHtEXnn0iSUmMVgmVN3hKQffsRUTs#list</t>
         </is>
       </c>
-      <c r="AY27" s="2" t="inlineStr">
+      <c r="CH27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1U3W5-JAhWnkltblYdK8kiXZJ2JCe-2Ci#list</t>
         </is>
       </c>
-      <c r="AZ27" s="2" t="inlineStr">
+      <c r="CI27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bXxzvgCMXaAJax1kVe_UNFanUw7fdt92#list</t>
         </is>
       </c>
-      <c r="BA27" s="2" t="inlineStr">
+      <c r="CJ27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Vs2zF2by0Wvf122qP-ZnwJSqfWdC50cG#list</t>
         </is>
       </c>
-      <c r="BB27" s="2" t="inlineStr">
+      <c r="CK27" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1pPfh4Oj1MUGuiG9hg4HeSvzplNfyf_kr#list</t>
         </is>
       </c>
+      <c r="CL27" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1TNEFev3ZHkPt1aqzBDRYpw0nrvQ6adr7#list</t>
+        </is>
+      </c>
+      <c r="CM27" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UYEKVoQ0Yw56OEGXKgNW0sqK2URtgwhI#list</t>
+        </is>
+      </c>
+      <c r="CN27" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_bS0ZdtaPpaugvraajHyBlRoB87WWcL-#list</t>
+        </is>
+      </c>
+      <c r="CO27" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rH4brsaHb5stLeRhPxSmFfjNO1F8Ev7V#list</t>
+        </is>
+      </c>
+      <c r="CP27" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1P9aBkXvNeNeVaC2JSmHy1zzu9PNsgim_#list</t>
+        </is>
+      </c>
+      <c r="CQ27" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1hBxXgGABY-Tuaonq-1GgwOCAHtbatdVG#list</t>
+        </is>
+      </c>
+      <c r="CR27" s="2" t="inlineStr"/>
+      <c r="CS27" s="2" t="inlineStr"/>
+      <c r="CT27" s="2" t="inlineStr"/>
+      <c r="CU27" s="2" t="inlineStr"/>
+      <c r="CV27" s="2" t="inlineStr"/>
+      <c r="CW27" s="2" t="inlineStr"/>
+      <c r="CX27" s="2" t="inlineStr"/>
+      <c r="CY27" s="2" t="inlineStr"/>
+      <c r="CZ27" s="2" t="inlineStr"/>
+      <c r="DA27" s="2" t="inlineStr"/>
+      <c r="DB27" s="2" t="inlineStr"/>
+      <c r="DC27" s="2" t="inlineStr"/>
+      <c r="DD27" s="2" t="inlineStr"/>
+      <c r="DE27" s="2" t="inlineStr"/>
+      <c r="DF27" s="2" t="inlineStr"/>
+      <c r="DG27" s="2" t="inlineStr"/>
+      <c r="DH27" s="2" t="inlineStr"/>
+      <c r="DI27" s="2" t="inlineStr"/>
+      <c r="DJ27" s="2" t="inlineStr"/>
+      <c r="DK27" s="2" t="inlineStr"/>
+      <c r="DL27" s="2" t="inlineStr"/>
+      <c r="DM27" s="2" t="inlineStr"/>
+      <c r="DN27" s="2" t="inlineStr"/>
+      <c r="DO27" s="2" t="inlineStr"/>
+      <c r="DP27" s="2" t="inlineStr"/>
+      <c r="DQ27" s="2" t="inlineStr"/>
+      <c r="DR27" s="2" t="inlineStr"/>
+      <c r="DS27" s="2" t="inlineStr"/>
+      <c r="DT27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6607,53 +9601,263 @@
       </c>
       <c r="AH28" s="2" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AM28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AN28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AP28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AR28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AS28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AT28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AU28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AV28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AW28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AX28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AY28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AZ28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BA28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BB28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BC28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BD28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BM28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BN28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BO28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BP28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BQ28" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=1IoLqN1Y9IEwEyBaRMOtAteKRrrGU6VOP#list</t>
         </is>
       </c>
-      <c r="AI28" s="2" t="inlineStr">
+      <c r="BR28" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1krSY13SKemdVYxdZxv4aJDIo-buBqhnO#list</t>
         </is>
       </c>
-      <c r="AJ28" s="2" t="inlineStr">
+      <c r="BS28" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1c4b0N8tBAeawhWPg6W9ipJcIMC9apF_E#list</t>
         </is>
       </c>
-      <c r="AK28" s="2" t="inlineStr">
+      <c r="BT28" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1V_K7VDMPVxffRgoWee0ia98WmkKz3Ilc#list</t>
         </is>
       </c>
-      <c r="AL28" s="2" t="inlineStr">
+      <c r="BU28" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=14QfvAvkaJYnsi6mLgpeDgIle_MU4AVBN#list</t>
         </is>
       </c>
-      <c r="AM28" s="2" t="inlineStr">
+      <c r="BV28" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=16pgL6MWFoEJD0FI_QW5sD9NetbL9AyoZ#list</t>
         </is>
       </c>
-      <c r="AN28" s="2" t="inlineStr">
+      <c r="BW28" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1AAAnP7nKq7OfMZi0K2Hg77P0BoJeTCYY#list</t>
         </is>
       </c>
-      <c r="AO28" s="2" t="inlineStr"/>
-      <c r="AP28" s="2" t="inlineStr"/>
-      <c r="AQ28" s="2" t="inlineStr"/>
-      <c r="AR28" s="2" t="inlineStr"/>
-      <c r="AS28" s="2" t="inlineStr"/>
-      <c r="AT28" s="2" t="inlineStr"/>
-      <c r="AU28" s="2" t="inlineStr"/>
-      <c r="AV28" s="2" t="inlineStr"/>
-      <c r="AW28" s="2" t="inlineStr"/>
-      <c r="AX28" s="2" t="inlineStr"/>
-      <c r="AY28" s="2" t="inlineStr"/>
-      <c r="AZ28" s="2" t="inlineStr"/>
-      <c r="BA28" s="2" t="inlineStr"/>
-      <c r="BB28" s="2" t="inlineStr"/>
+      <c r="BX28" s="2" t="inlineStr"/>
+      <c r="BY28" s="2" t="inlineStr"/>
+      <c r="BZ28" s="2" t="inlineStr"/>
+      <c r="CA28" s="2" t="inlineStr"/>
+      <c r="CB28" s="2" t="inlineStr"/>
+      <c r="CC28" s="2" t="inlineStr"/>
+      <c r="CD28" s="2" t="inlineStr"/>
+      <c r="CE28" s="2" t="inlineStr"/>
+      <c r="CF28" s="2" t="inlineStr"/>
+      <c r="CG28" s="2" t="inlineStr"/>
+      <c r="CH28" s="2" t="inlineStr"/>
+      <c r="CI28" s="2" t="inlineStr"/>
+      <c r="CJ28" s="2" t="inlineStr"/>
+      <c r="CK28" s="2" t="inlineStr"/>
+      <c r="CL28" s="2" t="inlineStr"/>
+      <c r="CM28" s="2" t="inlineStr"/>
+      <c r="CN28" s="2" t="inlineStr"/>
+      <c r="CO28" s="2" t="inlineStr"/>
+      <c r="CP28" s="2" t="inlineStr"/>
+      <c r="CQ28" s="2" t="inlineStr"/>
+      <c r="CR28" s="2" t="inlineStr"/>
+      <c r="CS28" s="2" t="inlineStr"/>
+      <c r="CT28" s="2" t="inlineStr"/>
+      <c r="CU28" s="2" t="inlineStr"/>
+      <c r="CV28" s="2" t="inlineStr"/>
+      <c r="CW28" s="2" t="inlineStr"/>
+      <c r="CX28" s="2" t="inlineStr"/>
+      <c r="CY28" s="2" t="inlineStr"/>
+      <c r="CZ28" s="2" t="inlineStr"/>
+      <c r="DA28" s="2" t="inlineStr"/>
+      <c r="DB28" s="2" t="inlineStr"/>
+      <c r="DC28" s="2" t="inlineStr"/>
+      <c r="DD28" s="2" t="inlineStr"/>
+      <c r="DE28" s="2" t="inlineStr"/>
+      <c r="DF28" s="2" t="inlineStr"/>
+      <c r="DG28" s="2" t="inlineStr"/>
+      <c r="DH28" s="2" t="inlineStr"/>
+      <c r="DI28" s="2" t="inlineStr"/>
+      <c r="DJ28" s="2" t="inlineStr"/>
+      <c r="DK28" s="2" t="inlineStr"/>
+      <c r="DL28" s="2" t="inlineStr"/>
+      <c r="DM28" s="2" t="inlineStr"/>
+      <c r="DN28" s="2" t="inlineStr"/>
+      <c r="DO28" s="2" t="inlineStr"/>
+      <c r="DP28" s="2" t="inlineStr"/>
+      <c r="DQ28" s="2" t="inlineStr"/>
+      <c r="DR28" s="2" t="inlineStr"/>
+      <c r="DS28" s="2" t="inlineStr"/>
+      <c r="DT28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -6795,109 +9999,359 @@
       </c>
       <c r="AH29" s="2" t="inlineStr">
         <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="AN29" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AP29" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="AR29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AT29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AU29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AV29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AW29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AX29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AY29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AZ29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BA29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BB29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BC29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BD29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BM29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BN29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BO29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BP29" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BQ29" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=19S8yyHcoaJnztP1HPXh8C3XjR2ybGg0s#list</t>
         </is>
       </c>
-      <c r="AI29" s="2" t="inlineStr">
+      <c r="BR29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ovtEhoOY3aKN-ihXM6u2ty5NePoiD6rZ#list</t>
         </is>
       </c>
-      <c r="AJ29" s="2" t="inlineStr">
+      <c r="BS29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1v0GziMYR4Zjnh_2xtQg77ZcPQsyGqwHw#list</t>
         </is>
       </c>
-      <c r="AK29" s="2" t="inlineStr">
+      <c r="BT29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1E2uEA5S6FnA9c0eKwAXhkuSrmPrF-284#list</t>
         </is>
       </c>
-      <c r="AL29" s="2" t="inlineStr">
+      <c r="BU29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1bn1Q-yk2_7au-n4cU3pPFAlkYw4nYN_F#list</t>
         </is>
       </c>
-      <c r="AM29" s="2" t="inlineStr">
+      <c r="BV29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1a2OhFk85yqvmfpw5oMFcMP5MnQNMEIVM#list</t>
         </is>
       </c>
-      <c r="AN29" s="2" t="inlineStr">
+      <c r="BW29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1IQOGeZ-fgl9U3lY4NAa2i-1-MJOWCy6e#list</t>
         </is>
       </c>
-      <c r="AO29" s="2" t="inlineStr">
+      <c r="BX29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1WXCJr9ePJ2erc4qpskbdufsOwBlQDHDM#list</t>
         </is>
       </c>
-      <c r="AP29" s="2" t="inlineStr">
+      <c r="BY29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1F-iPqdDRLI9c6AQSTiFdP2Kf4PMwDbfU#list</t>
         </is>
       </c>
-      <c r="AQ29" s="2" t="inlineStr">
+      <c r="BZ29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1RAtLuqUQJ9SGgtaMEZDEjtR3jk5FuWcL#list</t>
         </is>
       </c>
-      <c r="AR29" s="2" t="inlineStr">
+      <c r="CA29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1agDtoJUOA8Mg8wLocpjT-Po5_b9h7U7g#list</t>
         </is>
       </c>
-      <c r="AS29" s="2" t="inlineStr">
+      <c r="CB29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=171sblT8CkF-cTSBtAlkgh4d28k2XN52z#list</t>
         </is>
       </c>
-      <c r="AT29" s="2" t="inlineStr">
+      <c r="CC29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=13JOoHxgLzmSaosd1ef5BAbfPr0i7nTjK#list</t>
         </is>
       </c>
-      <c r="AU29" s="2" t="inlineStr">
+      <c r="CD29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1CDnNYKQzWg7mGyFabrHxR6dDm6LqkvKF#list</t>
         </is>
       </c>
-      <c r="AV29" s="2" t="inlineStr">
+      <c r="CE29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1j90RFVSdLTBFPXQJswNH6ItwLCYG_1ss#list</t>
         </is>
       </c>
-      <c r="AW29" s="2" t="inlineStr">
+      <c r="CF29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1xwo-rRy6n8FDQgujr8znO4M9rBDBDNBs#list</t>
         </is>
       </c>
-      <c r="AX29" s="2" t="inlineStr">
+      <c r="CG29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=10r97qh619FsvT-SLX2HFaFs_je0MlhU4#list</t>
         </is>
       </c>
-      <c r="AY29" s="2" t="inlineStr">
+      <c r="CH29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1BJ_y0DSzMkQvLL6RSkWSl7ZeO9kkHc6O#list</t>
         </is>
       </c>
-      <c r="AZ29" s="2" t="inlineStr">
+      <c r="CI29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=15k-LrRAuxj91ZXzbcHVFhOY91HvKRppP#list</t>
         </is>
       </c>
-      <c r="BA29" s="2" t="inlineStr">
+      <c r="CJ29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1WOBqY_agNshc3s-tNUfs9tWNw5NWEMeb#list</t>
         </is>
       </c>
-      <c r="BB29" s="2" t="inlineStr">
+      <c r="CK29" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1470R1Cy_C_SzmbIbqCpYFhaeT-xhtyQK#list</t>
         </is>
       </c>
+      <c r="CL29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Kp27mWnsDUHlbBvuWjZLmvclKB6RSVg6#list</t>
+        </is>
+      </c>
+      <c r="CM29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YIFfH6Itl9FC48S6LhVz7rSmy4GRwnKp#list</t>
+        </is>
+      </c>
+      <c r="CN29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1byUayd2ACuVtdyPNF6imiWSLNCA1b6vN#list</t>
+        </is>
+      </c>
+      <c r="CO29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1liYc7LVFZLFzm9dvCxF70osdLydez-QC#list</t>
+        </is>
+      </c>
+      <c r="CP29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18Mzuo51w0MvBhb05dNw7XrjF_PBA9vLQ#list</t>
+        </is>
+      </c>
+      <c r="CQ29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11Aw3chvUm8vWsAPW-RkkRWxNDANtHNQU#list</t>
+        </is>
+      </c>
+      <c r="CR29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XXIi1owp2DXgaIKX1NFkL9pgOdPVbsOK#list</t>
+        </is>
+      </c>
+      <c r="CS29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1y8LoJjYRe2IcjjHWcJyBmSjWGLvaoFRA#list</t>
+        </is>
+      </c>
+      <c r="CT29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1w-Sg_y6R7kue92OUuDg_NNBvrH7WVoKa#list</t>
+        </is>
+      </c>
+      <c r="CU29" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1C9X1cyxe3E5pm7blP-R14_NLK-iN-0nz#list</t>
+        </is>
+      </c>
+      <c r="CV29" s="2" t="inlineStr"/>
+      <c r="CW29" s="2" t="inlineStr"/>
+      <c r="CX29" s="2" t="inlineStr"/>
+      <c r="CY29" s="2" t="inlineStr"/>
+      <c r="CZ29" s="2" t="inlineStr"/>
+      <c r="DA29" s="2" t="inlineStr"/>
+      <c r="DB29" s="2" t="inlineStr"/>
+      <c r="DC29" s="2" t="inlineStr"/>
+      <c r="DD29" s="2" t="inlineStr"/>
+      <c r="DE29" s="2" t="inlineStr"/>
+      <c r="DF29" s="2" t="inlineStr"/>
+      <c r="DG29" s="2" t="inlineStr"/>
+      <c r="DH29" s="2" t="inlineStr"/>
+      <c r="DI29" s="2" t="inlineStr"/>
+      <c r="DJ29" s="2" t="inlineStr"/>
+      <c r="DK29" s="2" t="inlineStr"/>
+      <c r="DL29" s="2" t="inlineStr"/>
+      <c r="DM29" s="2" t="inlineStr"/>
+      <c r="DN29" s="2" t="inlineStr"/>
+      <c r="DO29" s="2" t="inlineStr"/>
+      <c r="DP29" s="2" t="inlineStr"/>
+      <c r="DQ29" s="2" t="inlineStr"/>
+      <c r="DR29" s="2" t="inlineStr"/>
+      <c r="DS29" s="2" t="inlineStr"/>
+      <c r="DT29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -7039,107 +10493,457 @@
       </c>
       <c r="AH30" s="2" t="inlineStr">
         <is>
+          <t>Mpumalanga March</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AN30" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AR30" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AT30" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr">
+        <is>
+          <t>Free State February</t>
+        </is>
+      </c>
+      <c r="AV30" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AW30" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="AX30" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="AY30" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AZ30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="BA30" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BB30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BC30" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BD30" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="BE30" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BF30" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BG30" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="BH30" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="BJ30" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BM30" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BN30" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="BO30" s="2" t="inlineStr">
+        <is>
+          <t>Free State March</t>
+        </is>
+      </c>
+      <c r="BP30" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BQ30" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=15lQRWQWQ4iRupI_kg8wC84CiRSG6adYb#list</t>
         </is>
       </c>
-      <c r="AI30" s="2" t="inlineStr">
+      <c r="BR30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1TMVURe1eqhRZNbAUvypTY867NY2eBVeN#list</t>
         </is>
       </c>
-      <c r="AJ30" s="2" t="inlineStr">
+      <c r="BS30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1RmzTDZEqjBqUOPas1ofqgK4v3RI17C5W#list</t>
         </is>
       </c>
-      <c r="AK30" s="2" t="inlineStr">
+      <c r="BT30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1FhQhyrwdSyuRfh_-Do7PMZKrXkF-bERt#list</t>
         </is>
       </c>
-      <c r="AL30" s="2" t="inlineStr">
+      <c r="BU30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1LrzzdFT8fbTfo7VQ-arVp2XnkA4jW8M8#list</t>
         </is>
       </c>
-      <c r="AM30" s="2" t="inlineStr">
+      <c r="BV30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1jEo8kMBY6w0BkMlL0KsJYqF8hA2Ehznv#list</t>
         </is>
       </c>
-      <c r="AN30" s="2" t="inlineStr">
+      <c r="BW30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1VtbgN5MXVG5JDbBWkkl8tYEpVzTVEoFB#list</t>
         </is>
       </c>
-      <c r="AO30" s="2" t="inlineStr">
+      <c r="BX30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1jeRNkbhAEa-j-9Prk73puiguRSBZoaAq#list</t>
         </is>
       </c>
-      <c r="AP30" s="2" t="inlineStr">
+      <c r="BY30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1L30jbO4WR4wzhgBfOi3jAeLnXq9GPZCy#list</t>
         </is>
       </c>
-      <c r="AQ30" s="2" t="inlineStr">
+      <c r="BZ30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1jctD48iM9JUHxtcrXaDZRmTF_vr7iKsC#list</t>
         </is>
       </c>
-      <c r="AR30" s="2" t="inlineStr">
+      <c r="CA30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1gh-yCTsLqbnFo7rl6Dw-eU0yO8o8XKbB#list</t>
         </is>
       </c>
-      <c r="AS30" s="2" t="inlineStr">
+      <c r="CB30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1A9SMhNkg_iibClZdqNvxOMNbvVCKJil_#list</t>
         </is>
       </c>
-      <c r="AT30" s="2" t="inlineStr">
+      <c r="CC30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=18xrDOTHkgWsZcFGqAbmeC9sHQMeNAdSE#list</t>
         </is>
       </c>
-      <c r="AU30" s="2" t="inlineStr">
+      <c r="CD30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=11zcvkibvv4qsxkKHGpMehiGvGa52Mrj9#list</t>
         </is>
       </c>
-      <c r="AV30" s="2" t="inlineStr">
+      <c r="CE30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1T93X1KWUGthNVuf0BzJKVNNCfZF0csJN#list</t>
         </is>
       </c>
-      <c r="AW30" s="2" t="inlineStr">
+      <c r="CF30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1mKwghy_oNxsmTeASIWwXNbD0_yX__qNm#list</t>
         </is>
       </c>
-      <c r="AX30" s="2" t="inlineStr">
+      <c r="CG30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=12cpHGDwt8ejwavX_9KCmLZ_lc3IhPMSE#list</t>
         </is>
       </c>
-      <c r="AY30" s="2" t="inlineStr">
+      <c r="CH30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1l01sBj0yqfav3ZOJraAoinG6GwqxINSe#list</t>
         </is>
       </c>
-      <c r="AZ30" s="2" t="inlineStr">
+      <c r="CI30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1uIzbfFXECBlNcpYe1wJdE1G9nPL6dKm7#list</t>
         </is>
       </c>
-      <c r="BA30" s="2" t="inlineStr">
+      <c r="CJ30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1Ql96QKTsuVCbRZwpdztMNPyjA1QGOgD2#list</t>
         </is>
       </c>
-      <c r="BB30" s="2" t="inlineStr">
+      <c r="CK30" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1tdUlSaxSmhus16vpSgk0uDx4i928DYjI#list</t>
+        </is>
+      </c>
+      <c r="CL30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1JX2-XGuezgsNoz4g6jRi-DctGt6aVcWK#list</t>
+        </is>
+      </c>
+      <c r="CM30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kZBBlDiR8Il-foWAbvR3Up_qAke_u-dG#list</t>
+        </is>
+      </c>
+      <c r="CN30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18d3EgKACmZ17c03xmpeejs2t8wlJy1vv#list</t>
+        </is>
+      </c>
+      <c r="CO30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vYjdt_ZLjYOwDhwyshOBMbtLCinWYbD3#list</t>
+        </is>
+      </c>
+      <c r="CP30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1z-0WBvqxSyC1BwEOebOTrOWlxlWgYblM#list</t>
+        </is>
+      </c>
+      <c r="CQ30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ljep43lPmTj88cdlgtKBgWUleqkHDZFC#list</t>
+        </is>
+      </c>
+      <c r="CR30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18a6FfzYsBifCEqUcbkDEs362i_1b95Wg#list</t>
+        </is>
+      </c>
+      <c r="CS30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1PP-5TAQtLFnRbCqqaegR0gIIKMCF6i9m#list</t>
+        </is>
+      </c>
+      <c r="CT30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1j0OqY-tH1o-FFz7NRCh0DsDMLKieFQfx#list</t>
+        </is>
+      </c>
+      <c r="CU30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1CIKgZGH8t27RNR3LdP4avoPerlgGa1xe#list</t>
+        </is>
+      </c>
+      <c r="CV30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=12sGGBTExsS8s57vnLR-wy6AGQ_u_XZan#list</t>
+        </is>
+      </c>
+      <c r="CW30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Q6rieJpOXE9CrSQwXUrKw0zA-4jrWMDf#list</t>
+        </is>
+      </c>
+      <c r="CX30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19eq0KwW379xACo3bg1_uI_keJfM3s5km#list</t>
+        </is>
+      </c>
+      <c r="CY30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vs7l1Ih-m7izVkF2d6M6Dsftb-R7SpIx#list</t>
+        </is>
+      </c>
+      <c r="CZ30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1CU8ewNiyF1y_64rCXXrw2yrYnRoxP8S0#list</t>
+        </is>
+      </c>
+      <c r="DA30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yH6LrII4aLDG64QLD_kC4ViH0ciDZ5Ji#list</t>
+        </is>
+      </c>
+      <c r="DB30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1AHE16MHvtu-77zPN16_JP6Lfl8zr2xpj#list</t>
+        </is>
+      </c>
+      <c r="DC30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jpD_9s5DByI_x3iRxtiWU_YK59h51ukN#list</t>
+        </is>
+      </c>
+      <c r="DD30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1DAxYqhCQMiEgaItZJSWQIIUN5jvVR1_E#list</t>
+        </is>
+      </c>
+      <c r="DE30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=17us6PIjPemWgHeiW39HG5I2mUs4p8Eq0#list</t>
+        </is>
+      </c>
+      <c r="DF30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ag8JEDCwm_RWVFaO_kr9UzfODbvwhKTs#list</t>
+        </is>
+      </c>
+      <c r="DG30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QOYSa7yHNmqXHR0s2U-enHgDE3SYBUyg#list</t>
+        </is>
+      </c>
+      <c r="DH30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OqCNak6d8SAOCPMvu-fkT4pkK0FvWau7#list</t>
+        </is>
+      </c>
+      <c r="DI30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1frUBXu0eHvQen_jAh-eZiCUMVm3Oz0ub#list</t>
+        </is>
+      </c>
+      <c r="DJ30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BH8fOD9rh_216hzLe3eC0Kgzjd_m7juN#list</t>
+        </is>
+      </c>
+      <c r="DK30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1dqz9IAT_7eG8JCVDh2w8kcd9DUhOLnOy#list</t>
+        </is>
+      </c>
+      <c r="DL30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18CHIM-KrKN-GvAV7HxZR48AYnre9UXUn#list</t>
+        </is>
+      </c>
+      <c r="DM30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1btrcgk1H-UTOv5_xRaRg-9KO0krH7dtd#list</t>
+        </is>
+      </c>
+      <c r="DN30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1H9Say2VAcNLJ5eBVVipGIHNjUA2n3Mk5#list</t>
+        </is>
+      </c>
+      <c r="DO30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_PKh3llXSgxrT5D_qjXQCjkta2FRikrc#list</t>
+        </is>
+      </c>
+      <c r="DP30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jLqmmEPO8zWVCOl-9b2Hxu44in9vX2vm#list</t>
+        </is>
+      </c>
+      <c r="DQ30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-S9g8HSzawjUUTm9YdFayQHY-XO4bZE6#list</t>
+        </is>
+      </c>
+      <c r="DR30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NGfGzgqc8Z7qQ32NahIJuNBQ6-eeHKXK#list</t>
+        </is>
+      </c>
+      <c r="DS30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NOe8KrjT0z4WA2qrPD3YdqwT4OsqGAAS#list</t>
+        </is>
+      </c>
+      <c r="DT30" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Xm0eSgKXbf-n8ER6A7QjKl6ni9Y-wROn#list</t>
         </is>
       </c>
     </row>
@@ -7283,107 +11087,457 @@
       </c>
       <c r="AH31" s="2" t="inlineStr">
         <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AN31" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="AP31" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AR31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="AT31" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="AU31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AV31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng September</t>
+        </is>
+      </c>
+      <c r="AW31" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AX31" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="AY31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AZ31" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="BA31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BB31" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BC31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="BD31" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BE31" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BF31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="BG31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="BH31" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga September</t>
+        </is>
+      </c>
+      <c r="BJ31" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BM31" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BN31" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="BO31" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BP31" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BQ31" s="2" t="inlineStr">
+        <is>
           <t>https://drive.google.com/embeddedfolderview?id=1IpDGDuGQGD0rOkfm-qOGIL1Hf9up4nVk#list</t>
         </is>
       </c>
-      <c r="AI31" s="2" t="inlineStr">
+      <c r="BR31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1lYj_Kq9BmTJD6Ag30tta7gH0n6-LK2Be#list</t>
         </is>
       </c>
-      <c r="AJ31" s="2" t="inlineStr">
+      <c r="BS31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1U2nq_RIMzLtJk_8MTkGWa_wJ7AamcIr0#list</t>
         </is>
       </c>
-      <c r="AK31" s="2" t="inlineStr">
+      <c r="BT31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1CB4T9gAt6PjErPf9qAs9pwP5M9M7U3qH#list</t>
         </is>
       </c>
-      <c r="AL31" s="2" t="inlineStr">
+      <c r="BU31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1nfXJUJXCTklnWmWTtvQ4HCklmSoK5EEE#list</t>
         </is>
       </c>
-      <c r="AM31" s="2" t="inlineStr">
+      <c r="BV31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1qZVFlpN7NMxcxN-xPvmybS1EHmmbN0pV#list</t>
         </is>
       </c>
-      <c r="AN31" s="2" t="inlineStr">
+      <c r="BW31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1S5v-kQ0TEke2-C8H2lNU6uxOM4T0upyh#list</t>
         </is>
       </c>
-      <c r="AO31" s="2" t="inlineStr">
+      <c r="BX31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1JaZ6JOsBT6kDdTEtPUymb1eA3-f8vluj#list</t>
         </is>
       </c>
-      <c r="AP31" s="2" t="inlineStr">
+      <c r="BY31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1KZE2VVFDFG4ZCJk7LZEeE-KFmahXyfP3#list</t>
         </is>
       </c>
-      <c r="AQ31" s="2" t="inlineStr">
+      <c r="BZ31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1HAowR6jDoo0otccEfCMr0ksx2T6r__ED#list</t>
         </is>
       </c>
-      <c r="AR31" s="2" t="inlineStr">
+      <c r="CA31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1XpwxjGed3uZ4af5sxLp2fLx4HRB5VkxL#list</t>
         </is>
       </c>
-      <c r="AS31" s="2" t="inlineStr">
+      <c r="CB31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1aWYg5WsTtsatLjRJ5O9Jy_uayXSgcUuS#list</t>
         </is>
       </c>
-      <c r="AT31" s="2" t="inlineStr">
+      <c r="CC31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1ifJxTqc1TlZw5rABrP0O8QAdFDHdDi32#list</t>
         </is>
       </c>
-      <c r="AU31" s="2" t="inlineStr">
+      <c r="CD31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1G4A3Zatr5264xLT0-FGa3UNcjNs7Ch4U#list</t>
         </is>
       </c>
-      <c r="AV31" s="2" t="inlineStr">
+      <c r="CE31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1RAX0JzWMT7DTfAz0EgnVum1lb82hBYy5#list</t>
         </is>
       </c>
-      <c r="AW31" s="2" t="inlineStr">
+      <c r="CF31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1pyP2Bx21sosaQEz7-8fLscBvt2ZYIkFl#list</t>
         </is>
       </c>
-      <c r="AX31" s="2" t="inlineStr">
+      <c r="CG31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1rYStRBAG41-z60NwpYTkzYyRigSkNtR4#list</t>
         </is>
       </c>
-      <c r="AY31" s="2" t="inlineStr">
+      <c r="CH31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1mJ3zMced12q-QIi9BBnt5XVdvpNsAV8i#list</t>
         </is>
       </c>
-      <c r="AZ31" s="2" t="inlineStr">
+      <c r="CI31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1FjUmBtTasOyPNqJYUb_dPln-NLlml4mK#list</t>
         </is>
       </c>
-      <c r="BA31" s="2" t="inlineStr">
+      <c r="CJ31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1LuyJ4LUNaYqs_wccrbUKQRBZb4nB0AfV#list</t>
         </is>
       </c>
-      <c r="BB31" s="2" t="inlineStr">
+      <c r="CK31" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/embeddedfolderview?id=1HJDu1FobG6iKojWfLR9zxoGsHyZhSWZn#list</t>
+        </is>
+      </c>
+      <c r="CL31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1L0tZCJkPJ3s9DP4pjaDzzp2QgxY_DAHp#list</t>
+        </is>
+      </c>
+      <c r="CM31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_0h0Lw1pjHHYI8AKbr936duxa10_DR2d#list</t>
+        </is>
+      </c>
+      <c r="CN31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jcqwRfGYVxqX7p-QtLLLSbwW48JALN3z#list</t>
+        </is>
+      </c>
+      <c r="CO31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1xWelqs-tzZo2ym8Jtfjr_ijECKm_OiQm#list</t>
+        </is>
+      </c>
+      <c r="CP31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1sQU10LmDWFr6fbPV2D4JcOxX3kvp1tYA#list</t>
+        </is>
+      </c>
+      <c r="CQ31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1KjpcqRcDcx9u6tMdMKFMsfj38tchEK9j#list</t>
+        </is>
+      </c>
+      <c r="CR31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FDaUM14bonPwM4VVEwxHF_mQmJ-e2DdY#list</t>
+        </is>
+      </c>
+      <c r="CS31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qsrOq-rfqJGTCxnFo8uI-8-Ua6-FEA_P#list</t>
+        </is>
+      </c>
+      <c r="CT31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1unWFr_s4mDtHs9LDhOqduBlScnG4PLrI#list</t>
+        </is>
+      </c>
+      <c r="CU31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=13k6dALVnVn1uoDb2R0B4cs0ZwItAFgN0#list</t>
+        </is>
+      </c>
+      <c r="CV31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16pMvCY2fTwctuEPU3yXnia24zGzQmagb#list</t>
+        </is>
+      </c>
+      <c r="CW31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BxLZX_1yssuHytP9iZGr75D_3SNFUE0_#list</t>
+        </is>
+      </c>
+      <c r="CX31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UTa7QgLmN86IBFn-aWp6Do0mxIzDF0FP#list</t>
+        </is>
+      </c>
+      <c r="CY31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rB5Byt1XF-LjQkIHQwQM_p-f9GTz7isr#list</t>
+        </is>
+      </c>
+      <c r="CZ31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ZxIenEf0Cdp4KavRAxC3M7HWvtoEIvls#list</t>
+        </is>
+      </c>
+      <c r="DA31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kbP-LqOeDVug-WcBILzR92qqSTKfhaf-#list</t>
+        </is>
+      </c>
+      <c r="DB31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1VxSXxTWdRTzGLMJUoPMGWscoNQwTMEJz#list</t>
+        </is>
+      </c>
+      <c r="DC31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QV-cySUStbBSk8oJp7FFqvNn6De41nAH#list</t>
+        </is>
+      </c>
+      <c r="DD31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rqbWsiwH1va4SzOQj5hnvD0HP5ugCxk4#list</t>
+        </is>
+      </c>
+      <c r="DE31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ZIv-Q7r9ggXUtVYk-pOYEJmQq7x8QO-P#list</t>
+        </is>
+      </c>
+      <c r="DF31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1SB6t-dqsDmv0Yt9CaudimJWxgqJQKUhy#list</t>
+        </is>
+      </c>
+      <c r="DG31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1G-HwgNG1e5_XrRTtZfU-G3Oz8f66lMKQ#list</t>
+        </is>
+      </c>
+      <c r="DH31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1dS2HSVxtNyHHSc6p7n4aMm31HuzQPuj5#list</t>
+        </is>
+      </c>
+      <c r="DI31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Jnu0MYqIG30wCj2wUi1QptZWUI5z8AS3#list</t>
+        </is>
+      </c>
+      <c r="DJ31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11gqW4XH8EzGOYxKCPfHrYcFwPBYteifD#list</t>
+        </is>
+      </c>
+      <c r="DK31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1tj5b4p0PkWTzvyrxv0Z_2OdTTIaaXGBn#list</t>
+        </is>
+      </c>
+      <c r="DL31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1O0Dpa7AXWphVbNyZuKgzZLwp7kx2q0Xg#list</t>
+        </is>
+      </c>
+      <c r="DM31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IBcScu9fRvauGjww8w94ADn62KFMldQE#list</t>
+        </is>
+      </c>
+      <c r="DN31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nzgb3UgytMAPCICG32eUQNl41T8PwYCn#list</t>
+        </is>
+      </c>
+      <c r="DO31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=17qOWfxUERrdJf8PtbckBo0IfCSNhoExr#list</t>
+        </is>
+      </c>
+      <c r="DP31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ia4TjcFRJczgxEAs32CVcfhmLWrsiCgn#list</t>
+        </is>
+      </c>
+      <c r="DQ31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1GG5HfDhzstqbWokkePlYQqn5InDm3rpv#list</t>
+        </is>
+      </c>
+      <c r="DR31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1w3RpoIYLg6hm2AR9v0elsN5tSScDoMEv#list</t>
+        </is>
+      </c>
+      <c r="DS31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yFpRDQityDLC3wuZq-eu8d_84cXS7sEc#list</t>
+        </is>
+      </c>
+      <c r="DT31" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QbYCMFTa03_1M-qCF7C7MEhq42a52N6i#list</t>
         </is>
       </c>
     </row>

--- a/GovGrade11.xlsx
+++ b/GovGrade11.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GovGrade11" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Papers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2022-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GovGrade11" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Papers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Papers'!$A$1:$D$772</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Papers'!$A$1:$D$772</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,6 +441,5056 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:EA9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026 T9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U8</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2026 U9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T8</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T9</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T10</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T11</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T12</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2025 T13</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U1</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U2</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U3</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U4</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U5</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U6</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U7</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U8</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U11</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U12</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>2025 U13</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T2</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T3</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T4</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T5</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T7</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T8</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T9</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T10</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T11</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T12</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T13</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T14</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T15</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T16</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>2024 T17</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U4</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U5</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U6</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U7</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U8</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U9</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U10</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U11</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U12</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U13</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U14</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U15</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U16</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>2024 U17</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T1</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T2</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T3</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T4</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T5</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T6</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T7</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T8</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T9</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T10</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T11</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T12</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T13</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T14</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>2023 T15</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U1</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U2</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U3</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U4</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U5</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U6</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U7</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U8</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U9</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U10</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U11</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U12</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>2023 U15</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T1</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T2</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T3</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T4</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T5</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T6</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T7</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T8</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T9</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T10</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>2022 T11</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U1</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U2</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U3</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U4</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U5</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U6</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U7</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U8</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U9</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U10</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>2022 U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BNLkoiz4Y9A8022YsDZfsiR4uCg_ov2h#list</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Pl01GgnSLUWAuPCLi7EyMDRAHK1lDi_h#list</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1cBBsl0Ruznlv0_lk47vk5eOMWryNt9PX#list</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1S7OJFW4ZNVjIw06db6mXcf0nfn2FzM1l#list</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga November</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga June</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Free State March</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1i1ZVnFAIh11ZBOyjRqgDWLa6ndNVSVE2#list</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=17rpijarHp65f3X7l7dZOuBvHkvr_s_r7#list</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_aoARbQ_hKvDcN0yyi8H8524aRMl7Aj9#list</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1joFRnzqSdw5XUCk5-Lyiku6XogHef6lD#list</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1T3VSiloSHJ-4o4VDHpxL-NL9VnUn586t#list</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1xv_0fQVpjuwlEJJWi_KIDpKa-F2EWMnl#list</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1aVs0nEGai_TGFCpeNtydS-WP8VypVoxy#list</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19WDlVj25cKkfkgXXfuqrCKUT0Rcossdg#list</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QDeyL6f5o83z3X9rqvTQBE8-KPTp_J_J#list</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="n"/>
+      <c r="AQ2" s="2" t="n"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2" t="n"/>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
+          <t>Northern Cape September</t>
+        </is>
+      </c>
+      <c r="AX2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AY2" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="AZ2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BC2" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="BD2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BG2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RhrBy107HdAeGseVHIrTjLukTLa1pE2x#list</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1htlC9rZg7vFHEn9tGXPXml2Cnw6YO5Bj#list</t>
+        </is>
+      </c>
+      <c r="BM2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1GfnJ_2ykfFG6roR7qITltWWWJ9LNUFw0#list</t>
+        </is>
+      </c>
+      <c r="BN2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ELNDUk6_WZq59evq1aeSDx-P5mVSMGBF#list</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nSBiNWWJY1N6u8Rd5-VcTViCPXpW3KCi#list</t>
+        </is>
+      </c>
+      <c r="BP2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14n4E1e49Av7ufRdHQnm2uHK13DU6lHsp#list</t>
+        </is>
+      </c>
+      <c r="BQ2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14Q1Cu7RObbqGX-6Nb2L9aZ-GoLpP_VP7#list</t>
+        </is>
+      </c>
+      <c r="BR2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bbNG_n4KkfAhnHPNih4ICq79NH_TyTd6#list</t>
+        </is>
+      </c>
+      <c r="BS2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_n3g-ENm1aeWSWPJ56wOsXF5djmsJvPx#list</t>
+        </is>
+      </c>
+      <c r="BT2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QUqEopYeYksT8rEgYDamhrdVKs_PqfqG#list</t>
+        </is>
+      </c>
+      <c r="BU2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=172GOd40ybZty2s9qMPVxPbY1OEfSPY09#list</t>
+        </is>
+      </c>
+      <c r="BV2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1afND2fyUXQv-MgNi3f0FSkP-doudCOio#list</t>
+        </is>
+      </c>
+      <c r="BW2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OxeiTpPqufzDXVS9Ig0FR3aHiYsQpIpF#list</t>
+        </is>
+      </c>
+      <c r="BX2" s="2" t="n"/>
+      <c r="BY2" s="2" t="n"/>
+      <c r="BZ2" s="2" t="n"/>
+      <c r="CA2" s="2" t="n"/>
+      <c r="CB2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="CC2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="CE2" s="2" t="inlineStr">
+        <is>
+          <t>Free State September</t>
+        </is>
+      </c>
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="CH2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="CI2" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="CJ2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="CK2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="CL2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="CM2" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="CN2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="CO2" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="CP2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="CQ2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1AMyi7w8rJVDK4aRNgdEvpwk4ku-PWn5B#list</t>
+        </is>
+      </c>
+      <c r="CR2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1v9czssjA1G5eB2EA-g-KEUv379pEW6Hc#list</t>
+        </is>
+      </c>
+      <c r="CS2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16utpmapUrzzWyXlbwgT5mx3qUveAG7Kk#list</t>
+        </is>
+      </c>
+      <c r="CT2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Y7cfG8QnjoxiO4mOPgkptgGi4XvF9GK1#list</t>
+        </is>
+      </c>
+      <c r="CU2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iNj7jSaW9G4Ir3BSvPLH_eB2cvI-dpFX#list</t>
+        </is>
+      </c>
+      <c r="CV2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YaXGedL1zhMdwbvO2g2e10zCs5W8_LWH#list</t>
+        </is>
+      </c>
+      <c r="CW2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1GUg0_80DgW2Zed6DFygkRr7soPhsT_ND#list</t>
+        </is>
+      </c>
+      <c r="CX2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yTPBFVRbK6QN-YYy-zufjJ1fJrD_HZFq#list</t>
+        </is>
+      </c>
+      <c r="CY2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vFw6BjGRlkCqse1bTGaYAxnaiL7TJfTg#list</t>
+        </is>
+      </c>
+      <c r="CZ2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1e1l_WJZqlu_xmMNHPXQOySfxCDumqL_N#list</t>
+        </is>
+      </c>
+      <c r="DA2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XJk-U-l11QzJIz0p8TI07_km1UqYLRBB#list</t>
+        </is>
+      </c>
+      <c r="DB2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15xhMgtY0KTBAsfnyOf3iEf3wKRsZF0ZU#list</t>
+        </is>
+      </c>
+      <c r="DC2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iEObK9RdGXhg1ah8C1yG6RshBfvXOK_c#list</t>
+        </is>
+      </c>
+      <c r="DD2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UqGMQASSnL1-fx3IDIOUfhdpbGWlBvGH#list</t>
+        </is>
+      </c>
+      <c r="DE2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-pi7dnC-I-3s1cjFchtA5sq6qUrBB-1B#list</t>
+        </is>
+      </c>
+      <c r="DF2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG2" s="2" t="inlineStr">
+        <is>
+          <t>Free State November</t>
+        </is>
+      </c>
+      <c r="DH2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="DI2" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="DJ2" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="DK2" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="DL2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="DM2" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="DN2" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="DO2" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="DP2" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1T_qQGp7UhCjYx_0KAhuPX8AAqXLt0Bd3#list</t>
+        </is>
+      </c>
+      <c r="DR2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1WryZmJhMDm81PxtR0wOUJm1TZlJ7938D#list</t>
+        </is>
+      </c>
+      <c r="DS2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YtgARypSH04yz6kepL1uVaKy6aHpPkqf#list</t>
+        </is>
+      </c>
+      <c r="DT2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1EHHF4wym6NCyBFvvL01gJx4Xje9nnp3P#list</t>
+        </is>
+      </c>
+      <c r="DU2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UySvU9qiZgc7CA-T_lMCCo3_MkMhEa1u#list</t>
+        </is>
+      </c>
+      <c r="DV2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1R7gXff80AxgmWcQwN-b6OmhoaPS6Ifx-#list</t>
+        </is>
+      </c>
+      <c r="DW2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1x2QEGtaufcxggr0Lmqw1nPTCRoJHR_Bk#list</t>
+        </is>
+      </c>
+      <c r="DX2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1q7OwDqIyPqZUcaAjPiDrxmkk8bMul_QX#list</t>
+        </is>
+      </c>
+      <c r="DY2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-M0xG-2lQIEN98HE_i4u_ty4y_BLagB0#list</t>
+        </is>
+      </c>
+      <c r="DZ2" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_u7gK2bXNEwFh9ZxIPUsQ11U9GzIJmoi#list</t>
+        </is>
+      </c>
+      <c r="EA2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ILSbEx09OrugKOSZ9S2LOUqUDxl6w69l#list</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vfvWqQ9kh9jLIElzGt08tiT9riSPuAE1#list</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bG6T3uJH9o_IX7lrPUUU1znYLD94XkNw#list</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1wTqRW_9GIqsEkOGJggD7ejqfWUTQgh2z#list</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1VPmyBaRjaJxupF8Jmrmax3ha8XpocVsI#list</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>North West March</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18UM5OUnEBTV8hJaGhi_ETKn2c6Uv00vv#list</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ngCu9JSUO-XMWzQMYtvYec89BfLHaaMY#list</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1MsG6nnZK_YDWJPDjWl66i_Sk49WxKy19#list</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kxLG1ZQHPs6Dck_PK_FffuyGCsLB1CB9#list</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11KTHokdznKnru8175cC7yOKDl_dqPDJK#list</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Qx2i9FrEq6BFeYtTrnL82CFbadIpOcwb#list</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1uHb1Evf3rMZpMk_OESN7G8oHfUfx5M-0#list</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nhb-iZ8DUoi8AxP-EgCsF1OBTZizbKVE#list</t>
+        </is>
+      </c>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fqEL6xstybEHtL-gg5doGOYyX-87_WuI#list</t>
+        </is>
+      </c>
+      <c r="AP3" s="2" t="n"/>
+      <c r="AQ3" s="2" t="n"/>
+      <c r="AR3" s="2" t="n"/>
+      <c r="AS3" s="2" t="n"/>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="AV3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo November</t>
+        </is>
+      </c>
+      <c r="AW3" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AX3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AY3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AZ3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="BA3" s="2" t="inlineStr">
+        <is>
+          <t>North West September</t>
+        </is>
+      </c>
+      <c r="BB3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="BC3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BD3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BE3" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="BF3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="BG3" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="BH3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BJ3" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga March</t>
+        </is>
+      </c>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1xUILWpltl1210jknhc2pHrVuBad1wyif#list</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11stNj61r_em2IAMN9q_RcUpL1al642nN#list</t>
+        </is>
+      </c>
+      <c r="BM3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1O2bqUFV4Rf97xyoF9foz3PV4wKRKWf8A#list</t>
+        </is>
+      </c>
+      <c r="BN3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1G__IB1tjqgQ4G8fWcfh7zK9iy2-W-jOv#list</t>
+        </is>
+      </c>
+      <c r="BO3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NhvWZKrYkh0eEIr0oqC8hXsCmmWaVo1m#list</t>
+        </is>
+      </c>
+      <c r="BP3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FxUFEvbDYevRRaWsp2n0GUMXMd-8Pdxd#list</t>
+        </is>
+      </c>
+      <c r="BQ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1VlnTDpsD68CkvfSGlkWH7JICjRRKEVy0#list</t>
+        </is>
+      </c>
+      <c r="BR3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14uyWirLI7X_Zz-1vgf8KaYw38ObCsIf6#list</t>
+        </is>
+      </c>
+      <c r="BS3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15zBq7evNUtMGh9T6Nvi43EXTaOiePyvf#list</t>
+        </is>
+      </c>
+      <c r="BT3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IOLntE-Fo68YEyHEsCIJ_KcEnpskdQV2#list</t>
+        </is>
+      </c>
+      <c r="BU3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XeGESgnRrUmhP8J4vfNudPTO_RBLXQ08#list</t>
+        </is>
+      </c>
+      <c r="BV3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1LCnDWDg8HDBrx7nr3xOYsO5FFcFtCH2r#list</t>
+        </is>
+      </c>
+      <c r="BW3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FAkTGYzmapUnuLo37GyS9MxbRmTVcoSu#list</t>
+        </is>
+      </c>
+      <c r="BX3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1O2YZZ-LTn78rQd_NMYZoGtFAC_G6wQIn#list</t>
+        </is>
+      </c>
+      <c r="BY3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fakh80UZPjlksgyznkti3Zlo-zW8OxAl#list</t>
+        </is>
+      </c>
+      <c r="BZ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iOoynXyvv1ArDLMWAbha6lKkmDcqtPgQ#list</t>
+        </is>
+      </c>
+      <c r="CA3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vP59zgJBNRCrSbiqEXHqjG4IMm4mMZSu#list</t>
+        </is>
+      </c>
+      <c r="CB3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="CC3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="CD3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="CE3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="CF3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="CG3" s="2" t="inlineStr">
+        <is>
+          <t>National Term 3</t>
+        </is>
+      </c>
+      <c r="CH3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="CI3" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="CJ3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="CK3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="CL3" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="CM3" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="CN3" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="CO3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CP3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1oQYJUeE4i6kV9pCOek_vhlcq-cB60fsz#list</t>
+        </is>
+      </c>
+      <c r="CR3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Tgr3A5aPiJEu6HBugLa3PM93Gkym1h5K#list</t>
+        </is>
+      </c>
+      <c r="CS3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nBZ8jqJpSUnB-Awmnu1ZnJgSqqxmk-qz#list</t>
+        </is>
+      </c>
+      <c r="CT3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=187XuXC0NK6zImuIZbHpg63VWYyChat0a#list</t>
+        </is>
+      </c>
+      <c r="CU3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1sTstpxeQ8OJSyf5fqK_Smc0onEak9un_#list</t>
+        </is>
+      </c>
+      <c r="CV3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pnY18aB96YP_Cb6l7-rgcaJ3ujRLqweZ#list</t>
+        </is>
+      </c>
+      <c r="CW3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qsLyJs4zup4w3lbNRYi4qpinDjpsWxOm#list</t>
+        </is>
+      </c>
+      <c r="CX3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18UCrZm0pWlRTCx4MMQ83WGneQ6L-EZUf#list</t>
+        </is>
+      </c>
+      <c r="CY3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IboP2sv9T4IaSkPdUGbQVjLWlo6pbrQy#list</t>
+        </is>
+      </c>
+      <c r="CZ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1tqQ_0-0nWBVWrnk0_v--fyDFOY3ChX7z#list</t>
+        </is>
+      </c>
+      <c r="DA3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fXS_MlI1L99j7G8Mf1MXai0RMlJ-ehLk#list</t>
+        </is>
+      </c>
+      <c r="DB3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19tZZzu8_sp0KY5jwLAf9zMA6ojiXXFV9#list</t>
+        </is>
+      </c>
+      <c r="DC3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OQAaU2CBt6w9bghG18vtzFST9-Ben3VN#list</t>
+        </is>
+      </c>
+      <c r="DD3" s="2" t="n"/>
+      <c r="DE3" s="2" t="n"/>
+      <c r="DF3" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG3" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="DH3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DI3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DJ3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DK3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DL3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DM3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DN3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DO3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DP3" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1fyyVnYlNLCRWLeWfrCZOclgjlw-DDHwa#list</t>
+        </is>
+      </c>
+      <c r="DR3" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1d_VKaHoHR4DttEFPjb90JchXSHMjPTo5#list</t>
+        </is>
+      </c>
+      <c r="DS3" s="2" t="n"/>
+      <c r="DT3" s="2" t="n"/>
+      <c r="DU3" s="2" t="n"/>
+      <c r="DV3" s="2" t="n"/>
+      <c r="DW3" s="2" t="n"/>
+      <c r="DX3" s="2" t="n"/>
+      <c r="DY3" s="2" t="n"/>
+      <c r="DZ3" s="2" t="n"/>
+      <c r="EA3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1t7Ruy_7LSeHFm1iDklpBHBenJUcI-ysX#list</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qbz1G0h9MdqfGDdLfRs_hFvg_Xfzrpjk#list</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QDz1Y9zipyiKaV72nluOvu2xsR56DM_-#list</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga June</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qnWLa7Fs7N1X9LpHtvOb-L-rPYR185IE#list</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1e_B7ZMRsNP-DLJG7f9SaH28rK9IMMq9b#list</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-e_OWGH4UZGHkR8MPxIghDLuZ4HfTEZM#list</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1VipE7qp9Co_xbzl2TwaGWrxB-XCopXMI#list</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="n"/>
+      <c r="AL4" s="2" t="n"/>
+      <c r="AM4" s="2" t="n"/>
+      <c r="AN4" s="2" t="n"/>
+      <c r="AO4" s="2" t="n"/>
+      <c r="AP4" s="2" t="n"/>
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2" t="n"/>
+      <c r="AT4" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo November</t>
+        </is>
+      </c>
+      <c r="AV4" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AW4" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="AX4" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga June</t>
+        </is>
+      </c>
+      <c r="AY4" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AZ4" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BA4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BB4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BC4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BD4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14UN3Lu7emOciPOyc11af2V2S6O2EqPLi#list</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1SREIqdL8aqSv1sIJxPgOuOidM4sdNbd8#list</t>
+        </is>
+      </c>
+      <c r="BM4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pgWD3I0_0I6pOcGIp41tPj0ciSzUMwYg#list</t>
+        </is>
+      </c>
+      <c r="BN4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1KipvINHOvclShh6hP3qr0xUaj4tJU8Z2#list</t>
+        </is>
+      </c>
+      <c r="BO4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1HTg7yrkprpKa6d4kPKdSH8g7WVt-tCo1#list</t>
+        </is>
+      </c>
+      <c r="BP4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qH8abS3puOKSdD46843dbViMM-ZhF7EI#list</t>
+        </is>
+      </c>
+      <c r="BQ4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1wnCa1gI8g43fjBEZGVEPWGj1_t-9mirR#list</t>
+        </is>
+      </c>
+      <c r="BR4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nPv4b-a7xTNSK6oSfTd9bcOz6QZcvpd0#list</t>
+        </is>
+      </c>
+      <c r="BS4" s="2" t="n"/>
+      <c r="BT4" s="2" t="n"/>
+      <c r="BU4" s="2" t="n"/>
+      <c r="BV4" s="2" t="n"/>
+      <c r="BW4" s="2" t="n"/>
+      <c r="BX4" s="2" t="n"/>
+      <c r="BY4" s="2" t="n"/>
+      <c r="BZ4" s="2" t="n"/>
+      <c r="CA4" s="2" t="n"/>
+      <c r="CB4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="CC4" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="CD4" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="CE4" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="CF4" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="CG4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CH4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CI4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CJ4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CK4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CL4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CM4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CN4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CO4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CP4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16NWHeXez-ZabNAzhHatykycmacYjnxXO#list</t>
+        </is>
+      </c>
+      <c r="CR4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rztyyjQO6_tigvAT5ye4UghckmawFt6H#list</t>
+        </is>
+      </c>
+      <c r="CS4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1mIZ8WdvR0_1uLZJKHEmdeVdtRECGwCzD#list</t>
+        </is>
+      </c>
+      <c r="CT4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=119xYuPQCAQ7AZSsEdF9wpHtcBOttPDzG#list</t>
+        </is>
+      </c>
+      <c r="CU4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bkvyxXo6VGR8uZqoK30_T6c5oDcY4nJd#list</t>
+        </is>
+      </c>
+      <c r="CV4" s="2" t="n"/>
+      <c r="CW4" s="2" t="n"/>
+      <c r="CX4" s="2" t="n"/>
+      <c r="CY4" s="2" t="n"/>
+      <c r="CZ4" s="2" t="n"/>
+      <c r="DA4" s="2" t="n"/>
+      <c r="DB4" s="2" t="n"/>
+      <c r="DC4" s="2" t="n"/>
+      <c r="DD4" s="2" t="n"/>
+      <c r="DE4" s="2" t="n"/>
+      <c r="DF4" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG4" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="DH4" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="DI4" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="DJ4" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="DK4" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="DL4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DM4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DN4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DO4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DP4" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1acBTs3bYw6MORHp_JPvD9rmqP-y7z2Mn#list</t>
+        </is>
+      </c>
+      <c r="DR4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1LtHbMu6tcExQXLfMWGmy2ufN30Yi1cYC#list</t>
+        </is>
+      </c>
+      <c r="DS4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1uOxAjb0LfVtwmk_AK7t2yQluzMeOk9bo#list</t>
+        </is>
+      </c>
+      <c r="DT4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1lD6lQuLbM6er2hJCvDMTe5oE7Nv4EmFh#list</t>
+        </is>
+      </c>
+      <c r="DU4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14cm3YrMA1A1ZaLq2OSW34sD3xquWBzbR#list</t>
+        </is>
+      </c>
+      <c r="DV4" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1U_fEp9Zd-C9ae3OMT_5sDs_e3iJ0o2cH#list</t>
+        </is>
+      </c>
+      <c r="DW4" s="2" t="n"/>
+      <c r="DX4" s="2" t="n"/>
+      <c r="DY4" s="2" t="n"/>
+      <c r="DZ4" s="2" t="n"/>
+      <c r="EA4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Free State March</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rVhKPh9JIG1EaVgmCtuCCYt5c3U8gw_y#list</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Tv5AbmSYXlxpTXAK9_Rcfh3TZhJDMMB8#list</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Free State March</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ep8XnMIOTqd2jpzoOjDfDdRsCqzH4sa8#list</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qguq6ceoejLWXrS4roP-J8jFjBgkk7nY#list</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1TmzQj6rs8s-t4nE57ediVp7Rbd2wOBtC#list</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1doLBqu6nUGKcZ_j5NfK2aZF8jDDwUorH#list</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1HHwwfjhLbF_sq_lgUDDeM97RWz1i-x1I#list</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1P1f7oEZPrgrLhBULvbAWWwi96zAFh1gW#list</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16nq9u1ikdKi9zhSuM2OFyt3yLWxaCIRo#list</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="n"/>
+      <c r="AO5" s="2" t="n"/>
+      <c r="AP5" s="2" t="n"/>
+      <c r="AQ5" s="2" t="n"/>
+      <c r="AR5" s="2" t="n"/>
+      <c r="AS5" s="2" t="n"/>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga November</t>
+        </is>
+      </c>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AX5" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="AY5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AZ5" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BA5" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="BB5" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BC5" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga March</t>
+        </is>
+      </c>
+      <c r="BD5" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="BE5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YajEZmx7g9NAMdjyIvcwzcOwouj5Alms#list</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11bZiXQgbMt0mei3ARLjUYHzTqsK_mcgu#list</t>
+        </is>
+      </c>
+      <c r="BM5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1JBt2A621mkvP5Nh1z_gaDKGsRoSjHZI-#list</t>
+        </is>
+      </c>
+      <c r="BN5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1iisItRY-NE6AP_fqMALsjUhZwhb6v17B#list</t>
+        </is>
+      </c>
+      <c r="BO5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1MAD_CoecHpq-oUOHxlaWChCDpOhM0vey#list</t>
+        </is>
+      </c>
+      <c r="BP5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1tDwySF4NOSo4XUtzcq2jl40scZDo4f8M#list</t>
+        </is>
+      </c>
+      <c r="BQ5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_AFXqXfH0nNOShqyWO0a0ZixeHNZPtnj#list</t>
+        </is>
+      </c>
+      <c r="BR5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18M3CHtEXnn0iSUmMVgmVN3hKQffsRUTs#list</t>
+        </is>
+      </c>
+      <c r="BS5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1U3W5-JAhWnkltblYdK8kiXZJ2JCe-2Ci#list</t>
+        </is>
+      </c>
+      <c r="BT5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bXxzvgCMXaAJax1kVe_UNFanUw7fdt92#list</t>
+        </is>
+      </c>
+      <c r="BU5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Vs2zF2by0Wvf122qP-ZnwJSqfWdC50cG#list</t>
+        </is>
+      </c>
+      <c r="BV5" s="2" t="n"/>
+      <c r="BW5" s="2" t="n"/>
+      <c r="BX5" s="2" t="n"/>
+      <c r="BY5" s="2" t="n"/>
+      <c r="BZ5" s="2" t="n"/>
+      <c r="CA5" s="2" t="n"/>
+      <c r="CB5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="CC5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="CD5" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="CE5" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="CF5" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="CG5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CH5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CI5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CJ5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CK5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CL5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CM5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CN5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CO5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CP5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pPfh4Oj1MUGuiG9hg4HeSvzplNfyf_kr#list</t>
+        </is>
+      </c>
+      <c r="CR5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1TNEFev3ZHkPt1aqzBDRYpw0nrvQ6adr7#list</t>
+        </is>
+      </c>
+      <c r="CS5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UYEKVoQ0Yw56OEGXKgNW0sqK2URtgwhI#list</t>
+        </is>
+      </c>
+      <c r="CT5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_bS0ZdtaPpaugvraajHyBlRoB87WWcL-#list</t>
+        </is>
+      </c>
+      <c r="CU5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rH4brsaHb5stLeRhPxSmFfjNO1F8Ev7V#list</t>
+        </is>
+      </c>
+      <c r="CV5" s="2" t="n"/>
+      <c r="CW5" s="2" t="n"/>
+      <c r="CX5" s="2" t="n"/>
+      <c r="CY5" s="2" t="n"/>
+      <c r="CZ5" s="2" t="n"/>
+      <c r="DA5" s="2" t="n"/>
+      <c r="DB5" s="2" t="n"/>
+      <c r="DC5" s="2" t="n"/>
+      <c r="DD5" s="2" t="n"/>
+      <c r="DE5" s="2" t="n"/>
+      <c r="DF5" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG5" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="DH5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DI5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DJ5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DK5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DL5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DM5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DN5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DO5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DP5" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1P9aBkXvNeNeVaC2JSmHy1zzu9PNsgim_#list</t>
+        </is>
+      </c>
+      <c r="DR5" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1hBxXgGABY-Tuaonq-1GgwOCAHtbatdVG#list</t>
+        </is>
+      </c>
+      <c r="DS5" s="2" t="n"/>
+      <c r="DT5" s="2" t="n"/>
+      <c r="DU5" s="2" t="n"/>
+      <c r="DV5" s="2" t="n"/>
+      <c r="DW5" s="2" t="n"/>
+      <c r="DX5" s="2" t="n"/>
+      <c r="DY5" s="2" t="n"/>
+      <c r="DZ5" s="2" t="n"/>
+      <c r="EA5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>IsiZulu</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IoLqN1Y9IEwEyBaRMOtAteKRrrGU6VOP#list</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1krSY13SKemdVYxdZxv4aJDIo-buBqhnO#list</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="n"/>
+      <c r="AJ6" s="2" t="n"/>
+      <c r="AK6" s="2" t="n"/>
+      <c r="AL6" s="2" t="n"/>
+      <c r="AM6" s="2" t="n"/>
+      <c r="AN6" s="2" t="n"/>
+      <c r="AO6" s="2" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2" t="n"/>
+      <c r="AT6" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="AU6" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="AW6" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AX6" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="AY6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AZ6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BA6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BB6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BC6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BD6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1c4b0N8tBAeawhWPg6W9ipJcIMC9apF_E#list</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1V_K7VDMPVxffRgoWee0ia98WmkKz3Ilc#list</t>
+        </is>
+      </c>
+      <c r="BM6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=14QfvAvkaJYnsi6mLgpeDgIle_MU4AVBN#list</t>
+        </is>
+      </c>
+      <c r="BN6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16pgL6MWFoEJD0FI_QW5sD9NetbL9AyoZ#list</t>
+        </is>
+      </c>
+      <c r="BO6" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1AAAnP7nKq7OfMZi0K2Hg77P0BoJeTCYY#list</t>
+        </is>
+      </c>
+      <c r="BP6" s="2" t="n"/>
+      <c r="BQ6" s="2" t="n"/>
+      <c r="BR6" s="2" t="n"/>
+      <c r="BS6" s="2" t="n"/>
+      <c r="BT6" s="2" t="n"/>
+      <c r="BU6" s="2" t="n"/>
+      <c r="BV6" s="2" t="n"/>
+      <c r="BW6" s="2" t="n"/>
+      <c r="BX6" s="2" t="n"/>
+      <c r="BY6" s="2" t="n"/>
+      <c r="BZ6" s="2" t="n"/>
+      <c r="CA6" s="2" t="n"/>
+      <c r="CB6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CC6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CD6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CE6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CF6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CG6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CH6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CI6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CJ6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CK6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CL6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CM6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CN6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CO6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CP6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ6" s="2" t="n"/>
+      <c r="CR6" s="2" t="n"/>
+      <c r="CS6" s="2" t="n"/>
+      <c r="CT6" s="2" t="n"/>
+      <c r="CU6" s="2" t="n"/>
+      <c r="CV6" s="2" t="n"/>
+      <c r="CW6" s="2" t="n"/>
+      <c r="CX6" s="2" t="n"/>
+      <c r="CY6" s="2" t="n"/>
+      <c r="CZ6" s="2" t="n"/>
+      <c r="DA6" s="2" t="n"/>
+      <c r="DB6" s="2" t="n"/>
+      <c r="DC6" s="2" t="n"/>
+      <c r="DD6" s="2" t="n"/>
+      <c r="DE6" s="2" t="n"/>
+      <c r="DF6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DG6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DH6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DI6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DJ6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DK6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DL6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DM6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DN6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DO6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DP6" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ6" s="2" t="n"/>
+      <c r="DR6" s="2" t="n"/>
+      <c r="DS6" s="2" t="n"/>
+      <c r="DT6" s="2" t="n"/>
+      <c r="DU6" s="2" t="n"/>
+      <c r="DV6" s="2" t="n"/>
+      <c r="DW6" s="2" t="n"/>
+      <c r="DX6" s="2" t="n"/>
+      <c r="DY6" s="2" t="n"/>
+      <c r="DZ6" s="2" t="n"/>
+      <c r="EA6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Life Science</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19S8yyHcoaJnztP1HPXh8C3XjR2ybGg0s#list</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ovtEhoOY3aKN-ihXM6u2ty5NePoiD6rZ#list</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1v0GziMYR4Zjnh_2xtQg77ZcPQsyGqwHw#list</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1E2uEA5S6FnA9c0eKwAXhkuSrmPrF-284#list</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1bn1Q-yk2_7au-n4cU3pPFAlkYw4nYN_F#list</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1a2OhFk85yqvmfpw5oMFcMP5MnQNMEIVM#list</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IQOGeZ-fgl9U3lY4NAa2i-1-MJOWCy6e#list</t>
+        </is>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1WXCJr9ePJ2erc4qpskbdufsOwBlQDHDM#list</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1F-iPqdDRLI9c6AQSTiFdP2Kf4PMwDbfU#list</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="n"/>
+      <c r="AO7" s="2" t="n"/>
+      <c r="AP7" s="2" t="n"/>
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AS7" s="2" t="n"/>
+      <c r="AT7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU7" s="2" t="inlineStr">
+        <is>
+          <t>Free State November</t>
+        </is>
+      </c>
+      <c r="AV7" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AW7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AX7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="AY7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AZ7" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="BA7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BB7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BC7" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BD7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BE7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BF7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BG7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RAtLuqUQJ9SGgtaMEZDEjtR3jk5FuWcL#list</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1agDtoJUOA8Mg8wLocpjT-Po5_b9h7U7g#list</t>
+        </is>
+      </c>
+      <c r="BM7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=171sblT8CkF-cTSBtAlkgh4d28k2XN52z#list</t>
+        </is>
+      </c>
+      <c r="BN7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=13JOoHxgLzmSaosd1ef5BAbfPr0i7nTjK#list</t>
+        </is>
+      </c>
+      <c r="BO7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1CDnNYKQzWg7mGyFabrHxR6dDm6LqkvKF#list</t>
+        </is>
+      </c>
+      <c r="BP7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1j90RFVSdLTBFPXQJswNH6ItwLCYG_1ss#list</t>
+        </is>
+      </c>
+      <c r="BQ7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1xwo-rRy6n8FDQgujr8znO4M9rBDBDNBs#list</t>
+        </is>
+      </c>
+      <c r="BR7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=10r97qh619FsvT-SLX2HFaFs_je0MlhU4#list</t>
+        </is>
+      </c>
+      <c r="BS7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BJ_y0DSzMkQvLL6RSkWSl7ZeO9kkHc6O#list</t>
+        </is>
+      </c>
+      <c r="BT7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15k-LrRAuxj91ZXzbcHVFhOY91HvKRppP#list</t>
+        </is>
+      </c>
+      <c r="BU7" s="2" t="n"/>
+      <c r="BV7" s="2" t="n"/>
+      <c r="BW7" s="2" t="n"/>
+      <c r="BX7" s="2" t="n"/>
+      <c r="BY7" s="2" t="n"/>
+      <c r="BZ7" s="2" t="n"/>
+      <c r="CA7" s="2" t="n"/>
+      <c r="CB7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="CC7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="CD7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="CE7" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="CF7" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="CG7" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="CH7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CI7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CJ7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CK7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CL7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CM7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CN7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CO7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CP7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1WOBqY_agNshc3s-tNUfs9tWNw5NWEMeb#list</t>
+        </is>
+      </c>
+      <c r="CR7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1470R1Cy_C_SzmbIbqCpYFhaeT-xhtyQK#list</t>
+        </is>
+      </c>
+      <c r="CS7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Kp27mWnsDUHlbBvuWjZLmvclKB6RSVg6#list</t>
+        </is>
+      </c>
+      <c r="CT7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1YIFfH6Itl9FC48S6LhVz7rSmy4GRwnKp#list</t>
+        </is>
+      </c>
+      <c r="CU7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1byUayd2ACuVtdyPNF6imiWSLNCA1b6vN#list</t>
+        </is>
+      </c>
+      <c r="CV7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1liYc7LVFZLFzm9dvCxF70osdLydez-QC#list</t>
+        </is>
+      </c>
+      <c r="CW7" s="2" t="n"/>
+      <c r="CX7" s="2" t="n"/>
+      <c r="CY7" s="2" t="n"/>
+      <c r="CZ7" s="2" t="n"/>
+      <c r="DA7" s="2" t="n"/>
+      <c r="DB7" s="2" t="n"/>
+      <c r="DC7" s="2" t="n"/>
+      <c r="DD7" s="2" t="n"/>
+      <c r="DE7" s="2" t="n"/>
+      <c r="DF7" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG7" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="DH7" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="DI7" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="DJ7" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="DK7" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="DL7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DM7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DN7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DO7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DP7" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18Mzuo51w0MvBhb05dNw7XrjF_PBA9vLQ#list</t>
+        </is>
+      </c>
+      <c r="DR7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11Aw3chvUm8vWsAPW-RkkRWxNDANtHNQU#list</t>
+        </is>
+      </c>
+      <c r="DS7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XXIi1owp2DXgaIKX1NFkL9pgOdPVbsOK#list</t>
+        </is>
+      </c>
+      <c r="DT7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1y8LoJjYRe2IcjjHWcJyBmSjWGLvaoFRA#list</t>
+        </is>
+      </c>
+      <c r="DU7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1w-Sg_y6R7kue92OUuDg_NNBvrH7WVoKa#list</t>
+        </is>
+      </c>
+      <c r="DV7" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1C9X1cyxe3E5pm7blP-R14_NLK-iN-0nz#list</t>
+        </is>
+      </c>
+      <c r="DW7" s="2" t="n"/>
+      <c r="DX7" s="2" t="n"/>
+      <c r="DY7" s="2" t="n"/>
+      <c r="DZ7" s="2" t="n"/>
+      <c r="EA7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga March</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>North West March</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Northern Cape March</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=15lQRWQWQ4iRupI_kg8wC84CiRSG6adYb#list</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1TMVURe1eqhRZNbAUvypTY867NY2eBVeN#list</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RmzTDZEqjBqUOPas1ofqgK4v3RI17C5W#list</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FhQhyrwdSyuRfh_-Do7PMZKrXkF-bERt#list</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1LrzzdFT8fbTfo7VQ-arVp2XnkA4jW8M8#list</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jEo8kMBY6w0BkMlL0KsJYqF8hA2Ehznv#list</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1VtbgN5MXVG5JDbBWkkl8tYEpVzTVEoFB#list</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jeRNkbhAEa-j-9Prk73puiguRSBZoaAq#list</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1L30jbO4WR4wzhgBfOi3jAeLnXq9GPZCy#list</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga March</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jctD48iM9JUHxtcrXaDZRmTF_vr7iKsC#list</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1gh-yCTsLqbnFo7rl6Dw-eU0yO8o8XKbB#list</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1A9SMhNkg_iibClZdqNvxOMNbvVCKJil_#list</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18xrDOTHkgWsZcFGqAbmeC9sHQMeNAdSE#list</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11zcvkibvv4qsxkKHGpMehiGvGa52Mrj9#list</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1T93X1KWUGthNVuf0BzJKVNNCfZF0csJN#list</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1mKwghy_oNxsmTeASIWwXNbD0_yX__qNm#list</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=12cpHGDwt8ejwavX_9KCmLZ_lc3IhPMSE#list</t>
+        </is>
+      </c>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1l01sBj0yqfav3ZOJraAoinG6GwqxINSe#list</t>
+        </is>
+      </c>
+      <c r="AP8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1uIzbfFXECBlNcpYe1wJdE1G9nPL6dKm7#list</t>
+        </is>
+      </c>
+      <c r="AQ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ql96QKTsuVCbRZwpdztMNPyjA1QGOgD2#list</t>
+        </is>
+      </c>
+      <c r="AR8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1tdUlSaxSmhus16vpSgk0uDx4i928DYjI#list</t>
+        </is>
+      </c>
+      <c r="AS8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1JX2-XGuezgsNoz4g6jRi-DctGt6aVcWK#list</t>
+        </is>
+      </c>
+      <c r="AT8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="AV8" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AW8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="AX8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AY8" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="AZ8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BA8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BB8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BC8" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="BD8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BE8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BF8" s="2" t="inlineStr">
+        <is>
+          <t>Free State February</t>
+        </is>
+      </c>
+      <c r="BG8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BH8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kZBBlDiR8Il-foWAbvR3Up_qAke_u-dG#list</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18d3EgKACmZ17c03xmpeejs2t8wlJy1vv#list</t>
+        </is>
+      </c>
+      <c r="BM8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vYjdt_ZLjYOwDhwyshOBMbtLCinWYbD3#list</t>
+        </is>
+      </c>
+      <c r="BN8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1z-0WBvqxSyC1BwEOebOTrOWlxlWgYblM#list</t>
+        </is>
+      </c>
+      <c r="BO8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ljep43lPmTj88cdlgtKBgWUleqkHDZFC#list</t>
+        </is>
+      </c>
+      <c r="BP8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18a6FfzYsBifCEqUcbkDEs362i_1b95Wg#list</t>
+        </is>
+      </c>
+      <c r="BQ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1PP-5TAQtLFnRbCqqaegR0gIIKMCF6i9m#list</t>
+        </is>
+      </c>
+      <c r="BR8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1j0OqY-tH1o-FFz7NRCh0DsDMLKieFQfx#list</t>
+        </is>
+      </c>
+      <c r="BS8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1CIKgZGH8t27RNR3LdP4avoPerlgGa1xe#list</t>
+        </is>
+      </c>
+      <c r="BT8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=12sGGBTExsS8s57vnLR-wy6AGQ_u_XZan#list</t>
+        </is>
+      </c>
+      <c r="BU8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Q6rieJpOXE9CrSQwXUrKw0zA-4jrWMDf#list</t>
+        </is>
+      </c>
+      <c r="BV8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=19eq0KwW379xACo3bg1_uI_keJfM3s5km#list</t>
+        </is>
+      </c>
+      <c r="BW8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1vs7l1Ih-m7izVkF2d6M6Dsftb-R7SpIx#list</t>
+        </is>
+      </c>
+      <c r="BX8" s="2" t="n"/>
+      <c r="BY8" s="2" t="n"/>
+      <c r="BZ8" s="2" t="n"/>
+      <c r="CA8" s="2" t="n"/>
+      <c r="CB8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="CC8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="CD8" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="CE8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="CF8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="CG8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="CH8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="CI8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="CJ8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="CK8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="CL8" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="CM8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CN8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CO8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CP8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1CU8ewNiyF1y_64rCXXrw2yrYnRoxP8S0#list</t>
+        </is>
+      </c>
+      <c r="CR8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yH6LrII4aLDG64QLD_kC4ViH0ciDZ5Ji#list</t>
+        </is>
+      </c>
+      <c r="CS8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1AHE16MHvtu-77zPN16_JP6Lfl8zr2xpj#list</t>
+        </is>
+      </c>
+      <c r="CT8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jpD_9s5DByI_x3iRxtiWU_YK59h51ukN#list</t>
+        </is>
+      </c>
+      <c r="CU8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1DAxYqhCQMiEgaItZJSWQIIUN5jvVR1_E#list</t>
+        </is>
+      </c>
+      <c r="CV8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=17us6PIjPemWgHeiW39HG5I2mUs4p8Eq0#list</t>
+        </is>
+      </c>
+      <c r="CW8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ag8JEDCwm_RWVFaO_kr9UzfODbvwhKTs#list</t>
+        </is>
+      </c>
+      <c r="CX8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QOYSa7yHNmqXHR0s2U-enHgDE3SYBUyg#list</t>
+        </is>
+      </c>
+      <c r="CY8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1OqCNak6d8SAOCPMvu-fkT4pkK0FvWau7#list</t>
+        </is>
+      </c>
+      <c r="CZ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1frUBXu0eHvQen_jAh-eZiCUMVm3Oz0ub#list</t>
+        </is>
+      </c>
+      <c r="DA8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BH8fOD9rh_216hzLe3eC0Kgzjd_m7juN#list</t>
+        </is>
+      </c>
+      <c r="DB8" s="2" t="n"/>
+      <c r="DC8" s="2" t="n"/>
+      <c r="DD8" s="2" t="n"/>
+      <c r="DE8" s="2" t="n"/>
+      <c r="DF8" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="DH8" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="DI8" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="DJ8" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="DK8" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="DL8" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="DM8" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="DN8" s="2" t="inlineStr">
+        <is>
+          <t>Free State March</t>
+        </is>
+      </c>
+      <c r="DO8" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="DP8" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="DQ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1dqz9IAT_7eG8JCVDh2w8kcd9DUhOLnOy#list</t>
+        </is>
+      </c>
+      <c r="DR8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=18CHIM-KrKN-GvAV7HxZR48AYnre9UXUn#list</t>
+        </is>
+      </c>
+      <c r="DS8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1btrcgk1H-UTOv5_xRaRg-9KO0krH7dtd#list</t>
+        </is>
+      </c>
+      <c r="DT8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1H9Say2VAcNLJ5eBVVipGIHNjUA2n3Mk5#list</t>
+        </is>
+      </c>
+      <c r="DU8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_PKh3llXSgxrT5D_qjXQCjkta2FRikrc#list</t>
+        </is>
+      </c>
+      <c r="DV8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jLqmmEPO8zWVCOl-9b2Hxu44in9vX2vm#list</t>
+        </is>
+      </c>
+      <c r="DW8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1-S9g8HSzawjUUTm9YdFayQHY-XO4bZE6#list</t>
+        </is>
+      </c>
+      <c r="DX8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NGfGzgqc8Z7qQ32NahIJuNBQ6-eeHKXK#list</t>
+        </is>
+      </c>
+      <c r="DY8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1NOe8KrjT0z4WA2qrPD3YdqwT4OsqGAAS#list</t>
+        </is>
+      </c>
+      <c r="DZ8" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Xm0eSgKXbf-n8ER6A7QjKl6ni9Y-wROn#list</t>
+        </is>
+      </c>
+      <c r="EA8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Physical Sciences</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Northern Cape June</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IpDGDuGQGD0rOkfm-qOGIL1Hf9up4nVk#list</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1lYj_Kq9BmTJD6Ag30tta7gH0n6-LK2Be#list</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1U2nq_RIMzLtJk_8MTkGWa_wJ7AamcIr0#list</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1CB4T9gAt6PjErPf9qAs9pwP5M9M7U3qH#list</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nfXJUJXCTklnWmWTtvQ4HCklmSoK5EEE#list</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga June</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>North West March</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qZVFlpN7NMxcxN-xPvmybS1EHmmbN0pV#list</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1S5v-kQ0TEke2-C8H2lNU6uxOM4T0upyh#list</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1JaZ6JOsBT6kDdTEtPUymb1eA3-f8vluj#list</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1KZE2VVFDFG4ZCJk7LZEeE-KFmahXyfP3#list</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1HAowR6jDoo0otccEfCMr0ksx2T6r__ED#list</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1XpwxjGed3uZ4af5sxLp2fLx4HRB5VkxL#list</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1aWYg5WsTtsatLjRJ5O9Jy_uayXSgcUuS#list</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ifJxTqc1TlZw5rABrP0O8QAdFDHdDi32#list</t>
+        </is>
+      </c>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1G4A3Zatr5264xLT0-FGa3UNcjNs7Ch4U#list</t>
+        </is>
+      </c>
+      <c r="AP9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1RAX0JzWMT7DTfAz0EgnVum1lb82hBYy5#list</t>
+        </is>
+      </c>
+      <c r="AQ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1pyP2Bx21sosaQEz7-8fLscBvt2ZYIkFl#list</t>
+        </is>
+      </c>
+      <c r="AR9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rYStRBAG41-z60NwpYTkzYyRigSkNtR4#list</t>
+        </is>
+      </c>
+      <c r="AS9" s="2" t="n"/>
+      <c r="AT9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="AU9" s="2" t="inlineStr">
+        <is>
+          <t>Free State November</t>
+        </is>
+      </c>
+      <c r="AV9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal November</t>
+        </is>
+      </c>
+      <c r="AW9" s="2" t="inlineStr">
+        <is>
+          <t>North West November</t>
+        </is>
+      </c>
+      <c r="AX9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="AY9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="AZ9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="BA9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="BB9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="BC9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo June</t>
+        </is>
+      </c>
+      <c r="BD9" s="2" t="inlineStr">
+        <is>
+          <t>North West June</t>
+        </is>
+      </c>
+      <c r="BE9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape March</t>
+        </is>
+      </c>
+      <c r="BF9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal March</t>
+        </is>
+      </c>
+      <c r="BG9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="BH9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1mJ3zMced12q-QIi9BBnt5XVdvpNsAV8i#list</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FjUmBtTasOyPNqJYUb_dPln-NLlml4mK#list</t>
+        </is>
+      </c>
+      <c r="BM9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1LuyJ4LUNaYqs_wccrbUKQRBZb4nB0AfV#list</t>
+        </is>
+      </c>
+      <c r="BN9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1HJDu1FobG6iKojWfLR9zxoGsHyZhSWZn#list</t>
+        </is>
+      </c>
+      <c r="BO9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1L0tZCJkPJ3s9DP4pjaDzzp2QgxY_DAHp#list</t>
+        </is>
+      </c>
+      <c r="BP9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1_0h0Lw1pjHHYI8AKbr936duxa10_DR2d#list</t>
+        </is>
+      </c>
+      <c r="BQ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1jcqwRfGYVxqX7p-QtLLLSbwW48JALN3z#list</t>
+        </is>
+      </c>
+      <c r="BR9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1xWelqs-tzZo2ym8Jtfjr_ijECKm_OiQm#list</t>
+        </is>
+      </c>
+      <c r="BS9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1sQU10LmDWFr6fbPV2D4JcOxX3kvp1tYA#list</t>
+        </is>
+      </c>
+      <c r="BT9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1KjpcqRcDcx9u6tMdMKFMsfj38tchEK9j#list</t>
+        </is>
+      </c>
+      <c r="BU9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1FDaUM14bonPwM4VVEwxHF_mQmJ-e2DdY#list</t>
+        </is>
+      </c>
+      <c r="BV9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1qsrOq-rfqJGTCxnFo8uI-8-Ua6-FEA_P#list</t>
+        </is>
+      </c>
+      <c r="BW9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1unWFr_s4mDtHs9LDhOqduBlScnG4PLrI#list</t>
+        </is>
+      </c>
+      <c r="BX9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=13k6dALVnVn1uoDb2R0B4cs0ZwItAFgN0#list</t>
+        </is>
+      </c>
+      <c r="BY9" s="2" t="n"/>
+      <c r="BZ9" s="2" t="n"/>
+      <c r="CA9" s="2" t="n"/>
+      <c r="CB9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="CC9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="CD9" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="CE9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape September</t>
+        </is>
+      </c>
+      <c r="CF9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng September</t>
+        </is>
+      </c>
+      <c r="CG9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal September</t>
+        </is>
+      </c>
+      <c r="CH9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo September</t>
+        </is>
+      </c>
+      <c r="CI9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="CJ9" s="2" t="inlineStr">
+        <is>
+          <t>Free State June</t>
+        </is>
+      </c>
+      <c r="CK9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="CL9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="CM9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng March</t>
+        </is>
+      </c>
+      <c r="CN9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="CO9" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="CP9" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="CQ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=16pMvCY2fTwctuEPU3yXnia24zGzQmagb#list</t>
+        </is>
+      </c>
+      <c r="CR9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1BxLZX_1yssuHytP9iZGr75D_3SNFUE0_#list</t>
+        </is>
+      </c>
+      <c r="CS9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1UTa7QgLmN86IBFn-aWp6Do0mxIzDF0FP#list</t>
+        </is>
+      </c>
+      <c r="CT9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rB5Byt1XF-LjQkIHQwQM_p-f9GTz7isr#list</t>
+        </is>
+      </c>
+      <c r="CU9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ZxIenEf0Cdp4KavRAxC3M7HWvtoEIvls#list</t>
+        </is>
+      </c>
+      <c r="CV9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1kbP-LqOeDVug-WcBILzR92qqSTKfhaf-#list</t>
+        </is>
+      </c>
+      <c r="CW9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1VxSXxTWdRTzGLMJUoPMGWscoNQwTMEJz#list</t>
+        </is>
+      </c>
+      <c r="CX9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QV-cySUStbBSk8oJp7FFqvNn6De41nAH#list</t>
+        </is>
+      </c>
+      <c r="CY9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1rqbWsiwH1va4SzOQj5hnvD0HP5ugCxk4#list</t>
+        </is>
+      </c>
+      <c r="CZ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1ZIv-Q7r9ggXUtVYk-pOYEJmQq7x8QO-P#list</t>
+        </is>
+      </c>
+      <c r="DA9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1SB6t-dqsDmv0Yt9CaudimJWxgqJQKUhy#list</t>
+        </is>
+      </c>
+      <c r="DB9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1G-HwgNG1e5_XrRTtZfU-G3Oz8f66lMKQ#list</t>
+        </is>
+      </c>
+      <c r="DC9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1dS2HSVxtNyHHSc6p7n4aMm31HuzQPuj5#list</t>
+        </is>
+      </c>
+      <c r="DD9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Jnu0MYqIG30wCj2wUi1QptZWUI5z8AS3#list</t>
+        </is>
+      </c>
+      <c r="DE9" s="2" t="n"/>
+      <c r="DF9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape November</t>
+        </is>
+      </c>
+      <c r="DG9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng November</t>
+        </is>
+      </c>
+      <c r="DH9" s="2" t="inlineStr">
+        <is>
+          <t>National November</t>
+        </is>
+      </c>
+      <c r="DI9" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga September</t>
+        </is>
+      </c>
+      <c r="DJ9" s="2" t="inlineStr">
+        <is>
+          <t>National September</t>
+        </is>
+      </c>
+      <c r="DK9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape June</t>
+        </is>
+      </c>
+      <c r="DL9" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng June</t>
+        </is>
+      </c>
+      <c r="DM9" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu Natal June</t>
+        </is>
+      </c>
+      <c r="DN9" s="2" t="inlineStr">
+        <is>
+          <t>National June</t>
+        </is>
+      </c>
+      <c r="DO9" s="2" t="inlineStr">
+        <is>
+          <t>Limpopo March</t>
+        </is>
+      </c>
+      <c r="DP9" s="2" t="inlineStr">
+        <is>
+          <t>National March</t>
+        </is>
+      </c>
+      <c r="DQ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=11gqW4XH8EzGOYxKCPfHrYcFwPBYteifD#list</t>
+        </is>
+      </c>
+      <c r="DR9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1tj5b4p0PkWTzvyrxv0Z_2OdTTIaaXGBn#list</t>
+        </is>
+      </c>
+      <c r="DS9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1O0Dpa7AXWphVbNyZuKgzZLwp7kx2q0Xg#list</t>
+        </is>
+      </c>
+      <c r="DT9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1IBcScu9fRvauGjww8w94ADn62KFMldQE#list</t>
+        </is>
+      </c>
+      <c r="DU9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1nzgb3UgytMAPCICG32eUQNl41T8PwYCn#list</t>
+        </is>
+      </c>
+      <c r="DV9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=17qOWfxUERrdJf8PtbckBo0IfCSNhoExr#list</t>
+        </is>
+      </c>
+      <c r="DW9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1Ia4TjcFRJczgxEAs32CVcfhmLWrsiCgn#list</t>
+        </is>
+      </c>
+      <c r="DX9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1GG5HfDhzstqbWokkePlYQqn5InDm3rpv#list</t>
+        </is>
+      </c>
+      <c r="DY9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1w3RpoIYLg6hm2AR9v0elsN5tSScDoMEv#list</t>
+        </is>
+      </c>
+      <c r="DZ9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1yFpRDQityDLC3wuZq-eu8d_84cXS7sEc#list</t>
+        </is>
+      </c>
+      <c r="EA9" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/embeddedfolderview?id=1QbYCMFTa03_1M-qCF7C7MEhq42a52N6i#list</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:GB31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -14606,7 +19657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
